--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13 03:04:49</t>
+          <t>2026-06-14 03:07:24</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13 02:00:00</t>
+          <t>2026-06-14 02:00:00</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. NEW Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 7 days 800 total 5 Objectives 94% 6% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. NEW Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 6 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. NEW Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 7 days 6 Objectives 87% 13% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. NEW Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 6 days 6 Objectives 90% 10% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 6 days 5 Objectives 79% 21% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 79% 21% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 6 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 6 days 1,500 total 5 Objectives 95% 5% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 5 days 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Path to Glory! Path to Glory! - EA SPORTS FC 26 Objectives Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. Path to Glory! Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. 170 Tokens Evo Unlock Expires in 2 days 500 total 9 Objectives 86% 14% Rewards 500 SP 90 Tokens Award Evo Unlock 40 Tokens Evo Unlock 170 Tokens Evo Unlock 1x 3x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 4x 85+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 82+ Rare Gold Players Pack 1x 10x 81+ Rare Gold Players Pack Brazil vs. Morocco Assist 5 goals in the Path to Glory Live Event while having min. 4 players from Brazil or Morocco in your starting 11. 500 SP Qatar vs. Switzerland Win 3 matches in the Path to Glory Live Event while having min. 4 players from Qatar or Switzerland in your starting 11. 90 Tokens 3X 84+ Rare Gold Players Pack Austria vs. Türkiye Score 5 goals in the Path to Glory Live Event while having min. 4 players from Austria or Turkiye in your starting 11. 3X 86+ Rare Gold Players Pack Canada vs. Bosnia and Herzegovina Win 2 matches in the Path to Glory Live Event while having min. 4 players from Canada or Bosnia and Herzegovina in your starting 11. 4X 85+ Rare Gold Players Pack United States vs. Paraguay Play 2 matches in the Path to Glory Live Event while having min. 4 players from USA or Paraguay in your starting 11. 7X 84+ Rare Gold Players Pack Mexico vs. South Africa Score 3 goals in the Path to Glory Live Event while having min. 4 players from Mexico or South Africa in your starting 11. Award South Korea vs. Czechia Score 2 goals with Finesse Shots in the Path to Glory Live Event while having min. 4 players from South Korea or Czechia in your starting 11. Earn an Evo consumable. All EVO details can be previewed. Evo Unlock Score 10 Score 10 goals in the Path to Glory Live Event. 40 Tokens 7X 82+ Rare Gold Players Pack Score 1 Score 1 goal in the Path to Glory Live Event. Earn a Cosmetic EVO. All EVO details can be previewed. Evo Unlock 10X 81+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Path to Glory! Path to Glory! - EA SPORTS FC 26 Objectives Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. Path to Glory! Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. 170 Tokens Evo Unlock Expires in 23 hours 500 total 9 Objectives 86% 14% Rewards 500 SP 90 Tokens Award Evo Unlock 40 Tokens Evo Unlock 170 Tokens Evo Unlock 1x 3x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 4x 85+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 82+ Rare Gold Players Pack 1x 10x 81+ Rare Gold Players Pack Brazil vs. Morocco Assist 5 goals in the Path to Glory Live Event while having min. 4 players from Brazil or Morocco in your starting 11. 500 SP Qatar vs. Switzerland Win 3 matches in the Path to Glory Live Event while having min. 4 players from Qatar or Switzerland in your starting 11. 90 Tokens 3X 84+ Rare Gold Players Pack Austria vs. Türkiye Score 5 goals in the Path to Glory Live Event while having min. 4 players from Austria or Turkiye in your starting 11. 3X 86+ Rare Gold Players Pack Canada vs. Bosnia and Herzegovina Win 2 matches in the Path to Glory Live Event while having min. 4 players from Canada or Bosnia and Herzegovina in your starting 11. 4X 85+ Rare Gold Players Pack United States vs. Paraguay Play 2 matches in the Path to Glory Live Event while having min. 4 players from USA or Paraguay in your starting 11. 7X 84+ Rare Gold Players Pack Mexico vs. South Africa Score 3 goals in the Path to Glory Live Event while having min. 4 players from Mexico or South Africa in your starting 11. Award South Korea vs. Czechia Score 2 goals with Finesse Shots in the Path to Glory Live Event while having min. 4 players from South Korea or Czechia in your starting 11. Earn an Evo consumable. All EVO details can be previewed. Evo Unlock Score 10 Score 10 goals in the Path to Glory Live Event. 40 Tokens 7X 82+ Rare Gold Players Pack Score 1 Score 1 goal in the Path to Glory Live Event. Earn a Cosmetic EVO. All EVO details can be previewed. Evo Unlock 10X 81+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 6 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 5 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 27 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 26 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 27 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 26 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 27 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 26 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 27 days 7 Objectives 90% 10% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 26 days 7 Objectives 90% 10% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4962,17 +4962,17 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -5038,17 +5038,17 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -5114,17 +5114,17 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -5190,17 +5190,17 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -5266,17 +5266,17 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5494,17 +5494,17 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5570,17 +5570,17 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 7 days 800 total 5 Objectives 94% 6%</t>
+          <t>NEW Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 6 days 800 total 5 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -17278,12 +17278,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NEW Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 7 days 6 Objectives 87% 13%</t>
+          <t>NEW Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 6 days 6 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -17315,12 +17315,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 6 days 5 Objectives 79% 21%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 79% 21%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -17352,12 +17352,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 6 days 2,000 total 3 of 5 Objectives 94% 6%</t>
+          <t>Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -17389,12 +17389,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 6 days 1,500 total 5 Objectives 95% 5%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 5 days 1,500 total 5 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -17426,22 +17426,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory! Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. 170 Tokens Evo Unlock Expires in 2 days 500 total 9 Objectives 86% 14%</t>
+          <t>Path to Glory! Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. 170 Tokens Evo Unlock Expires in 23 hours 500 total 9 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6/15 02:00</t>
+          <t>6/15 01:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00+09:00</t>
+          <t>2026-06-15T01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17463,12 +17463,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 6 days 190 total 2 Objectives 92% 8%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 5 days 190 total 2 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -17500,12 +17500,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 27 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 26 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -17537,12 +17537,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 27 days 5 Objectives 89% 11%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 26 days 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -17574,12 +17574,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 27 days 1 Objectives 91% 9%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 26 days 1 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -17611,12 +17611,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 27 days 7 Objectives 90% 10%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 26 days 7 Objectives 90% 10%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. NEW Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 7 days 800 total 5 Objectives 94% 6% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. NEW Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 6 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. NEW Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 7 days 6 Objectives 87% 13% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. NEW Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 6 days 6 Objectives 90% 10% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18612,7 +18612,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 6 days 5 Objectives 79% 21% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 79% 21% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 6 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 6 days 1,500 total 5 Objectives 95% 5% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 5 days 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18678,7 +18678,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Path to Glory! Path to Glory! - EA SPORTS FC 26 Objectives Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. Path to Glory! Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. 170 Tokens Evo Unlock Expires in 2 days 500 total 9 Objectives 86% 14% Rewards 500 SP 90 Tokens Award Evo Unlock 40 Tokens Evo Unlock 170 Tokens Evo Unlock 1x 3x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 4x 85+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 82+ Rare Gold Players Pack 1x 10x 81+ Rare Gold Players Pack Brazil vs. Morocco Assist 5 goals in the Path to Glory Live Event while having min. 4 players from Brazil or Morocco in your starting 11. 500 SP Qatar vs. Switzerland Win 3 matches in the Path to Glory Live Event while having min. 4 players from Qatar or Switzerland in your starting 11. 90 Tokens 3X 84+ Rare Gold Players Pack Austria vs. Türkiye Score 5 goals in the Path to Glory Live Event while having min. 4 players from Austria or Turkiye in your starting 11. 3X 86+ Rare Gold Players Pack Canada vs. Bosnia and Herzegovina Win 2 matches in the Path to Glory Live Event while having min. 4 players from Canada or Bosnia and Herzegovina in your starting 11. 4X 85+ Rare Gold Players Pack United States vs. Paraguay Play 2 matches in the Path to Glory Live Event while having min. 4 players from USA or Paraguay in your starting 11. 7X 84+ Rare Gold Players Pack Mexico vs. South Africa Score 3 goals in the Path to Glory Live Event while having min. 4 players from Mexico or South Africa in your starting 11. Award South Korea vs. Czechia Score 2 goals with Finesse Shots in the Path to Glory Live Event while having min. 4 players from South Korea or Czechia in your starting 11. Earn an Evo consumable. All EVO details can be previewed. Evo Unlock Score 10 Score 10 goals in the Path to Glory Live Event. 40 Tokens 7X 82+ Rare Gold Players Pack Score 1 Score 1 goal in the Path to Glory Live Event. Earn a Cosmetic EVO. All EVO details can be previewed. Evo Unlock 10X 81+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Path to Glory! Path to Glory! - EA SPORTS FC 26 Objectives Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. Path to Glory! Celebrate some of the week's standout international matches in the Path to Glory Live Event with this themed Objective! Earn packs, FOF Tokens, SP, one celebration item, and EVO Rewards. All rewards are untradeable. 170 Tokens Evo Unlock Expires in 23 hours 500 total 9 Objectives 86% 14% Rewards 500 SP 90 Tokens Award Evo Unlock 40 Tokens Evo Unlock 170 Tokens Evo Unlock 1x 3x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 4x 85+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 82+ Rare Gold Players Pack 1x 10x 81+ Rare Gold Players Pack Brazil vs. Morocco Assist 5 goals in the Path to Glory Live Event while having min. 4 players from Brazil or Morocco in your starting 11. 500 SP Qatar vs. Switzerland Win 3 matches in the Path to Glory Live Event while having min. 4 players from Qatar or Switzerland in your starting 11. 90 Tokens 3X 84+ Rare Gold Players Pack Austria vs. Türkiye Score 5 goals in the Path to Glory Live Event while having min. 4 players from Austria or Turkiye in your starting 11. 3X 86+ Rare Gold Players Pack Canada vs. Bosnia and Herzegovina Win 2 matches in the Path to Glory Live Event while having min. 4 players from Canada or Bosnia and Herzegovina in your starting 11. 4X 85+ Rare Gold Players Pack United States vs. Paraguay Play 2 matches in the Path to Glory Live Event while having min. 4 players from USA or Paraguay in your starting 11. 7X 84+ Rare Gold Players Pack Mexico vs. South Africa Score 3 goals in the Path to Glory Live Event while having min. 4 players from Mexico or South Africa in your starting 11. Award South Korea vs. Czechia Score 2 goals with Finesse Shots in the Path to Glory Live Event while having min. 4 players from South Korea or Czechia in your starting 11. Earn an Evo consumable. All EVO details can be previewed. Evo Unlock Score 10 Score 10 goals in the Path to Glory Live Event. 40 Tokens 7X 82+ Rare Gold Players Pack Score 1 Score 1 goal in the Path to Glory Live Event. Earn a Cosmetic EVO. All EVO details can be previewed. Evo Unlock 10X 81+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 6 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 5 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 27 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 26 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 27 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 26 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18766,7 +18766,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 27 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 26 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 27 days 7 Objectives 90% 10% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 26 days 7 Objectives 90% 10% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 05:29:05</t>
+          <t>2026-06-17 05:14:09</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 02:00:00</t>
+          <t>2026-06-17 02:00:00</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. NEW Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 7 days 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 6 days 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. NEW Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 7 days 10 Objectives 34% 66% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 6 days 10 Objectives 28% 72% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 4 days 6 Objectives 91% 9% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 3 days 6 Objectives 91% 9% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 4 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 3 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 78% 22% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 77% 23% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 3 days 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 2 days 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 23 days 7 Objectives 90% 10% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 22 days 7 Objectives 88% 12% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 23 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 22 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 23 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 22 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 23 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 22 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 3 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 2 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -17466,17 +17466,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NEW Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens</t>
+          <t>Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 7 days 500 total 5 Objectives 53% 47%</t>
+          <t>Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 6 days 500 total 5 Objectives 53% 47%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NEW Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o</t>
+          <t>Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NEW Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 7 days 10 Objectives 34% 66%</t>
+          <t>Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 6 days 10 Objectives 28% 72%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -17545,12 +17545,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 4 days 6 Objectives 91% 9%</t>
+          <t>Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 3 days 6 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -17582,12 +17582,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 4 days 800 total 5 Objectives 93% 7%</t>
+          <t>Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 3 days 800 total 5 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -17619,12 +17619,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 78% 22%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -17656,12 +17656,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 94% 6%</t>
+          <t>Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -17693,12 +17693,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 3 days 1,500 total 5 Objectives 96% 4%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 2 days 1,500 total 5 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -17730,12 +17730,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 23 days 7 Objectives 90% 10%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 22 days 7 Objectives 88% 12%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -17767,12 +17767,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 23 days 1 Objectives 91% 9%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 22 days 1 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -17804,12 +17804,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 23 days 5 Objectives 89% 11%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 22 days 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -17841,12 +17841,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 23 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 22 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -17878,12 +17878,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 3 days 190 total 2 Objectives 92% 8%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 2 days 190 total 2 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. NEW Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 7 days 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 6 days 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. NEW Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 7 days 10 Objectives 34% 66% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 6 days 10 Objectives 28% 72% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 4 days 6 Objectives 91% 9% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 3 days 6 Objectives 91% 9% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 4 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 3 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18923,7 +18923,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 78% 22% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 77% 23% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 3 days 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 2 days 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18989,7 +18989,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 23 days 7 Objectives 90% 10% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 22 days 7 Objectives 88% 12% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 23 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 22 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 23 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 22 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19055,7 +19055,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 23 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 22 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 3 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 2 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17 05:14:09</t>
+          <t>2026-06-18 04:25:52</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17 02:00:00</t>
+          <t>2026-06-18 02:00:00</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 6 days 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 5 days 500 total 5 Objectives 54% 46% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 6 days 10 Objectives 28% 72% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 5 days 10 Objectives 27% 73% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 3 days 6 Objectives 91% 9% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 2 days 6 Objectives 91% 9% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 3 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 2 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -866,22 +866,22 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 77% 23% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 78% 22% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -966,22 +966,22 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 2 days 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 22 hours 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 22 days 7 Objectives 88% 12% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 21 days 7 Objectives 89% 11% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 22 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 21 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 22 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 21 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 22 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 21 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1216,22 +1216,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 2 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 22 hours 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1635,7 +1635,7 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Ons Voetbal Is Van Iedereen Ons Voetbal Is Van Iedereen - EA SPORTS FC 26 Objectives Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Ons Voetbal Is Van Iedereen Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Gold Pack Expires in 3 months 5 Objectives 48% 52% Rewards Ons Voetbal Is Van Iedereen Background Tifo Ons Voetbal Is Van Iedereen Tifo Ons Voetbal Is Van Iedereen Ons Voetbal Is Van Iedereen Stadium Theme Badge 1x Gold Pack Score 6 Score 6 goals in any Ultimate Team game mode using an Eredivisie player. Ons Voetbal Is Van Iedereen Background Tifo Score 3 Score 3 goals in any Ultimate Team game mode using an Eredivisie player. Ons Voetbal Is Van Iedereen Tifo Play 3 Play 3 matches in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Ons Voetbal Is Van Iedereen Play 2 Play 2 matches in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Ons Voetbal Is Van Iedereen Stadium Theme Play 1 Play 1 match in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Badge © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Ons Voetbal Is Van Iedereen Ons Voetbal Is Van Iedereen - EA SPORTS FC 26 Objectives Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Ons Voetbal Is Van Iedereen Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Gold Pack Expires in 3 months 5 Objectives 47% 53% Rewards Ons Voetbal Is Van Iedereen Background Tifo Ons Voetbal Is Van Iedereen Tifo Ons Voetbal Is Van Iedereen Ons Voetbal Is Van Iedereen Stadium Theme Badge 1x Gold Pack Score 6 Score 6 goals in any Ultimate Team game mode using an Eredivisie player. Ons Voetbal Is Van Iedereen Background Tifo Score 3 Score 3 goals in any Ultimate Team game mode using an Eredivisie player. Ons Voetbal Is Van Iedereen Tifo Play 3 Play 3 matches in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Ons Voetbal Is Van Iedereen Play 2 Play 2 matches in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Ons Voetbal Is Van Iedereen Stadium Theme Play 1 Play 1 match in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Badge © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4420,17 +4420,17 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -4648,17 +4648,17 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -4724,17 +4724,17 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4800,17 +4800,17 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4876,17 +4876,17 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4952,17 +4952,17 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -5028,17 +5028,17 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -5256,17 +5256,17 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -5408,17 +5408,17 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5484,17 +5484,17 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5564,17 +5564,17 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5640,17 +5640,17 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5720,17 +5720,17 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -5800,17 +5800,17 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7196,17 +7196,17 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
@@ -7272,17 +7272,17 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
@@ -7348,17 +7348,17 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 6 days 500 total 5 Objectives 53% 47%</t>
+          <t>Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 5 days 500 total 5 Objectives 54% 46%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 6 days 10 Objectives 28% 72%</t>
+          <t>Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 5 days 10 Objectives 27% 73%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -17545,12 +17545,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 3 days 6 Objectives 91% 9%</t>
+          <t>Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 2 days 6 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -17582,12 +17582,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 3 days 800 total 5 Objectives 93% 7%</t>
+          <t>Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 2 days 800 total 5 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -17619,22 +17619,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 77% 23%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 78% 22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17656,22 +17656,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 94% 6%</t>
+          <t>Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 94% 6%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17693,22 +17693,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 2 days 1,500 total 5 Objectives 96% 4%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 22 hours 1,500 total 5 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
     </row>
@@ -17730,12 +17730,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 22 days 7 Objectives 88% 12%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 21 days 7 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -17767,12 +17767,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 22 days 1 Objectives 91% 9%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 21 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -17804,12 +17804,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 22 days 5 Objectives 89% 11%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 21 days 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -17841,12 +17841,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 22 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 21 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -17878,22 +17878,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 2 days 190 total 2 Objectives 92% 8%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 22 hours 190 total 2 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6/19 02:00</t>
+          <t>6/19 00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T02:00+09:00</t>
+          <t>2026-06-19T00:00+09:00</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Ons Voetbal Is Van Iedereen Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Gold Pack Expires in 3 months 5 Objectives 48% 52%</t>
+          <t>Ons Voetbal Is Van Iedereen Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Gold Pack Expires in 3 months 5 Objectives 47% 53%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 6 days 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 5 days 500 total 5 Objectives 54% 46% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 6 days 10 Objectives 28% 72% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 5 days 10 Objectives 27% 73% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 3 days 6 Objectives 91% 9% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Asia &amp; Oceania Journey of Nations Asia &amp; Oceania - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Asia &amp; Oceania Compete in the Journey of Nations Asia &amp; Oceania Live Event to earn exclusive rewards! All rewards are untradeable. 87+ Rare Gold Player Pack Expires in 2 days 6 Objectives 91% 9% Rewards Shadow Award Hunter 1x 2x 84+ Rare Gold Players Pack 1x 5x 81+ Rare Gold Players Pack 1x 5x 80+ Rare Gold Players Pack 1x 87+ Rare Gold Player Pack Win 3 Win 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Shadow Play 3 Play 3 matches in the Journey of Nations Asia &amp; Oceania Live Event. Award Win 2 Win 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 2X 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Asia &amp; Oceania Live Event. 5X 81+ Rare Gold Players Pack Win 1 Win 1 match in the Journey of Nations Asia &amp; Oceania Live Event. 5X 80+ Rare Gold Players Pack Play 1 Play 1 match in the Journey of Nations Asia &amp; Oceania Live Event. Hunter © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 3 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Path to Glory Week 2 Path to Glory Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. Path to Glory Week 2 Complete all the challenges to earn Festival of Football Tokens and SP. All rewards are Untradeable. 20 Tokens Expires in 2 days 800 total 5 Objectives 93% 7% Rewards 800 SP 20 Tokens 15 Tokens 10 Tokens 20 Tokens Goal Getter Score a total of 40 goals in any Ultimate Team Game Mode. 20 Tokens Domination Win 4 games by 3 goals or more in Squad Battles matches on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions/Rush). 300 SP Finesse Glory Score 3 goals with a Finesse Shot in any Ultimate Team Game Mode while having at least 4 players from Australia, Uzbekistan, Qatar or New Zealand in your starting 11. 15 Tokens Path to Glory Win 5 matches in any Ultimate Team Game Mode while having at least 1 Path to Glory or National Pride Player Item in your starting 11. 500 SP The Underdogs Win 6 games in any Ultimate Team Game Mode while having at least 1 Player Item from Saudi Arabia, South Korea and Japan in your starting 11. 10 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18923,7 +18923,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 77% 23% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 78% 22% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 2 Season 8 Weekly Play 2 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 2 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 94% 6% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 2 days 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 22 hours 1,500 total 5 Objectives 96% 4% Rewards 1,500 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Canada. 200 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 200 SP Buy 10 Buy 10 Player Items on the Transfer Market. 200 SP List 10 List 10 Player Items on the Transfer Market. 200 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -18989,7 +18989,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 22 days 7 Objectives 88% 12% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 21 days 7 Objectives 89% 11% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 22 days 1 Objectives 91% 9% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 21 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 22 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 21 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19055,7 +19055,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 22 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 21 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 2 days 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 90 SP Expires in 22 hours 190 total 2 Objectives 92% 8% Rewards 190 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Ons Voetbal Is Van Iedereen Ons Voetbal Is Van Iedereen - EA SPORTS FC 26 Objectives Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Ons Voetbal Is Van Iedereen Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Gold Pack Expires in 3 months 5 Objectives 48% 52% Rewards Ons Voetbal Is Van Iedereen Background Tifo Ons Voetbal Is Van Iedereen Tifo Ons Voetbal Is Van Iedereen Ons Voetbal Is Van Iedereen Stadium Theme Badge 1x Gold Pack Score 6 Score 6 goals in any Ultimate Team game mode using an Eredivisie player. Ons Voetbal Is Van Iedereen Background Tifo Score 3 Score 3 goals in any Ultimate Team game mode using an Eredivisie player. Ons Voetbal Is Van Iedereen Tifo Play 3 Play 3 matches in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Ons Voetbal Is Van Iedereen Play 2 Play 2 matches in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Ons Voetbal Is Van Iedereen Stadium Theme Play 1 Play 1 match in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Badge © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Ons Voetbal Is Van Iedereen Ons Voetbal Is Van Iedereen - EA SPORTS FC 26 Objectives Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Ons Voetbal Is Van Iedereen Complete this objective and earn exclusive Ons Voetbal Is Van Iedereen stadium items. All rewards are untradeable. Gold Pack Expires in 3 months 5 Objectives 47% 53% Rewards Ons Voetbal Is Van Iedereen Background Tifo Ons Voetbal Is Van Iedereen Tifo Ons Voetbal Is Van Iedereen Ons Voetbal Is Van Iedereen Stadium Theme Badge 1x Gold Pack Score 6 Score 6 goals in any Ultimate Team game mode using an Eredivisie player. Ons Voetbal Is Van Iedereen Background Tifo Score 3 Score 3 goals in any Ultimate Team game mode using an Eredivisie player. Ons Voetbal Is Van Iedereen Tifo Play 3 Play 3 matches in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Ons Voetbal Is Van Iedereen Play 2 Play 2 matches in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Ons Voetbal Is Van Iedereen Stadium Theme Play 1 Play 1 match in any Ultimate Team game mode while using Min. 1 Eredivisie player in your starting 11. Badge © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21 03:10:34</t>
+          <t>2026-06-22 03:19:25</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21 02:00:00</t>
+          <t>2026-06-22 02:00:00</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; International Legends: Flash Rush International Legends: Flash Rush - EA SPORTS FC 26 Objectives Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. NEW International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 4 days 4 of 5 Objectives 11% 89% Rewards 3x 2x 83+ Rare Gold Players Pack 2x 3x 82+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Win 3 Win 3 Rush matches in the "International Legends" Flash Rush Event. 3X 82+ Rare Gold Players Pack Assist in 5 Assist at least 1 goal in 5 separate matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the "International Legends" Flash Rush Event while using any FOF GOTG player. 3X 82+ Rare Gold Players Pack Rush Points Earn 40,000 Rush Points. 2X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; International Legends: Flash Rush International Legends: Flash Rush - EA SPORTS FC 26 Objectives Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 3 days 4 of 5 Objectives 11% 89% Rewards 3x 2x 83+ Rare Gold Players Pack 2x 3x 82+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Win 3 Win 3 Rush matches in the "International Legends" Flash Rush Event. 3X 82+ Rare Gold Players Pack Assist in 5 Assist at least 1 goal in 5 separate matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the "International Legends" Flash Rush Event while using any FOF GOTG player. 3X 82+ Rare Gold Players Pack Rush Points Earn 40,000 Rush Points. 2X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 80% 20% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 5 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 6 days 450 total 10 Objectives 85% 15% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 5 days 450 total 10 Objectives 86% 14% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 6 days 350 total 10 Objectives 94% 6% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 5 days 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 66% 34% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 4 days 5 Objectives 66% 34% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 4 days 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 19 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 18 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 5 days 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 4 days 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 5 days 175 total 2 Objectives 96% 4% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 4 days 175 total 2 Objectives 96% 4% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 19 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 18 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 2 days 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 23 hours 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1216,22 +1216,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 2 days 10 Objectives 27% 73% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 23 hours 10 Objectives 27% 73% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 19 days 7 Objectives 85% 15% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 18 days 7 Objectives 85% 15% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 19 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 18 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 19 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 18 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 19 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 18 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Mastery Live Events Mastery - EA SPORTS FC 26 Objectives Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Live Events Mastery Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Stadium Trophy 5 Objectives 85% 15% Rewards Stadium Trophy Stadium Trophy 1x Rare Players Pack 1x Premium Gold Players Pack 1x 2x 75+ Rare Gold Players Pack 1x x2 Players Pack 150 Live Events Matches Win 150 Ultimate Team Live Events matches. Rare Players Pack 75 Live Events Matches Win 75 Ultimate Team Live Events matches. Stadium Trophy 50 Live Events Matches Win 50 Ultimate Team Live Events matches. Premium Gold Players Pack 25 Live Events Matches Win 25 Ultimate Team Live Events matches. 2X 75+ Rare Gold Players Pack 10 Live Events Matches Win 10 Ultimate Team Live Events matches. X2 Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Mastery Live Events Mastery - EA SPORTS FC 26 Objectives Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Live Events Mastery Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Stadium Trophy 5 Objectives 86% 14% Rewards Stadium Trophy Stadium Trophy 1x Rare Players Pack 1x Premium Gold Players Pack 1x 2x 75+ Rare Gold Players Pack 1x x2 Players Pack 150 Live Events Matches Win 150 Ultimate Team Live Events matches. Rare Players Pack 75 Live Events Matches Win 75 Ultimate Team Live Events matches. Stadium Trophy 50 Live Events Matches Win 50 Ultimate Team Live Events matches. Premium Gold Players Pack 25 Live Events Matches Win 25 Ultimate Team Live Events matches. 2X 75+ Rare Gold Players Pack 10 Live Events Matches Win 10 Ultimate Team Live Events matches. X2 Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Mastery Squad Battles Mastery - EA SPORTS FC 26 Objectives Keep battling over the year to prove you are a Squad Battles Master! Squad Battles Mastery Keep battling over the year to prove you are a Squad Battles Master! Stadium Trophy 5 Objectives 87% 13% Rewards Stadium Trophy Stadium Trophy 1x Jumbo Rare Players Pack 1x Prime Gold Players Pack 1x 2x 75+ Rare Gold Players Pack 1x 75+ Rare Gold Player Pack 250 Squad Battles Wins Win 250 Matches in Squad Battles on any difficulty. Jumbo Rare Players Pack 100 Squad Battles Wins Win 100 Matches in Squad Battles on any difficulty. Stadium Trophy 50 Squad Battles Wins Win 50 Matches in Squad Battles on any difficulty. Prime Gold Players Pack 25 Squad Battles Wins Win 25 Matches in Squad Battles on any difficulty. 2X 75+ Rare Gold Players Pack 10 Squad Battles Wins Win 10 Matches in Squad Battles on any difficulty. 75+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Mastery Squad Battles Mastery - EA SPORTS FC 26 Objectives Keep battling over the year to prove you are a Squad Battles Master! Squad Battles Mastery Keep battling over the year to prove you are a Squad Battles Master! Stadium Trophy 5 Objectives 88% 13% Rewards Stadium Trophy Stadium Trophy 1x Jumbo Rare Players Pack 1x Prime Gold Players Pack 1x 2x 75+ Rare Gold Players Pack 1x 75+ Rare Gold Player Pack 250 Squad Battles Wins Win 250 Matches in Squad Battles on any difficulty. Jumbo Rare Players Pack 100 Squad Battles Wins Win 100 Matches in Squad Battles on any difficulty. Stadium Trophy 50 Squad Battles Wins Win 50 Matches in Squad Battles on any difficulty. Prime Gold Players Pack 25 Squad Battles Wins Win 25 Matches in Squad Battles on any difficulty. 2X 75+ Rare Gold Players Pack 10 Squad Battles Wins Win 10 Matches in Squad Battles on any difficulty. 75+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7504,17 +7504,17 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
@@ -7576,17 +7576,17 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -7648,17 +7648,17 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
@@ -7720,17 +7720,17 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -7792,17 +7792,17 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
@@ -7864,17 +7864,17 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
@@ -7936,17 +7936,17 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -8080,17 +8080,17 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
@@ -8152,17 +8152,17 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -8224,17 +8224,17 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
@@ -8296,17 +8296,17 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -19738,17 +19738,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NEW International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack</t>
+          <t>International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 4 days 4 of 5 Objectives 11% 89%</t>
+          <t>International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 3 days 4 of 5 Objectives 11% 89%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -19780,12 +19780,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 80% 20%</t>
+          <t>Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 5 days 6 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -19817,12 +19817,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 6 days 450 total 10 Objectives 85% 15%</t>
+          <t>Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 5 days 450 total 10 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -19854,12 +19854,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 6 days 350 total 10 Objectives 94% 6%</t>
+          <t>Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 5 days 350 total 10 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -19891,12 +19891,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 66% 34%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 4 days 5 Objectives 66% 34%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -19928,12 +19928,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 95% 5%</t>
+          <t>Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 4 days 2,000 total 3 of 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -19965,12 +19965,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 19 days 3,000 total 5 Objectives 95% 5%</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 18 days 3,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -20002,12 +20002,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 5 days 2,000 total 5 Objectives 95% 5%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 4 days 2,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -20039,12 +20039,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 5 days 175 total 2 Objectives 96% 4%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 4 days 175 total 2 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -20076,12 +20076,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 19 days 2,000 total 3 Objectives 85% 15%</t>
+          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 18 days 2,000 total 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -20113,22 +20113,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 2 days 500 total 5 Objectives 53% 47%</t>
+          <t>Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 23 hours 500 total 5 Objectives 53% 47%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20150,22 +20150,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 2 days 10 Objectives 27% 73%</t>
+          <t>Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 23 hours 10 Objectives 27% 73%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6/23 02:00</t>
+          <t>6/23 01:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T02:00+09:00</t>
+          <t>2026-06-23T01:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20187,12 +20187,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 19 days 7 Objectives 85% 15%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 18 days 7 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -20224,12 +20224,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 19 days 1 Objectives 92% 8%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 18 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -20261,12 +20261,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 19 days 5 Objectives 89% 11%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 18 days 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -20298,12 +20298,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 19 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 18 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Live Events Mastery Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Stadium Trophy 5 Objectives 85% 15%</t>
+          <t>Live Events Mastery Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Stadium Trophy 5 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Squad Battles Mastery Keep battling over the year to prove you are a Squad Battles Master! Stadium Trophy 5 Objectives 87% 13%</t>
+          <t>Squad Battles Mastery Keep battling over the year to prove you are a Squad Battles Master! Stadium Trophy 5 Objectives 88% 13%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -21255,7 +21255,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; International Legends: Flash Rush International Legends: Flash Rush - EA SPORTS FC 26 Objectives Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. NEW International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 4 days 4 of 5 Objectives 11% 89% Rewards 3x 2x 83+ Rare Gold Players Pack 2x 3x 82+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Win 3 Win 3 Rush matches in the "International Legends" Flash Rush Event. 3X 82+ Rare Gold Players Pack Assist in 5 Assist at least 1 goal in 5 separate matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the "International Legends" Flash Rush Event while using any FOF GOTG player. 3X 82+ Rare Gold Players Pack Rush Points Earn 40,000 Rush Points. 2X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; International Legends: Flash Rush International Legends: Flash Rush - EA SPORTS FC 26 Objectives Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 3 days 4 of 5 Objectives 11% 89% Rewards 3x 2x 83+ Rare Gold Players Pack 2x 3x 82+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Win 3 Win 3 Rush matches in the "International Legends" Flash Rush Event. 3X 82+ Rare Gold Players Pack Assist in 5 Assist at least 1 goal in 5 separate matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the "International Legends" Flash Rush Event while using any FOF GOTG player. 3X 82+ Rare Gold Players Pack Rush Points Earn 40,000 Rush Points. 2X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21277,7 +21277,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 80% 20% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 5 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 6 days 450 total 10 Objectives 85% 15% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 5 days 450 total 10 Objectives 86% 14% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 6 days 350 total 10 Objectives 94% 6% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 5 days 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 66% 34% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 4 days 5 Objectives 66% 34% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21365,7 +21365,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 4 days 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 19 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 18 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 5 days 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 4 days 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21431,7 +21431,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 5 days 175 total 2 Objectives 96% 4% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 4 days 175 total 2 Objectives 96% 4% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21453,7 +21453,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 19 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 18 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21475,7 +21475,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 2 days 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Bonus Objective Festival of Football Gauntlet Bonus Objective - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. Festival of Football Gauntlet Bonus Objective Compete in the Festival of Football Gauntlet and earn exclusive rewards! All rewards are untradeable. 50 Tokens Expires in 23 hours 500 total 5 Objectives 53% 47% Rewards 500 SP 10 Tokens 25 Tokens 50 Tokens 1x 7x 82+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack Score 1 Score 1 goal in the Festival of Football Gauntlet. 7X 82+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet. 500 SP Complete 2 series Play 10 matches in the Festival of Football Gauntlet. 10 Tokens Score 14 Score at least 1 goal in 14 separate matches in the Festival of Football Gauntlet. 7X 84+ Rare Gold Players Pack Complete 4 series with 1 win Complete at least 4 Festival of Football Gauntlet series, winning at least 1 round per series. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21497,7 +21497,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 2 days 10 Objectives 27% 73% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet Festival of Football Gauntlet - EA SPORTS FC 26 Objectives Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Festival of Football Gauntlet Complete challenges in the Festival of Football Gauntlet and earn big rewards! All rewards are Untradeable. Samuel Eto'o Expires in 23 hours 10 Objectives 27% 73% Rewards 20 Tokens 30 Tokens Evo Unlock 1 Of 4 88+ Rare Gold Players 1 Of 2 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick 1x 4x 85+ Rare Gold Players Pack 1x 10x 85+ Rare Gold Players Pack 1x 5x 86+ Rare Gold Players Pack 1x 4x 90+ Rare Gold Players Pack 1x 7x 88+ Rare Gold Players Pack 1x 3x 93+ FOF PTG Team 2 Players Pack (Untradeable) Round Runner Play 5 matches in the Festival of Football Gauntlet. 20 Tokens Hat Trick Win at least 3 matches within a single round in the Festival of Football Gauntlet. 30 Tokens Double Down Win at least 3 matches within a single round in the Festival of Football Gauntlet, twice. 4X 85+ Rare Gold Players Pack Triple Crown Win at least 3 matches within a single round in the Festival of Football Gauntlet, three times. Evo Unlock Quad Strike Win at least 4 matches within a single round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players Double Quad Win at least 4 matches within a single round in the Festival of Football Gauntlet, twice. 10X 85+ Rare Gold Players Pack Quad Dynasty Win at least 4 matches within a single round in the Festival of Football Gauntlet, three times. 5X 86+ Rare Gold Players Pack 1 Of 2 89+ Rare Gold Player Pick Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet. 1 Of 4 88+ Rare Gold Players 1 Of 4 89+ Rare Gold Player Pick Double Perfect Complete a Perfect Round, twice in the Festival of Football Gauntlet. 4X 90+ Rare Gold Players Pack Triple Perfect Complete a Perfect Round, three times in the Festival of Football Gauntlet. 7X 88+ Rare Gold Players Pack 3X 93+ Fof Ptg Team 2 Players Pack (Untradeable) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21519,7 +21519,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 19 days 7 Objectives 85% 15% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 18 days 7 Objectives 85% 15% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21541,7 +21541,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 19 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 18 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21563,7 +21563,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 19 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 18 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 19 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 18 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22157,7 +22157,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Mastery Live Events Mastery - EA SPORTS FC 26 Objectives Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Live Events Mastery Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Stadium Trophy 5 Objectives 85% 15% Rewards Stadium Trophy Stadium Trophy 1x Rare Players Pack 1x Premium Gold Players Pack 1x 2x 75+ Rare Gold Players Pack 1x x2 Players Pack 150 Live Events Matches Win 150 Ultimate Team Live Events matches. Rare Players Pack 75 Live Events Matches Win 75 Ultimate Team Live Events matches. Stadium Trophy 50 Live Events Matches Win 50 Ultimate Team Live Events matches. Premium Gold Players Pack 25 Live Events Matches Win 25 Ultimate Team Live Events matches. 2X 75+ Rare Gold Players Pack 10 Live Events Matches Win 10 Ultimate Team Live Events matches. X2 Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Live Events Mastery Live Events Mastery - EA SPORTS FC 26 Objectives Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Live Events Mastery Generate that winning feeling in Ultimate Team Live Events! All rewards are Untradeable. Stadium Trophy 5 Objectives 86% 14% Rewards Stadium Trophy Stadium Trophy 1x Rare Players Pack 1x Premium Gold Players Pack 1x 2x 75+ Rare Gold Players Pack 1x x2 Players Pack 150 Live Events Matches Win 150 Ultimate Team Live Events matches. Rare Players Pack 75 Live Events Matches Win 75 Ultimate Team Live Events matches. Stadium Trophy 50 Live Events Matches Win 50 Ultimate Team Live Events matches. Premium Gold Players Pack 25 Live Events Matches Win 25 Ultimate Team Live Events matches. 2X 75+ Rare Gold Players Pack 10 Live Events Matches Win 10 Ultimate Team Live Events matches. X2 Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22311,7 +22311,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Mastery Squad Battles Mastery - EA SPORTS FC 26 Objectives Keep battling over the year to prove you are a Squad Battles Master! Squad Battles Mastery Keep battling over the year to prove you are a Squad Battles Master! Stadium Trophy 5 Objectives 87% 13% Rewards Stadium Trophy Stadium Trophy 1x Jumbo Rare Players Pack 1x Prime Gold Players Pack 1x 2x 75+ Rare Gold Players Pack 1x 75+ Rare Gold Player Pack 250 Squad Battles Wins Win 250 Matches in Squad Battles on any difficulty. Jumbo Rare Players Pack 100 Squad Battles Wins Win 100 Matches in Squad Battles on any difficulty. Stadium Trophy 50 Squad Battles Wins Win 50 Matches in Squad Battles on any difficulty. Prime Gold Players Pack 25 Squad Battles Wins Win 25 Matches in Squad Battles on any difficulty. 2X 75+ Rare Gold Players Pack 10 Squad Battles Wins Win 10 Matches in Squad Battles on any difficulty. 75+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Squad Battles Mastery Squad Battles Mastery - EA SPORTS FC 26 Objectives Keep battling over the year to prove you are a Squad Battles Master! Squad Battles Mastery Keep battling over the year to prove you are a Squad Battles Master! Stadium Trophy 5 Objectives 88% 13% Rewards Stadium Trophy Stadium Trophy 1x Jumbo Rare Players Pack 1x Prime Gold Players Pack 1x 2x 75+ Rare Gold Players Pack 1x 75+ Rare Gold Player Pack 250 Squad Battles Wins Win 250 Matches in Squad Battles on any difficulty. Jumbo Rare Players Pack 100 Squad Battles Wins Win 100 Matches in Squad Battles on any difficulty. Stadium Trophy 50 Squad Battles Wins Win 50 Matches in Squad Battles on any difficulty. Prime Gold Players Pack 25 Squad Battles Wins Win 25 Matches in Squad Battles on any difficulty. 2X 75+ Rare Gold Players Pack 10 Squad Battles Wins Win 10 Matches in Squad Battles on any difficulty. 75+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23 05:10:17</t>
+          <t>2026-06-24 04:10:52</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23 02:00:00</t>
+          <t>2026-06-24 02:00:00</t>
         </is>
       </c>
     </row>
@@ -666,22 +666,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>6/25 02:00</t>
+          <t>6/25 00:00</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25T02:00+09:00</t>
+          <t>2026-06-25T00:00+09:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; International Legends: Flash Rush International Legends: Flash Rush - EA SPORTS FC 26 Objectives Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 2 days 4 of 5 Objectives 11% 89% Rewards 3x 2x 83+ Rare Gold Players Pack 2x 3x 82+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Win 3 Win 3 Rush matches in the "International Legends" Flash Rush Event. 3X 82+ Rare Gold Players Pack Assist in 5 Assist at least 1 goal in 5 separate matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the "International Legends" Flash Rush Event while using any FOF GOTG player. 3X 82+ Rare Gold Players Pack Rush Points Earn 40,000 Rush Points. 2X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; International Legends: Flash Rush International Legends: Flash Rush - EA SPORTS FC 26 Objectives Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 22 hours 4 of 5 Objectives 12% 88% Rewards 3x 2x 83+ Rare Gold Players Pack 2x 3x 82+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Win 3 Win 3 Rush matches in the "International Legends" Flash Rush Event. 3X 82+ Rare Gold Players Pack Assist in 5 Assist at least 1 goal in 5 separate matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the "International Legends" Flash Rush Event while using any FOF GOTG player. 3X 82+ Rare Gold Players Pack Rush Points Earn 40,000 Rush Points. 2X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 4 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 80% 20% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 4 days 450 total 10 Objectives 84% 16% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 3 days 450 total 10 Objectives 83% 17% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 4 days 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 3 days 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 66% 34% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 66% 34% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 16 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 15 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 3 days 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 2 days 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 3 days 175 total 2 Objectives 96% 4% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 175 total 2 Objectives 96% 4% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 16 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 15 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 16 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 15 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 16 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 15 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 16 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 15 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 16 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 15 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1366,14 +1366,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 year</t>
+          <t>Expires in 11 months</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; eCL Finals eCL Finals - EA SPORTS FC 26 Objectives Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. eCL Finals Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. 1 Of 5 88+ Rare Gold Players Expires in 1 year 3 Objectives 67% 33% Rewards 1 Of 5 88+ Rare Gold Players 1x Premium Gold Pack 1x 2x 86+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in any Ultimate Team game mode. Premium Gold Pack eCL Finals Watch the eCL Finals Broadcast for at least 60 minutes. Broadcasts will go live May 27 at 16:30 UTC until 21:30 UTC. 2X 86+ Rare Gold Players Pack eCL Finals Watch the eCL Finals Broadcast for at least 15 minutes. Broadcasts will go live May 27 at 16:30 UTC until 21:30 UTC. 2X 85+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; eCL Finals eCL Finals - EA SPORTS FC 26 Objectives Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. eCL Finals Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. 1 Of 5 88+ Rare Gold Players Expires in 11 months 3 Objectives 67% 33% Rewards 1 Of 5 88+ Rare Gold Players 1x Premium Gold Pack 1x 2x 86+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in any Ultimate Team game mode. Premium Gold Pack eCL Finals Watch the eCL Finals Broadcast for at least 60 minutes. Broadcasts will go live May 27 at 16:30 UTC until 21:30 UTC. 2X 86+ Rare Gold Players Pack eCL Finals Watch the eCL Finals Broadcast for at least 15 minutes. Broadcasts will go live May 27 at 16:30 UTC until 21:30 UTC. 2X 85+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>6/25 02:00</t>
+          <t>6/25 00:00</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25T02:00+09:00</t>
+          <t>2026-06-25T00:00+09:00</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -2892,17 +2892,17 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>6/25 02:00</t>
+          <t>6/25 00:00</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25T02:00+09:00</t>
+          <t>2026-06-25T00:00+09:00</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>6/25 02:00</t>
+          <t>6/25 00:00</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25T02:00+09:00</t>
+          <t>2026-06-25T00:00+09:00</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>6/25 02:00</t>
+          <t>6/25 00:00</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25T02:00+09:00</t>
+          <t>2026-06-25T00:00+09:00</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -3120,17 +3120,17 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>6/25 02:00</t>
+          <t>6/25 00:00</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25T02:00+09:00</t>
+          <t>2026-06-25T00:00+09:00</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 year</t>
+          <t>Expires in 11 months</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr"/>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 year</t>
+          <t>Expires in 11 months</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 year</t>
+          <t>Expires in 11 months</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
@@ -18779,22 +18779,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 2 days 4 of 5 Objectives 11% 89%</t>
+          <t>International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 22 hours 4 of 5 Objectives 12% 88%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>6/25 02:00</t>
+          <t>6/25 00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T02:00+09:00</t>
+          <t>2026-06-25T00:00+09:00</t>
         </is>
       </c>
     </row>
@@ -18816,12 +18816,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 4 days 6 Objectives 81% 19%</t>
+          <t>Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 80% 20%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -18853,12 +18853,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 4 days 450 total 10 Objectives 84% 16%</t>
+          <t>Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 3 days 450 total 10 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -18890,12 +18890,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 4 days 350 total 10 Objectives 93% 7%</t>
+          <t>Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 3 days 350 total 10 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -18927,12 +18927,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 66% 34%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 66% 34%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -18964,12 +18964,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 95% 5%</t>
+          <t>Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -19001,12 +19001,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 16 days 3,000 total 5 Objectives 95% 5%</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 15 days 3,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -19038,12 +19038,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 3 days 2,000 total 5 Objectives 95% 5%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 2 days 2,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -19075,12 +19075,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 3 days 175 total 2 Objectives 96% 4%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 175 total 2 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -19112,12 +19112,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 16 days 2,000 total 3 Objectives 85% 15%</t>
+          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 15 days 2,000 total 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -19149,12 +19149,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 16 days 7 Objectives 84% 16%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 15 days 7 Objectives 84% 16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -19186,12 +19186,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 16 days 1 Objectives 92% 8%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 15 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -19223,12 +19223,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 16 days 5 Objectives 89% 11%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 15 days 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 16 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 15 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 16 days</t>
+          <t>Expires in 15 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -19297,12 +19297,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>eCL Finals Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. 1 Of 5 88+ Rare Gold Players Expires in 1 year 3 Objectives 67% 33%</t>
+          <t>eCL Finals Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. 1 Of 5 88+ Rare Gold Players Expires in 11 months 3 Objectives 67% 33%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 1 year</t>
+          <t>Expires in 11 months</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -20217,7 +20217,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; International Legends: Flash Rush International Legends: Flash Rush - EA SPORTS FC 26 Objectives Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 2 days 4 of 5 Objectives 11% 89% Rewards 3x 2x 83+ Rare Gold Players Pack 2x 3x 82+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Win 3 Win 3 Rush matches in the "International Legends" Flash Rush Event. 3X 82+ Rare Gold Players Pack Assist in 5 Assist at least 1 goal in 5 separate matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the "International Legends" Flash Rush Event while using any FOF GOTG player. 3X 82+ Rare Gold Players Pack Rush Points Earn 40,000 Rush Points. 2X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; International Legends: Flash Rush International Legends: Flash Rush - EA SPORTS FC 26 Objectives Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. International Legends: Flash Rush Join the "International Legends" Flash Rush Event and complete 4 of 5 challenges to earn pack rewards! All rewards are untradeable. 2X 85+ Rare Gold Players Pack Expires in 22 hours 4 of 5 Objectives 12% 88% Rewards 3x 2x 83+ Rare Gold Players Pack 2x 3x 82+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Win 3 Win 3 Rush matches in the "International Legends" Flash Rush Event. 3X 82+ Rare Gold Players Pack Assist in 5 Assist at least 1 goal in 5 separate matches in the "International Legends" Flash Rush Event. 2X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the "International Legends" Flash Rush Event while using any FOF GOTG player. 3X 82+ Rare Gold Players Pack Rush Points Earn 40,000 Rush Points. 2X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 4 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 80% 20% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 4 days 450 total 10 Objectives 84% 16% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 3 days 450 total 10 Objectives 83% 17% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20283,7 +20283,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 4 days 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 3 days 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 66% 34% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 66% 34% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20327,7 +20327,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 16 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 15 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20371,7 +20371,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 3 days 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 2 days 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 3 days 175 total 2 Objectives 96% 4% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 175 total 2 Objectives 96% 4% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20415,7 +20415,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 16 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 15 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20437,7 +20437,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 16 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 15 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20459,7 +20459,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 16 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 15 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20481,7 +20481,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 16 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 15 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20503,7 +20503,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 16 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 15 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; eCL Finals eCL Finals - EA SPORTS FC 26 Objectives Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. eCL Finals Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. 1 Of 5 88+ Rare Gold Players Expires in 1 year 3 Objectives 67% 33% Rewards 1 Of 5 88+ Rare Gold Players 1x Premium Gold Pack 1x 2x 86+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in any Ultimate Team game mode. Premium Gold Pack eCL Finals Watch the eCL Finals Broadcast for at least 60 minutes. Broadcasts will go live May 27 at 16:30 UTC until 21:30 UTC. 2X 86+ Rare Gold Players Pack eCL Finals Watch the eCL Finals Broadcast for at least 15 minutes. Broadcasts will go live May 27 at 16:30 UTC until 21:30 UTC. 2X 85+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; eCL Finals eCL Finals - EA SPORTS FC 26 Objectives Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. eCL Finals Join in on the action of the eChampions League Broadcast at Twitch/EASPORTSFC to earn your viewership rewards! All rewards are untradeable. 1 Of 5 88+ Rare Gold Players Expires in 11 months 3 Objectives 67% 33% Rewards 1 Of 5 88+ Rare Gold Players 1x Premium Gold Pack 1x 2x 86+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack Play 5 Play 5 matches in any Ultimate Team game mode. Premium Gold Pack eCL Finals Watch the eCL Finals Broadcast for at least 60 minutes. Broadcasts will go live May 27 at 16:30 UTC until 21:30 UTC. 2X 86+ Rare Gold Players Pack eCL Finals Watch the eCL Finals Broadcast for at least 15 minutes. Broadcasts will go live May 27 at 16:30 UTC until 21:30 UTC. 2X 85+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25 03:51:33</t>
+          <t>2026-06-26 04:06:11</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25 02:00:00</t>
+          <t>2026-06-26 02:00:00</t>
         </is>
       </c>
     </row>
@@ -651,37 +651,37 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 2 days 6 Objectives 80% 20% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 7 days 5 Objectives 38% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -701,37 +701,37 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 2 days 450 total 10 Objectives 83% 17% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! NEW Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 7 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -751,37 +751,37 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 2 days 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! NEW Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 7 days 3,000 total 5 Objectives 79% 21% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -801,37 +801,37 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 67% 33% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 7 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -851,17 +851,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 22 hours 6 Objectives 78% 22% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -901,37 +901,37 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 15 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 22 hours 450 total 10 Objectives 83% 18% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -951,17 +951,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/953-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -971,17 +971,17 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 22 hours 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 22 hours 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/949-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 22 hours 175 total 2 Objectives 97% 3% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 13 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1066,22 +1066,22 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 15 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 13 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1116,22 +1116,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 15 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 13 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 15 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 13 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1216,22 +1216,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 15 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 13 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 15 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 13 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2720,22 +2720,22 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches in the Journey of Nations Africa Live Event.</t>
+          <t>Complete Rush Bonuses alongside your teammates to earn Rush Points!</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>3x 3x 83+ Rare Gold Players Pack / 1x 3x 84+ Rare Gold Players Pack / 3X 83+ Rare Gold Players Pack</t>
+          <t>2X 89+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Journey of Nations Africa Live Event</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
@@ -2751,37 +2751,37 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||play 2 matches in the journey of nations africa live event.||play 2</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||complete rush bonuses alongside your teammates to earn rush points!||weekly rush points - ea sports fc 26 objectives</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -2796,22 +2796,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Win 1</t>
+          <t>2,500 Rush Points</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Win 1 match in the Journey of Nations Africa Live Event.</t>
+          <t>Earn 2,500 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
+          <t>1x 2x 85+ Rare Gold Players Pack / 1x 88+ Rare Gold Player Pack / 1x 2x 89+ Rare Gold Players Pack / 4X 83+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Journey of Nations Africa Live Event</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
@@ -2827,37 +2827,37 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||win 1 match in the journey of nations africa live event.||win 1</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 2,500 points by completing bonuses in rush.||2,500 rush points</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -2872,22 +2872,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Play 4</t>
+          <t>10,000 Rush Points</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Play 4 matches in the Journey of Nations Africa Live Event.</t>
+          <t>Earn 10,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
+          <t>4X 83+ Rare Gold Players Pack / 3X 84+ Rare Gold Players Pack / 4X 84+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Journey of Nations Africa Live Event</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr"/>
@@ -2903,37 +2903,37 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||play 4 matches in the journey of nations africa live event.||play 4</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 10,000 points by completing bonuses in rush.||10,000 rush points</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -2948,22 +2948,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>25,000 Rush Points</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Win 2 matches in the Journey of Nations Africa Live Event.</t>
+          <t>Earn 25,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
+          <t>3X 84+ Rare Gold Players Pack / 4X 84+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Journey of Nations Africa Live Event</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr"/>
@@ -2979,37 +2979,37 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||win 2 matches in the journey of nations africa live event.||win 2</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 25,000 points by completing bonuses in rush.||25,000 rush points</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -3024,22 +3024,22 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Score 5</t>
+          <t>35,000 Rush Points</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals in the Journey of Nations Africa Live Event.</t>
+          <t>Earn 35,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
+          <t>4X 84+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack / 88+ Rare Gold Player Pack</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Journey of Nations Africa Live Event</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -3055,37 +3055,37 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||score 5 goals in the journey of nations africa live event.||score 5</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 35,000 points by completing bonuses in rush.||35,000 rush points</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>45,000 Rush Points</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Win 3 matches in the Journey of Nations Africa Live Event.</t>
+          <t>Earn 45,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
+          <t>2X 85+ Rare Gold Players Pack / 88+ Rare Gold Player Pack</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Journey of Nations Africa Live Event</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
@@ -3131,37 +3131,37 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||win 3 matches in the journey of nations africa live event.||win 3</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 45,000 points by completing bonuses in rush.||45,000 rush points</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -3176,20 +3176,24 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>3 of 5 Objectives</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in the Festival of Football: Home Colours League.</t>
+          <t>Play 5 Squad Battles</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1x 3x 84+ Rare Gold Players Pack / 1x 2x 85+ Rare Gold Players Pack / 1x 94+ FOF GOTG Guarantee Pack / 100 SP</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>2,000 SP / 250 SP</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -3203,37 +3207,37 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||play 5 matches in the festival of football: home colours league.||play 5</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 squad battles||3 of 5 objectives</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -3248,21 +3252,29 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>3 of 5 Objectives</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Play 10 matches in the Festival of Football: Home Colours League.</t>
+          <t>Play 5 Squad Battles matches on Min. Semi-Pro difficulty.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>100 SP / 5X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+          <t>2,000 SP / 250 SP</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -3275,37 +3287,37 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||play 10 matches in the festival of football: home colours league.||play 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 squad battles matches on min. semi-pro difficulty.||3 of 5 objectives</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -3320,20 +3332,24 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>Play 5 Rivals</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Win 3 matches in the Festival of Football: Home Colours League.</t>
+          <t>Play 5 Rivals</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100 SP / 3X 84+ Rare Gold Players Pack / Evo Unlock</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
+          <t>2,000 SP / 250 SP</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -3347,37 +3363,37 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||win 3 matches in the festival of football: home colours league.||win 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 rivals||play 5 rivals</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -3392,20 +3408,24 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Win 5</t>
+          <t>Play 5 matches in Rivals.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed.</t>
+          <t>Play 5 matches in Rivals.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>100 SP / 3X 84+ Rare Gold Players Pack / Evo Unlock</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -3419,37 +3439,37 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||win 5 matches in the festival of football: home colours league to earn an evo consumable. all evo details can be previewed.||win 5</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 matches in rivals.||play 5 matches in rivals.</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -3464,20 +3484,24 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Win 12</t>
+          <t>Play 5 Champions</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed.</t>
+          <t>Play 5 Champions</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / 150 SP</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -3491,37 +3515,37 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||win 12 matches in the festival of football: home colours league to earn an evo consumable. all evo details can be previewed.||win 12</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 champions||play 5 champions</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -3536,20 +3560,24 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Score 3 in 1</t>
+          <t>Play 5 matches in Champions.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Score at least 3 goals in one match in the Festival of Football: Home Colours League.</t>
+          <t>Play 5 matches in Champions.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / 150 SP</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -3563,37 +3591,37 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||score at least 3 goals in one match in the festival of football: home colours league.||score 3 in 1</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 matches in champions.||play 5 matches in champions.</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -3608,20 +3636,24 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Score in 4</t>
+          <t>Play 5 Rush</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Score a goal in 4 separate matches in the Festival of Football: Home Colours League.</t>
+          <t>Play 5 Rush</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>150 SP / 2X 85+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -3635,37 +3667,37 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||score a goal in 4 separate matches in the festival of football: home colours league.||score in 4</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 rush||play 5 rush</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -3680,20 +3712,24 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Score in 6</t>
+          <t>Play 5 Ultimate Team Rush matches.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Score a goal in 6 separate matches in the Festival of Football: Home Colours League.</t>
+          <t>Play 5 Ultimate Team Rush matches.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2X 85+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -3707,37 +3743,37 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||score a goal in 6 separate matches in the festival of football: home colours league.||score in 6</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 ultimate team rush matches.||play 5 ultimate team rush matches.</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -3752,20 +3788,24 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Score in 12</t>
+          <t>Play 5 Live Events</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Score a goal in 12 separate matches in the Festival of Football: Home Colours League.</t>
+          <t>Play 5 Live Events</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>2X 85+ Rare Gold Players Pack / Evo Unlock</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Live Events</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -3779,37 +3819,37 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||score a goal in 12 separate matches in the festival of football: home colours league.||score in 12</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 live events||play 5 live events</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -3824,20 +3864,24 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Win 2 [4-4-2 (2)]</t>
+          <t>Play 5 matches in any Ultimate Team Live Event.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League.</t>
+          <t>Play 5 matches in any Ultimate Team Live Event.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Any Ultimate Team mode</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -3851,37 +3895,37 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||win 2 matches using only the 4-4-2 (2) formation (without changing) in the festival of football: home colours league.||win 2 [4-4-2 (2)]</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 matches in any ultimate team live event.||play 5 matches in any ultimate team live event.</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -3896,21 +3940,29 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Icons Take the Field</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11.</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr"/>
+          <t>Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events).</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Buy 10 Player Items on the Transfer Market. / 450 SP</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Any Ultimate Team mode</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr"/>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -3923,37 +3975,37 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||play 5 matches in any ultimate team game mode while having min. 1 icon player in your starting 11.||icons take the field</t>
+          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/||play 10 matches in squad battles on min. semi-pro difficulty (or rush/rivals/champions/live events).||play 10</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -3968,25 +4020,29 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Heroic Victories</t>
+          <t>Win 10</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11.</t>
+          <t>Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events).</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Paolo Maldini (Loan)</t>
+          <t>450 SP</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Any Ultimate Team mode</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr"/>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -3999,37 +4055,37 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||win 5 matches in any ultimate team game mode while having min. 1 hero player in your starting 11.||heroic victories</t>
+          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rush/rivals/champions/live events).||win 10</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -4044,17 +4100,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>The Art of Defending</t>
+          <t>Score 10</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11.</t>
+          <t>Score 10 goals in any Ultimate Team game mode using a player from Mexico.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Paolo Maldini (Loan) / Zico (Loan)</t>
+          <t>450 SP</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -4075,37 +4131,37 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||keep 4 clean sheets in any ultimate team game mode while having min. 1 italian defender in your starting 11.||the art of defending</t>
+          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/||score 10 goals in any ultimate team game mode using a player from mexico.||score 10</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -4116,21 +4172,21 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Samba Long Shots</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11.</t>
+          <t>Play 1 match in any Ultimate Team game mode and earn SP!</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Paolo Maldini (Loan) / Zico (Loan)</t>
+          <t>225 SP / 75 SP</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -4146,42 +4202,42 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 5 goals from outside the box in any ultimate team game mode while having min. 1 brazilian player in your starting 11.||samba long shots</t>
+          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/||play 1 match in any ultimate team game mode and earn sp!||play 1</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -4192,28 +4248,24 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Architect of Attack</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11.</t>
+          <t>Score 2 goals</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Zico (Loan) / Iniesta (Loan) / Miroslav Klose (Loan)</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Any Ultimate Team mode</t>
-        </is>
-      </c>
+          <t>225 SP / 75 SP</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -4222,42 +4274,42 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||assist 6 goals using through ball passes in any ultimate team game mode while having min. 1 spanish player in your starting 11.||architect of attack</t>
+          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/||score 2 goals||play 1</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -4268,21 +4320,21 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Above the Rest</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11.</t>
+          <t>Score 2 goals in any Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Iniesta (Loan) / Miroslav Klose (Loan)</t>
+          <t>75 SP</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -4298,42 +4350,42 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 3 goals with a header in any ultimate team game mode while having min. 1 german player in your starting 11.||above the rest</t>
+          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/||score 2 goals in any ultimate team game mode.||play 1</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -4344,26 +4396,26 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Cross &amp; Crown</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11.</t>
+          <t>Play 2 matches in the Journey of Nations Africa Live Event.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Miroslav Klose (Loan) / Bobby Charlton (Loan) / Custom Kit</t>
+          <t>3x 3x 83+ Rare Gold Players Pack / 1x 3x 84+ Rare Gold Players Pack / 3X 83+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Any Ultimate Team mode</t>
+          <t>Live Events / Journey of Nations Africa Live Event</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
@@ -4374,42 +4426,42 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||assist 4 goals using crosses in any ultimate team game mode while having min. 1 english player in your starting 11.||cross &amp; crown</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||play 2 matches in the journey of nations africa live event.||play 2</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -4420,26 +4472,26 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Full Throttle Finisher</t>
+          <t>Win 1</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals with a Power Shot in any Ultimate Team game mode.</t>
+          <t>Win 1 match in the Journey of Nations Africa Live Event.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Bobby Charlton (Loan) / Custom Kit</t>
+          <t>3X 83+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Any Ultimate Team mode</t>
+          <t>Live Events / Journey of Nations Africa Live Event</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
@@ -4450,42 +4502,42 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 5 goals with a power shot in any ultimate team game mode.||full throttle finisher</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||win 1 match in the journey of nations africa live event.||win 1</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -4496,22 +4548,26 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Precision Perfection</t>
+          <t>Play 4</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals with a Finesse Shot in any Ultimate Team game mode.</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr"/>
+          <t>Play 4 matches in the Journey of Nations Africa Live Event.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>3X 83+ Rare Gold Players Pack</t>
+        </is>
+      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Any Ultimate Team mode</t>
+          <t>Live Events / Journey of Nations Africa Live Event</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr"/>
@@ -4522,42 +4578,42 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 5 goals with a finesse shot in any ultimate team game mode.||precision perfection</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||play 4 matches in the journey of nations africa live event.||play 4</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -4568,22 +4624,26 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>From Distance</t>
+          <t>Win 2</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals from outside the box in any Ultimate Team game mode.</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr"/>
+          <t>Win 2 matches in the Journey of Nations Africa Live Event.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>3X 83+ Rare Gold Players Pack</t>
+        </is>
+      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Any Ultimate Team mode</t>
+          <t>Live Events / Journey of Nations Africa Live Event</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr"/>
@@ -4594,42 +4654,42 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 5 goals from outside the box in any ultimate team game mode.||from distance</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||win 2 matches in the journey of nations africa live event.||win 2</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -4640,26 +4700,26 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Score 5</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Complete Rush Bonuses alongside your teammates to earn Rush Points!</t>
+          <t>Score 5 goals in the Journey of Nations Africa Live Event.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2X 89+ Rare Gold Players Pack</t>
+          <t>3X 83+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Live Events / Journey of Nations Africa Live Event</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr"/>
@@ -4670,22 +4730,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4695,17 +4755,17 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/||complete rush bonuses alongside your teammates to earn rush points!||weekly rush points - ea sports fc 26 objectives</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||score 5 goals in the journey of nations africa live event.||score 5</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -4716,26 +4776,26 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>45,000 Rush Points</t>
+          <t>Win 3</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Earn 45,000 points by completing bonuses in Rush.</t>
+          <t>Win 3 matches in the Journey of Nations Africa Live Event.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1x 3x 84+ Rare Gold Players Pack / 1x 4x 83+ Rare Gold Players Pack / 1x 2x 89+ Rare Gold Players Pack / 88+ Rare Gold Player Pack</t>
+          <t>3X 83+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Live Events / Journey of Nations Africa Live Event</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr"/>
@@ -4746,22 +4806,22 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G005</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -4771,17 +4831,17 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/||earn 45,000 points by completing bonuses in rush.||45,000 rush points</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/||win 3 matches in the journey of nations africa live event.||win 3</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4792,28 +4852,24 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>35,000 Rush Points</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Earn 35,000 points by completing bonuses in Rush.</t>
+          <t>Play 5 matches in the Festival of Football: Home Colours League.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>88+ Rare Gold Player Pack / 2X 85+ Rare Gold Players Pack / 4X 84+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1x 3x 84+ Rare Gold Players Pack / 1x 2x 85+ Rare Gold Players Pack / 1x 94+ FOF GOTG Guarantee Pack / 100 SP</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -4822,22 +4878,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4847,17 +4903,17 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/||earn 35,000 points by completing bonuses in rush.||35,000 rush points</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||play 5 matches in the festival of football: home colours league.||play 5</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4868,28 +4924,24 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>25,000 Rush Points</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Earn 25,000 points by completing bonuses in Rush.</t>
+          <t>Play 10 matches in the Festival of Football: Home Colours League.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2X 85+ Rare Gold Players Pack / 4X 84+ Rare Gold Players Pack / 3X 84+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>100 SP / 5X 83+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -4898,22 +4950,22 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4923,17 +4975,17 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/||earn 25,000 points by completing bonuses in rush.||25,000 rush points</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||play 10 matches in the festival of football: home colours league.||play 10</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4944,28 +4996,24 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>10,000 Rush Points</t>
+          <t>Win 3</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Earn 10,000 points by completing bonuses in Rush.</t>
+          <t>Win 3 matches in the Festival of Football: Home Colours League.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>4X 84+ Rare Gold Players Pack / 3X 84+ Rare Gold Players Pack / 4X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>100 SP / 3X 84+ Rare Gold Players Pack / Evo Unlock</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -4974,22 +5022,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4999,17 +5047,17 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/||earn 10,000 points by completing bonuses in rush.||10,000 rush points</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||win 3 matches in the festival of football: home colours league.||win 3</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -5020,28 +5068,24 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2,500 Rush Points</t>
+          <t>Win 5</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Earn 2,500 points by completing bonuses in Rush.</t>
+          <t>Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3X 84+ Rare Gold Players Pack / 4X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>100 SP / 3X 84+ Rare Gold Players Pack / Evo Unlock</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -5050,22 +5094,22 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -5075,17 +5119,17 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/||earn 2,500 points by completing bonuses in rush.||2,500 rush points</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||win 5 matches in the festival of football: home colours league to earn an evo consumable. all evo details can be previewed.||win 5</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -5096,28 +5140,24 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>3 of 5 Objectives</t>
+          <t>Win 12</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Live Events</t>
+          <t>Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>2,000 SP / 250 SP</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>Evo Unlock / 150 SP</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -5126,22 +5166,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -5151,17 +5191,17 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 live events||3 of 5 objectives</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||win 12 matches in the festival of football: home colours league to earn an evo consumable. all evo details can be previewed.||win 12</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -5172,28 +5212,24 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>3 of 5 Objectives</t>
+          <t>Score 3 in 1</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in any Ultimate Team Live Event.</t>
+          <t>Score at least 3 goals in one match in the Festival of Football: Home Colours League.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2,000 SP / 250 SP</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Any Ultimate Team mode</t>
-        </is>
-      </c>
+          <t>Evo Unlock / 150 SP</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -5202,22 +5238,22 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -5227,17 +5263,17 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 matches in any ultimate team live event.||3 of 5 objectives</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||score at least 3 goals in one match in the festival of football: home colours league.||score 3 in 1</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -5248,28 +5284,24 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rush</t>
+          <t>Score in 4</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rush</t>
+          <t>Score a goal in 4 separate matches in the Festival of Football: Home Colours League.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>2,000 SP / 250 SP</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>150 SP / 2X 85+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -5278,22 +5310,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -5303,17 +5335,17 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 rush||play 5 rush</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||score a goal in 4 separate matches in the festival of football: home colours league.||score in 4</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -5324,28 +5356,24 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Ultimate Team Rush matches.</t>
+          <t>Score in 6</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Ultimate Team Rush matches.</t>
+          <t>Score a goal in 6 separate matches in the Festival of Football: Home Colours League.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>2X 85+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -5354,22 +5382,22 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -5379,17 +5407,17 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 ultimate team rush matches.||play 5 ultimate team rush matches.</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||score a goal in 6 separate matches in the festival of football: home colours league.||score in 6</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -5400,28 +5428,24 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Champions</t>
+          <t>Score in 12</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Champions</t>
+          <t>Score a goal in 12 separate matches in the Festival of Football: Home Colours League.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Champions</t>
-        </is>
-      </c>
+          <t>2X 85+ Rare Gold Players Pack / Evo Unlock</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -5430,22 +5454,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5455,17 +5479,17 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 champions||play 5 champions</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||score a goal in 12 separate matches in the festival of football: home colours league.||score in 12</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -5476,28 +5500,24 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in Champions.</t>
+          <t>Win 2 [4-4-2 (2)]</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in Champions.</t>
+          <t>Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Champions</t>
-        </is>
-      </c>
+          <t>Evo Unlock</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -5506,22 +5526,22 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -5531,17 +5551,17 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 matches in champions.||play 5 matches in champions.</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/||win 2 matches using only the 4-4-2 (2) formation (without changing) in the festival of football: home colours league.||win 2 [4-4-2 (2)]</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5552,26 +5572,22 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rivals</t>
+          <t>Icons Take the Field</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rivals</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>250 SP</t>
-        </is>
-      </c>
+          <t>Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11.</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Rivals</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr"/>
@@ -5582,22 +5598,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -5607,17 +5623,17 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 rivals||play 5 rivals</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||play 5 matches in any ultimate team game mode while having min. 1 icon player in your starting 11.||icons take the field</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -5628,26 +5644,26 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in Rivals.</t>
+          <t>Heroic Victories</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in Rivals.</t>
+          <t>Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
+          <t>Paolo Maldini (Loan)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Rivals</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
@@ -5658,22 +5674,22 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -5683,17 +5699,17 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 matches in rivals.||play 5 matches in rivals.</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||win 5 matches in any ultimate team game mode while having min. 1 hero player in your starting 11.||heroic victories</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5704,26 +5720,26 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles</t>
+          <t>The Art of Defending</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles</t>
+          <t>Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
+          <t>Paolo Maldini (Loan) / Zico (Loan)</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr"/>
@@ -5734,22 +5750,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -5759,17 +5775,17 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 squad battles||play 5 squad battles</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||keep 4 clean sheets in any ultimate team game mode while having min. 1 italian defender in your starting 11.||the art of defending</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5780,33 +5796,29 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles matches on Min. Semi-Pro difficulty.</t>
+          <t>Samba Long Shots</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles matches on Min. Semi-Pro difficulty.</t>
+          <t>Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
+          <t>Paolo Maldini (Loan) / Zico (Loan)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>Any Ultimate Team mode</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -5814,22 +5826,22 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -5839,17 +5851,17 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/||play 5 squad battles matches on min. semi-pro difficulty.||play 5 squad battles matches on min. semi-pro difficulty.</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 5 goals from outside the box in any ultimate team game mode while having min. 1 brazilian player in your starting 11.||samba long shots</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -5860,26 +5872,26 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Play 25</t>
+          <t>Architect of Attack</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
+          <t>Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3,000 SP / 350 SP</t>
+          <t>Zico (Loan) / Iniesta (Loan) / Miroslav Klose (Loan)</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr"/>
@@ -5890,42 +5902,42 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 25 matches in squad battles, rush, rivals, champions or live events.||play 25</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||assist 6 goals using through ball passes in any ultimate team game mode while having min. 1 spanish player in your starting 11.||architect of attack</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5936,26 +5948,26 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Play 20</t>
+          <t>Above the Rest</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
+          <t>Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>350 SP</t>
+          <t>Iniesta (Loan) / Miroslav Klose (Loan)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
@@ -5966,42 +5978,42 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 20 matches in squad battles, rush, rivals, champions or live events.||play 20</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 3 goals with a header in any ultimate team game mode while having min. 1 german player in your starting 11.||above the rest</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6012,26 +6024,26 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Play 15</t>
+          <t>Cross &amp; Crown</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
+          <t>Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>350 SP</t>
+          <t>Miroslav Klose (Loan) / Bobby Charlton (Loan) / Custom Kit</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr"/>
@@ -6042,42 +6054,42 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 15 matches in squad battles, rush, rivals, champions or live events.||play 15</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||assist 4 goals using crosses in any ultimate team game mode while having min. 1 english player in your starting 11.||cross &amp; crown</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -6088,26 +6100,26 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Full Throttle Finisher</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
+          <t>Score 5 goals with a Power Shot in any Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>350 SP</t>
+          <t>Bobby Charlton (Loan) / Custom Kit</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr"/>
@@ -6118,42 +6130,42 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 10 matches in squad battles, rush, rivals, champions or live events.||play 10</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 5 goals with a power shot in any ultimate team game mode.||full throttle finisher</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -6164,26 +6176,22 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Play 5</t>
+          <t>Precision Perfection</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>350 SP</t>
-        </is>
-      </c>
+          <t>Score 5 goals with a Finesse Shot in any Ultimate Team game mode.</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr"/>
@@ -6194,42 +6202,42 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 5 matches in squad battles, rush, rivals, champions or live events.||play 5</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 5 goals with a finesse shot in any ultimate team game mode.||precision perfection</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -6240,23 +6248,19 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Score 10</t>
+          <t>From Distance</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Score 10 goals in any Ultimate Team game mode using a player from the United States.</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>2,000 SP / 300 SP</t>
-        </is>
-      </c>
+          <t>Score 5 goals from outside the box in any Ultimate Team game mode.</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
       <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Any Ultimate Team mode</t>
@@ -6275,17 +6279,17 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/953-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -6295,17 +6299,17 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/953-weekly-objectives/||score 10 goals in any ultimate team game mode using a player from the united states.||score 10</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/||score 5 goals from outside the box in any ultimate team game mode.||from distance</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -6316,21 +6320,21 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Play 25</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events).</t>
+          <t>Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>300 SP / Buy 10 Player Items on the Transfer Market.</t>
+          <t>3,000 SP / 350 SP</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -6338,11 +6342,7 @@
           <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+      <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -6365,27 +6365,27 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/953-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/953-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rush/rivals/champions/live events).||win 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 25 matches in squad battles, rush, rivals, champions or live events.||play 25</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -6396,21 +6396,21 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Play 20</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events).</t>
+          <t>Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>300 SP / Buy 10 Player Items on the Transfer Market. / List 10 Player Items on the Transfer Market.</t>
+          <t>350 SP</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -6418,11 +6418,7 @@
           <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+      <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -6430,12 +6426,12 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -6445,27 +6441,27 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/953-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/953-weekly-objectives/||play 10 matches in squad battles on min. semi-pro difficulty (or rush/rivals/champions/live events).||play 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 20 matches in squad battles, rush, rivals, champions or live events.||play 20</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -6476,24 +6472,28 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>2 Objectives</t>
+          <t>Play 15</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Score 2 goals</t>
+          <t>Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>175 SP / 50 SP</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
+          <t>350 SP</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -6517,27 +6517,27 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/949-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/949-daily-objectives/||score 2 goals||2 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 15 matches in squad battles, rush, rivals, champions or live events.||play 15</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -6548,26 +6548,26 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>2 Objectives</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Score 2 goals in any Ultimate Team game mode.</t>
+          <t>Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>175 SP / 50 SP</t>
+          <t>350 SP</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Any Ultimate Team mode</t>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -6593,27 +6593,27 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/949-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/949-daily-objectives/||score 2 goals in any ultimate team game mode.||2 objectives</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 10 matches in squad battles, rush, rivals, champions or live events.||play 10</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -6624,26 +6624,26 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Play 5</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in any Ultimate Team game mode and earn SP!</t>
+          <t>Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>50 SP</t>
+          <t>350 SP</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Any Ultimate Team mode</t>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr"/>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -6669,27 +6669,27 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/949-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/949-daily-objectives/||play 1 match in any ultimate team game mode and earn sp!||play 1</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/||play 5 matches in squad battles, rush, rivals, champions or live events.||play 5</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -6826,17 +6826,17 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -6902,17 +6902,17 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
@@ -6978,17 +6978,17 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7130,17 +7130,17 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -7206,17 +7206,17 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -7282,17 +7282,17 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -7434,17 +7434,17 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -7506,17 +7506,17 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -7578,17 +7578,17 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -7650,17 +7650,17 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -7722,17 +7722,17 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -7794,17 +7794,17 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -7866,17 +7866,17 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -7938,17 +7938,17 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -8154,17 +8154,17 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -8226,17 +8226,17 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -18334,170 +18334,170 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack</t>
+          <t>NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 2 days 6 Objectives 80% 20%</t>
+          <t>NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 7 days 5 Objectives 38% 63%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack</t>
+          <t>NEW Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 2 days 450 total 10 Objectives 83% 17%</t>
+          <t>NEW Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 7 days 2,000 total 3 of 5 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP</t>
+          <t>NEW Weekly Objectives Complete weekly Objectives to earn SP! 750 SP</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 2 days 350 total 10 Objectives 93% 7%</t>
+          <t>NEW Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 7 days 3,000 total 5 Objectives 79% 21%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6/27 02:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27T02:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens</t>
+          <t>NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 67% 33%</t>
+          <t>NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 7 days 225 total 2 Objectives 79% 21%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>7/3 02:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-07-03T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP</t>
+          <t>Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 95% 5%</t>
+          <t>Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 22 hours 6 Objectives 78% 22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -18507,71 +18507,71 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP</t>
+          <t>Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 15 days 3,000 total 5 Objectives 95% 5%</t>
+          <t>Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 22 hours 450 total 10 Objectives 83% 18%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/953-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP</t>
+          <t>Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 22 hours 2,000 total 5 Objectives 95% 5%</t>
+          <t>Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 22 hours 350 total 10 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -18581,19 +18581,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>6/27 00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-06-27T00:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/949-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -18603,27 +18603,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 22 hours 175 total 2 Objectives 97% 3%</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 13 days 3,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6/26 00:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T00:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -18645,22 +18645,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 15 days 2,000 total 3 Objectives 85% 15%</t>
+          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 13 days 2,000 total 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -18682,22 +18682,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 15 days 7 Objectives 84% 16%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 13 days 7 Objectives 84% 16%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -18719,22 +18719,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 15 days 1 Objectives 92% 8%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 13 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -18756,22 +18756,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 15 days 5 Objectives 89% 11%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 13 days 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -18793,22 +18793,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 15 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 13 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 15 days</t>
+          <t>Expires in 13 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7/10 02:00</t>
+          <t>7/9 02:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T02:00+09:00</t>
+          <t>2026-07-09T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -19740,17 +19740,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
+          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 2 days 6 Objectives 80% 20% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 7 days 5 Objectives 38% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19762,17 +19762,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
+          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 2 days 450 total 10 Objectives 83% 17% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! NEW Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 7 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19784,17 +19784,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
+          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 2 days 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! NEW Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 7 days 3,000 total 5 Objectives 79% 21% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19806,17 +19806,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/967-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 67% 33% Rewards 100 Tokens 1x 88+ Rare Gold Player Pack 1x 2x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 2x 89+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 7 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19828,17 +19828,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations Africa - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/973-season-8-weekly-play-3/</t>
+          <t>https://www.fut.gg/objectives/live-events/1028-journey-of-nations-africa/</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 3 Season 8 Weekly Play 3 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 3 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 95% 5% Rewards 2,000 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Africa Journey of Nations Africa - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. Journey of Nations Africa Compete in the Journey of Nations Africa Live Event to earn exclusive rewards! All rewards are untradeable. 3X 84+ Rare Gold Players Pack Expires in 22 hours 6 Objectives 78% 22% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Africa Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Africa Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Africa Live Event. Award Win 3 Win 3 matches in the Journey of Nations Africa Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19850,17 +19850,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
+          <t>https://www.fut.gg/objectives/live-events/1029-festival-of-football-home-colours-league/</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 15 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football: Home Colours League Festival of Football: Home Colours League - EA SPORTS FC 26 Objectives Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. Festival of Football: Home Colours League Compete in the Festival of Football: Home Colours League to earn Festival of Football Tokens, Packs, SP and Evolutions. All rewards are Untradeable. 94+ Fof Gotg Guarantee Pack Expires in 22 hours 450 total 10 Objectives 83% 18% Rewards 450 SP 15 Tokens 25 Tokens 15 Tokens Evo Unlock Evo Unlock 15 Tokens 20 Tokens 20 Tokens 40 Tokens Evo Unlock 1x 5x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 94+ FOF GOTG Guarantee Pack Play 5 Play 5 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 5X 83+ Rare Gold Players Pack Play 10 Play 10 matches in the Festival of Football: Home Colours League. 25 Tokens 100 SP Win 3 Win 3 matches in the Festival of Football: Home Colours League. 15 Tokens 100 SP 3X 84+ Rare Gold Players Pack Win 5 Win 5 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Win 12 Win 12 matches in the Festival of Football: Home Colours League to earn an EVO consumable. All EVO details can be previewed. Evo Unlock Score 3 in 1 Score at least 3 goals in one match in the Festival of Football: Home Colours League. 15 Tokens 150 SP Score in 4 Score a goal in 4 separate matches in the Festival of Football: Home Colours League. 20 Tokens Score in 6 Score a goal in 6 separate matches in the Festival of Football: Home Colours League. 20 Tokens 2X 85+ Rare Gold Players Pack Score in 12 Score a goal in 12 separate matches in the Festival of Football: Home Colours League. 40 Tokens Win 2 [4-4-2 (2)] Win 2 matches using only the 4-4-2 (2) formation (without changing) in the Festival of Football: Home Colours League. Evo Unlock © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19872,17 +19872,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/953-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1030-greats-of-the-game-football-royalty/</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 500 SP Expires in 22 hours 2,000 total 5 Objectives 95% 5% Rewards 2,000 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from the United States. 300 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 300 SP Buy 10 Buy 10 Player Items on the Transfer Market. 300 SP List 10 List 10 Player Items on the Transfer Market. 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Greats of the Game: Football Royalty Greats of the Game: Football Royalty - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. Greats of the Game: Football Royalty Complete all the challenges to earn Festival of Football Tokens, Loan Greats of the Game Items, and more! All rewards are Untradeable. 50 Tokens 350 SP Expires in 22 hours 350 total 10 Objectives 93% 7% Rewards 20 20 20 20 20 350 SP 10 Tokens 20 Tokens Brazil Brazil Germany Germany Custom Kit England 20 Tokens 50 Tokens Icons Take the Field Play 5 matches in any Ultimate Team game mode while having Min. 1 Icon player in your starting 11. 10 Tokens Heroic Victories Win 5 matches in any Ultimate Team game mode while having Min. 1 Hero Player in your starting 11. 20 Tokens The Art of Defending Keep 4 Clean Sheets in any Ultimate Team game mode while having Min. 1 Italian defender in your starting 11. 20 Paolo Maldini (Loan) Samba Long Shots Score 5 goals from outside the box in any Ultimate Team game mode while having Min. 1 Brazilian player in your starting 11. 20 Zico (Loan) Brazil Brazil Architect of Attack Assist 6 goals using Through Ball passes in any Ultimate Team game mode while having Min. 1 Spanish player in your starting 11. 20 Iniesta (Loan) Above the Rest Score 3 goals with a Header in any Ultimate Team game mode while having Min. 1 German player in your starting 11. 20 Miroslav Klose (Loan) Germany Germany Cross &amp; Crown Assist 4 goals using Crosses in any Ultimate Team game mode while having Min. 1 English player in your starting 11. 20 Bobby Charlton (Loan) Custom Kit England Full Throttle Finisher Score 5 goals with a Power Shot in any Ultimate Team game mode. Simon Banza Precision Perfection Score 5 goals with a Finesse Shot in any Ultimate Team game mode. Brandon Thomas-Asante From Distance Score 5 goals from outside the box in any Ultimate Team game mode. 20 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19894,17 +19894,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Seasonal Objective - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/949-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/seasonal/965-seasonal-objective/</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 22 hours 175 total 2 Objectives 97% 3% Rewards 175 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 50 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 50 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 13 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 15 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 13 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19948,7 +19948,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 15 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 13 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 15 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 13 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 15 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 13 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20014,7 +20014,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 15 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 13 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 03:31:22</t>
+          <t>2026-06-28 03:01:37</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27 02:00:00</t>
+          <t>2026-06-28 02:00:00</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 7 days 9 Objectives 93% 7% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 6 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 7 days 6 Objectives 84% 16% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 83% 17% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 7 days 2,000 total 4 Objectives 91% 9% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 6 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 27 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 26 days 15 Objectives 39% 61% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 6 days 5 Objectives 36% 64% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 36% 64% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 6 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 6 days 3,000 total 5 Objectives 76% 24% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 5 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 6 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 5 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 13 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 12 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 13 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 12 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 13 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 12 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 13 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 12 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 13 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 12 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 13 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 12 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -19309,7 +19309,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12%</t>
+          <t>NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -19334,12 +19334,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 7 days 9 Objectives 93% 7%</t>
+          <t>NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 6 days 9 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -19371,12 +19371,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 7 days 6 Objectives 84% 16%</t>
+          <t>NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -19408,12 +19408,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 7 days 2,000 total 4 Objectives 91% 9%</t>
+          <t>NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 6 days 2,000 total 4 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -19445,12 +19445,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 27 days 15 Objectives 41% 59%</t>
+          <t>NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 26 days 15 Objectives 39% 61%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 27 days</t>
+          <t>Expires in 26 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -19482,12 +19482,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 6 days 5 Objectives 36% 64%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 36% 64%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -19519,12 +19519,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 6 days 2,000 total 3 of 5 Objectives 81% 19%</t>
+          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -19556,12 +19556,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 6 days 3,000 total 5 Objectives 76% 24%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 5 days 3,000 total 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -19593,12 +19593,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 6 days 225 total 2 Objectives 79% 21%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 5 days 225 total 2 Objectives 79% 21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -19630,12 +19630,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 13 days 3,000 total 5 Objectives 95% 5%</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 12 days 3,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -19667,12 +19667,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 13 days 2,000 total 3 Objectives 85% 15%</t>
+          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 12 days 2,000 total 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -19704,12 +19704,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 13 days 7 Objectives 84% 16%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 12 days 7 Objectives 84% 16%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -19741,12 +19741,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 13 days 1 Objectives 92% 8%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 12 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -19778,12 +19778,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 13 days 5 Objectives 89% 11%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 12 days 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -19815,12 +19815,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 13 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 12 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 13 days</t>
+          <t>Expires in 12 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 7 days 9 Objectives 93% 7% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 6 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20816,7 +20816,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 7 days 6 Objectives 84% 16% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 83% 17% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20838,7 +20838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 7 days 2,000 total 4 Objectives 91% 9% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 6 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20860,7 +20860,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 27 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 26 days 15 Objectives 39% 61% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20882,7 +20882,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 6 days 5 Objectives 36% 64% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 36% 64% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20904,7 +20904,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 6 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20926,7 +20926,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 6 days 3,000 total 5 Objectives 76% 24% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 5 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 6 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 5 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 13 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 12 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20992,7 +20992,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 13 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 12 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 13 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 12 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 13 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 12 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21058,7 +21058,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 13 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 12 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 13 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 12 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28 03:01:37</t>
+          <t>2026-06-29 03:05:15</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28 02:00:00</t>
+          <t>2026-06-29 02:00:00</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 6 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 5 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 83% 17% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 5 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 6 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 5 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 26 days 15 Objectives 39% 61% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 25 days 15 Objectives 39% 61% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 36% 64% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 4 days 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 4 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 5 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 4 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 5 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 4 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 12 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 11 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 12 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 11 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 12 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 11 days 7 Objectives 85% 15% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 12 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 11 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 12 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 11 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 12 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 11 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -19304,12 +19304,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+</t>
+          <t>Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11%</t>
+          <t>Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -19329,17 +19329,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens</t>
+          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 6 days 9 Objectives 96% 4%</t>
+          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 5 days 9 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -19366,17 +19366,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack</t>
+          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 83% 17%</t>
+          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 5 days 6 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -19403,17 +19403,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP</t>
+          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 6 days 2,000 total 4 Objectives 93% 7%</t>
+          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 5 days 2,000 total 4 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -19440,17 +19440,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack</t>
+          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 26 days 15 Objectives 39% 61%</t>
+          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 25 days 15 Objectives 39% 61%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 26 days</t>
+          <t>Expires in 25 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -19482,12 +19482,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 36% 64%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 4 days 5 Objectives 37% 63%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -19519,12 +19519,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 81% 19%</t>
+          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 4 days 2,000 total 3 of 5 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -19556,12 +19556,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 5 days 3,000 total 5 Objectives 77% 23%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 4 days 3,000 total 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -19593,12 +19593,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 5 days 225 total 2 Objectives 79% 21%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 4 days 225 total 2 Objectives 79% 21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -19630,12 +19630,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 12 days 3,000 total 5 Objectives 95% 5%</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 11 days 3,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -19667,12 +19667,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 12 days 2,000 total 3 Objectives 85% 15%</t>
+          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 11 days 2,000 total 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -19704,12 +19704,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 12 days 7 Objectives 84% 16%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 11 days 7 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -19741,12 +19741,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 12 days 1 Objectives 92% 8%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 11 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -19778,12 +19778,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 12 days 5 Objectives 89% 11%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 11 days 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -19815,12 +19815,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 12 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 11 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 12 days</t>
+          <t>Expires in 11 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. NEW Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. NEW Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 6 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 5 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20816,7 +20816,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. NEW Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 83% 17% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 5 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20838,7 +20838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. NEW Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 6 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 5 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20860,7 +20860,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. NEW Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 26 days 15 Objectives 39% 61% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 25 days 15 Objectives 39% 61% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20882,7 +20882,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 36% 64% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 4 days 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20904,7 +20904,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 4 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20926,7 +20926,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 5 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 4 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 5 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 4 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 12 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 11 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -20992,7 +20992,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 12 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 11 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 12 days 7 Objectives 84% 16% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 11 days 7 Objectives 85% 15% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 12 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 11 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21058,7 +21058,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 12 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 11 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 12 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 11 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30 04:06:06</t>
+          <t>2026-07-01 03:57:02</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30 02:00:00</t>
+          <t>2026-07-01 02:00:00</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. NEW Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 77% 23% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 82% 18% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. NEW Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 7 days 8 of 10 Objectives 67% 33% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 6 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. NEW Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 7 days 5 Objectives 74% 26% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 6 days 5 Objectives 76% 24% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 4 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 3 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 4 days 6 Objectives 82% 18% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 4 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 3 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 24 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 23 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 3 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 2 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 3 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; TOTS Milestone TOTS Milestone - EA SPORTS FC 26 Objectives Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. TOTS Milestone Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. 3X 87+ Rare Gold Players Pack 16 Objectives 82% 18% Rewards Award Award 1 Of 3 88+ Rare Gold Players Award Award 1x 20x 80+ Rare Gold Players Pack 1x 2x 86+ Rare Gold Players Pack 1x 10x 82+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 10x 80+ Rare Gold Players Pack 1x 10x 81+ Rare Gold Players Pack 1x 86+ Rare Gold Player Pack 1x 3x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x Serie A/MLS TOTS Player Pack 1x 3x 87+ Rare Gold Players Pack Rise Above Score a headed goal in 8 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a Liga Portugal TOTS player. 20X 80+ Rare Gold Players Pack Selfless Assist a goal in 30 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a Liga F TOTS player. 2X 86+ Rare Gold Players Pack Finesse Dialled Score a finesse goal in 30 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a LALIGA TOTS player. 10X 82+ Rare Gold Players Pack Süper Lig Triple Win 3 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least one Süper Lig TOTS player in your starting 11. 7X 83+ Rare Gold Players Pack Leave No Doubt Score 6 goals in a single match in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) while having an Arkema Première Ligue TOTS player in your starting 11. Award Ligue 1 Leaders Win 15 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 1 Ligue 1 TOTS player in your starting 11. Award Shut Out Allow 1 goal or less in 20 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 NWSL TOTS players in your starting 11. 5X 83+ Rare Gold Players Pack Deadball Danger Score a free kick goal in 3 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) with a Roshn Saudi League TOTS player. 1 Of 3 88+ Rare Gold Players Hot Streak Score a goal in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a Frauen-Bundesliga TOTS player. 10X 80+ Rare Gold Players Pack High Margins Score 4 or more goals in 20 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 Bundesliga TOTS players in your starting 11. Award Championship Momentum Play 20 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having min. 1 EFL Championship TOTS player in your starting 11. Award Whip It Assist with a cross in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a BWSL TOTS player. 10X 81+ Rare Gold Players Pack Take a Risk Assist using through balls in 25 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a Premier League TOTS player. 86+ Rare Gold Player Pack Total Football Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 Eredivisie TOTS players in your starting 11. 3X 84+ Rare Gold Players Pack Cleat Rockets Score 10 Power Shots in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with an MLS TOTS player. 3X 86+ Rare Gold Players Pack Defensive Heritage Concede 1 goal or less in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) with at least 1 Serie A TOTS player in your Defense (Preferred Position only, RB/LB/CB). Serie A/Mls Tots Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; TOTS Milestone TOTS Milestone - EA SPORTS FC 26 Objectives Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. TOTS Milestone Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. 3X 87+ Rare Gold Players Pack 16 Objectives 81% 19% Rewards Award Award 1 Of 3 88+ Rare Gold Players Award Award 1x 20x 80+ Rare Gold Players Pack 1x 2x 86+ Rare Gold Players Pack 1x 10x 82+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 10x 80+ Rare Gold Players Pack 1x 10x 81+ Rare Gold Players Pack 1x 86+ Rare Gold Player Pack 1x 3x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x Serie A/MLS TOTS Player Pack 1x 3x 87+ Rare Gold Players Pack Rise Above Score a headed goal in 8 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a Liga Portugal TOTS player. 20X 80+ Rare Gold Players Pack Selfless Assist a goal in 30 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a Liga F TOTS player. 2X 86+ Rare Gold Players Pack Finesse Dialled Score a finesse goal in 30 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a LALIGA TOTS player. 10X 82+ Rare Gold Players Pack Süper Lig Triple Win 3 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least one Süper Lig TOTS player in your starting 11. 7X 83+ Rare Gold Players Pack Leave No Doubt Score 6 goals in a single match in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) while having an Arkema Première Ligue TOTS player in your starting 11. Award Ligue 1 Leaders Win 15 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 1 Ligue 1 TOTS player in your starting 11. Award Shut Out Allow 1 goal or less in 20 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 NWSL TOTS players in your starting 11. 5X 83+ Rare Gold Players Pack Deadball Danger Score a free kick goal in 3 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) with a Roshn Saudi League TOTS player. 1 Of 3 88+ Rare Gold Players Hot Streak Score a goal in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a Frauen-Bundesliga TOTS player. 10X 80+ Rare Gold Players Pack High Margins Score 4 or more goals in 20 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 Bundesliga TOTS players in your starting 11. Award Championship Momentum Play 20 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having min. 1 EFL Championship TOTS player in your starting 11. Award Whip It Assist with a cross in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a BWSL TOTS player. 10X 81+ Rare Gold Players Pack Take a Risk Assist using through balls in 25 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a Premier League TOTS player. 86+ Rare Gold Player Pack Total Football Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 Eredivisie TOTS players in your starting 11. 3X 84+ Rare Gold Players Pack Cleat Rockets Score 10 Power Shots in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with an MLS TOTS player. 3X 86+ Rare Gold Players Pack Defensive Heritage Concede 1 goal or less in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) with at least 1 Serie A TOTS player in your Defense (Preferred Position only, RB/LB/CB). Serie A/Mls Tots Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -9225,12 +9225,12 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -9301,12 +9301,12 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -9453,12 +9453,12 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -9601,12 +9601,12 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -10033,12 +10033,12 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
@@ -10249,12 +10249,12 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
@@ -20434,12 +20434,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NEW Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock</t>
+          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 77% 23%</t>
+          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 82% 18%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -20459,17 +20459,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NEW Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz</t>
+          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NEW Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 7 days 8 of 10 Objectives 67% 33%</t>
+          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 6 days 8 of 10 Objectives 68% 32%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -20496,17 +20496,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NEW Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick</t>
+          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NEW Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 7 days 5 Objectives 74% 26%</t>
+          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 6 days 5 Objectives 76% 24%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 7 days</t>
+          <t>Expires in 6 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -20563,12 +20563,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 4 days 9 Objectives 96% 4%</t>
+          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 3 days 9 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -20600,12 +20600,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 4 days 6 Objectives 82% 18%</t>
+          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 4 days 2,000 total 4 Objectives 93% 7%</t>
+          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 3 days 2,000 total 4 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -20674,12 +20674,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 24 days 15 Objectives 41% 59%</t>
+          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 23 days 15 Objectives 41% 59%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 24 days</t>
+          <t>Expires in 23 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -20711,12 +20711,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 37% 63%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 37% 63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -20748,12 +20748,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 81% 19%</t>
+          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -20785,12 +20785,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 3 days 3,000 total 5 Objectives 77% 23%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 2 days 3,000 total 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -20822,12 +20822,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 3 days 225 total 2 Objectives 79% 21%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 225 total 2 Objectives 79% 21%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -20869,12 +20869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20906,12 +20906,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20943,12 +20943,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20980,12 +20980,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -21017,12 +21017,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7/9 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TOTS Milestone Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. 3X 87+ Rare Gold Players Pack 16 Objectives 82% 18%</t>
+          <t>TOTS Milestone Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. 3X 87+ Rare Gold Players Pack 16 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -22001,7 +22001,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. NEW Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 77% 23% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 82% 18% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22023,7 +22023,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. NEW Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 7 days 8 of 10 Objectives 67% 33% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 6 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. NEW Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 7 days 5 Objectives 74% 26% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 6 days 5 Objectives 76% 24% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 4 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 3 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22111,7 +22111,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 4 days 6 Objectives 82% 18% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22133,7 +22133,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 4 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 3 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22155,7 +22155,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 24 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 23 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22221,7 +22221,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 3 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 2 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22243,7 +22243,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 3 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22419,7 +22419,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; TOTS Milestone TOTS Milestone - EA SPORTS FC 26 Objectives Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. TOTS Milestone Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. 3X 87+ Rare Gold Players Pack 16 Objectives 82% 18% Rewards Award Award 1 Of 3 88+ Rare Gold Players Award Award 1x 20x 80+ Rare Gold Players Pack 1x 2x 86+ Rare Gold Players Pack 1x 10x 82+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 10x 80+ Rare Gold Players Pack 1x 10x 81+ Rare Gold Players Pack 1x 86+ Rare Gold Player Pack 1x 3x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x Serie A/MLS TOTS Player Pack 1x 3x 87+ Rare Gold Players Pack Rise Above Score a headed goal in 8 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a Liga Portugal TOTS player. 20X 80+ Rare Gold Players Pack Selfless Assist a goal in 30 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a Liga F TOTS player. 2X 86+ Rare Gold Players Pack Finesse Dialled Score a finesse goal in 30 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a LALIGA TOTS player. 10X 82+ Rare Gold Players Pack Süper Lig Triple Win 3 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least one Süper Lig TOTS player in your starting 11. 7X 83+ Rare Gold Players Pack Leave No Doubt Score 6 goals in a single match in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) while having an Arkema Première Ligue TOTS player in your starting 11. Award Ligue 1 Leaders Win 15 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 1 Ligue 1 TOTS player in your starting 11. Award Shut Out Allow 1 goal or less in 20 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 NWSL TOTS players in your starting 11. 5X 83+ Rare Gold Players Pack Deadball Danger Score a free kick goal in 3 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) with a Roshn Saudi League TOTS player. 1 Of 3 88+ Rare Gold Players Hot Streak Score a goal in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a Frauen-Bundesliga TOTS player. 10X 80+ Rare Gold Players Pack High Margins Score 4 or more goals in 20 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 Bundesliga TOTS players in your starting 11. Award Championship Momentum Play 20 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having min. 1 EFL Championship TOTS player in your starting 11. Award Whip It Assist with a cross in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a BWSL TOTS player. 10X 81+ Rare Gold Players Pack Take a Risk Assist using through balls in 25 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a Premier League TOTS player. 86+ Rare Gold Player Pack Total Football Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 Eredivisie TOTS players in your starting 11. 3X 84+ Rare Gold Players Pack Cleat Rockets Score 10 Power Shots in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with an MLS TOTS player. 3X 86+ Rare Gold Players Pack Defensive Heritage Concede 1 goal or less in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) with at least 1 Serie A TOTS player in your Defense (Preferred Position only, RB/LB/CB). Serie A/Mls Tots Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; TOTS Milestone TOTS Milestone - EA SPORTS FC 26 Objectives Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. TOTS Milestone Complete the TOTS Milestone Objective group to earn pack and celebration rewards! All rewards are untradeable. 3X 87+ Rare Gold Players Pack 16 Objectives 81% 19% Rewards Award Award 1 Of 3 88+ Rare Gold Players Award Award 1x 20x 80+ Rare Gold Players Pack 1x 2x 86+ Rare Gold Players Pack 1x 10x 82+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 10x 80+ Rare Gold Players Pack 1x 10x 81+ Rare Gold Players Pack 1x 86+ Rare Gold Player Pack 1x 3x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x Serie A/MLS TOTS Player Pack 1x 3x 87+ Rare Gold Players Pack Rise Above Score a headed goal in 8 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a Liga Portugal TOTS player. 20X 80+ Rare Gold Players Pack Selfless Assist a goal in 30 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a Liga F TOTS player. 2X 86+ Rare Gold Players Pack Finesse Dialled Score a finesse goal in 30 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) using a LALIGA TOTS player. 10X 82+ Rare Gold Players Pack Süper Lig Triple Win 3 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least one Süper Lig TOTS player in your starting 11. 7X 83+ Rare Gold Players Pack Leave No Doubt Score 6 goals in a single match in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) while having an Arkema Première Ligue TOTS player in your starting 11. Award Ligue 1 Leaders Win 15 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 1 Ligue 1 TOTS player in your starting 11. Award Shut Out Allow 1 goal or less in 20 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 NWSL TOTS players in your starting 11. 5X 83+ Rare Gold Players Pack Deadball Danger Score a free kick goal in 3 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) with a Roshn Saudi League TOTS player. 1 Of 3 88+ Rare Gold Players Hot Streak Score a goal in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a Frauen-Bundesliga TOTS player. 10X 80+ Rare Gold Players Pack High Margins Score 4 or more goals in 20 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 Bundesliga TOTS players in your starting 11. Award Championship Momentum Play 20 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having min. 1 EFL Championship TOTS player in your starting 11. Award Whip It Assist with a cross in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a BWSL TOTS player. 10X 81+ Rare Gold Players Pack Take a Risk Assist using through balls in 25 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with a Premier League TOTS player. 86+ Rare Gold Player Pack Total Football Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) while having at least 2 Eredivisie TOTS players in your starting 11. 3X 84+ Rare Gold Players Pack Cleat Rockets Score 10 Power Shots in Squad Battles on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events/Rush) with an MLS TOTS player. 3X 86+ Rare Gold Players Pack Defensive Heritage Concede 1 goal or less in 15 separate Squad Battles matches on Min. Semi-Pro difficulty (or Rivals/Champions/Live Events) with at least 1 Serie A TOTS player in your Defense (Preferred Position only, RB/LB/CB). Serie A/Mls Tots Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:02</t>
+          <t>2026-07-02 04:00:36</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01 02:00:00</t>
+          <t>2026-07-02 02:00:00</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 82% 18% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 6 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 5 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 6 days 5 Objectives 76% 24% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 5 days 5 Objectives 77% 23% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -807,7 +807,7 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 3 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 2 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 2 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 3 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 2 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 23 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 22 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1042,22 +1042,22 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1142,22 +1142,22 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 2 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 22 hours 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1192,22 +1192,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 22 hours 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 9 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 8 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 9 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 8 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 9 days 7 Objectives 85% 15% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 8 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 9 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 8 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 9 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 8 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 9 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 8 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Mastery Rivals Mastery - EA SPORTS FC 26 Objectives Beat your Rivals to prove you are the G.O.A.T! Rivals Mastery Beat your Rivals to prove you are the G.O.A.T! Stadium Trophy 5 Objectives 83% 17% Rewards Stadium Trophy Stadium Trophy 1x Jumbo Rare Players Pack 1x Rare Players Pack 1x 2x 75+ Rare Gold Players Pack 1x 82+ Rare Gold Player Pack 250 Rivals Wins Win 250 Matches in Rivals. Jumbo Rare Players Pack 100 Rivals Wins Win 100 Matches in Rivals. Stadium Trophy 50 Rivals Wins Win 50 Matches in Rivals. Rare Players Pack 25 Rivals Wins Win 25 Matches in Rivals. 2X 75+ Rare Gold Players Pack 10 Rivals Wins Win 10 Matches in Rivals. 82+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Mastery Rivals Mastery - EA SPORTS FC 26 Objectives Beat your Rivals to prove you are the G.O.A.T! Rivals Mastery Beat your Rivals to prove you are the G.O.A.T! Stadium Trophy 5 Objectives 80% 20% Rewards Stadium Trophy Stadium Trophy 1x Jumbo Rare Players Pack 1x Rare Players Pack 1x 2x 75+ Rare Gold Players Pack 1x 82+ Rare Gold Player Pack 250 Rivals Wins Win 250 Matches in Rivals. Jumbo Rare Players Pack 100 Rivals Wins Win 100 Matches in Rivals. Stadium Trophy 50 Rivals Wins Win 50 Matches in Rivals. Rare Players Pack 25 Rivals Wins Win 25 Matches in Rivals. 2X 75+ Rare Gold Players Pack 10 Rivals Wins Win 10 Matches in Rivals. 82+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6780,17 +6780,17 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -6932,17 +6932,17 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
@@ -7084,17 +7084,17 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -7160,17 +7160,17 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
@@ -7236,17 +7236,17 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
@@ -7392,17 +7392,17 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
@@ -7468,17 +7468,17 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
@@ -7544,17 +7544,17 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -7620,17 +7620,17 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
@@ -7696,17 +7696,17 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -7772,17 +7772,17 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
@@ -7848,17 +7848,17 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
@@ -7924,17 +7924,17 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
@@ -8004,17 +8004,17 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -8084,17 +8084,17 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
@@ -8160,17 +8160,17 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -8236,17 +8236,17 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
@@ -8308,17 +8308,17 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
@@ -8384,17 +8384,17 @@
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 82% 18%</t>
+          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -20464,12 +20464,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 6 days 8 of 10 Objectives 68% 32%</t>
+          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 5 days 8 of 10 Objectives 68% 32%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -20501,12 +20501,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 6 days 5 Objectives 76% 24%</t>
+          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 5 days 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11%</t>
+          <t>Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -20563,12 +20563,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 3 days 9 Objectives 96% 4%</t>
+          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 2 days 9 Objectives 96% 4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -20600,12 +20600,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 81% 19%</t>
+          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 2 days 6 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 3 days 2,000 total 4 Objectives 93% 7%</t>
+          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 2 days 2,000 total 4 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -20674,12 +20674,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 23 days 15 Objectives 41% 59%</t>
+          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 22 days 15 Objectives 41% 59%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 23 days</t>
+          <t>Expires in 22 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -20711,22 +20711,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 37% 63%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 37% 63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20748,22 +20748,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 81% 19%</t>
+          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20785,22 +20785,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 2 days 3,000 total 5 Objectives 77% 23%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 22 hours 3,000 total 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20822,22 +20822,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 225 total 2 Objectives 79% 21%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 22 hours 225 total 2 Objectives 79% 21%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 22 hours</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7/3 02:00</t>
+          <t>7/3 00:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T02:00+09:00</t>
+          <t>2026-07-03T00:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20859,12 +20859,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 9 days 3,000 total 5 Objectives 95% 5%</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 8 days 3,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 9 days 2,000 total 3 Objectives 85% 15%</t>
+          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 8 days 2,000 total 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -20933,12 +20933,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 9 days 7 Objectives 85% 15%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 8 days 7 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -20970,12 +20970,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 9 days 1 Objectives 92% 8%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 8 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -21007,12 +21007,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 9 days 5 Objectives 89% 11%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 8 days 5 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -21044,12 +21044,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 9 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 8 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Expires in 9 days</t>
+          <t>Expires in 8 days</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -21908,7 +21908,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Rivals Mastery Beat your Rivals to prove you are the G.O.A.T! Stadium Trophy 5 Objectives 83% 17%</t>
+          <t>Rivals Mastery Beat your Rivals to prove you are the G.O.A.T! Stadium Trophy 5 Objectives 80% 20%</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -22001,7 +22001,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 82% 18% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22023,7 +22023,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 6 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 5 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 6 days 5 Objectives 76% 24% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 5 days 5 Objectives 77% 23% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22067,7 +22067,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 89% 11% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 3 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 2 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22111,7 +22111,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 2 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22133,7 +22133,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 3 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 2 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22155,7 +22155,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 23 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 22 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22221,7 +22221,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 2 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 22 hours 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22243,7 +22243,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 2 days 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 22 hours 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 9 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 8 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22287,7 +22287,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 9 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 8 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 9 days 7 Objectives 85% 15% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 8 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 9 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 8 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22353,7 +22353,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 9 days 5 Objectives 89% 11% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 8 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22375,7 +22375,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 9 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 8 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Mastery Rivals Mastery - EA SPORTS FC 26 Objectives Beat your Rivals to prove you are the G.O.A.T! Rivals Mastery Beat your Rivals to prove you are the G.O.A.T! Stadium Trophy 5 Objectives 83% 17% Rewards Stadium Trophy Stadium Trophy 1x Jumbo Rare Players Pack 1x Rare Players Pack 1x 2x 75+ Rare Gold Players Pack 1x 82+ Rare Gold Player Pack 250 Rivals Wins Win 250 Matches in Rivals. Jumbo Rare Players Pack 100 Rivals Wins Win 100 Matches in Rivals. Stadium Trophy 50 Rivals Wins Win 50 Matches in Rivals. Rare Players Pack 25 Rivals Wins Win 25 Matches in Rivals. 2X 75+ Rare Gold Players Pack 10 Rivals Wins Win 10 Matches in Rivals. 82+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Rivals Mastery Rivals Mastery - EA SPORTS FC 26 Objectives Beat your Rivals to prove you are the G.O.A.T! Rivals Mastery Beat your Rivals to prove you are the G.O.A.T! Stadium Trophy 5 Objectives 80% 20% Rewards Stadium Trophy Stadium Trophy 1x Jumbo Rare Players Pack 1x Rare Players Pack 1x 2x 75+ Rare Gold Players Pack 1x 82+ Rare Gold Player Pack 250 Rivals Wins Win 250 Matches in Rivals. Jumbo Rare Players Pack 100 Rivals Wins Win 100 Matches in Rivals. Stadium Trophy 50 Rivals Wins Win 50 Matches in Rivals. Rare Players Pack 25 Rivals Wins Win 25 Matches in Rivals. 2X 75+ Rare Gold Players Pack 10 Rivals Wins Win 10 Matches in Rivals. 82+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02 04:00:36</t>
+          <t>2026-07-03 03:27:04</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02 02:00:00</t>
+          <t>2026-07-03 02:00:00</t>
         </is>
       </c>
     </row>
@@ -651,25 +651,37 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Drive or Park the bus? - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 7 days 5 Objectives 36% 64% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -678,7 +690,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -689,37 +701,37 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 5 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! NEW Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 7 days 2,000 total 3 of 5 Objectives 76% 24% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -728,7 +740,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -739,37 +751,37 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
+          <t>https://www.fut.gg/objectives/seasonal/981-weekly-objectives/</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 5 days 5 Objectives 77% 23% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! NEW Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 7 days 3,000 total 5 Objectives 75% 25% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -778,7 +790,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -789,25 +801,37 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/951-daily-objectives/</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 7 days 300 total 2 Objectives 69% 31% Rewards 300 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 100 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 100 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -816,7 +840,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -827,37 +851,25 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Drive or Park the bus? - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 2 days</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>7/4 02:00</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-04T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 2 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -866,7 +878,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -877,7 +889,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -887,27 +899,27 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 2 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 4 days 8 of 10 Objectives 69% 31% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -916,7 +928,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -927,37 +939,37 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 2 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 4 days 5 Objectives 77% 23% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -977,37 +989,25 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 22 days</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>7/24 02:00</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-24T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 22 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1027,37 +1027,37 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 23 hours 9 Objectives 95% 5% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1077,37 +1077,37 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 23 hours 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1127,37 +1127,37 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 22 hours 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 23 hours 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1177,37 +1177,37 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 22 hours 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 21 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 8 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 7 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 8 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 7 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 8 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 7 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 8 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 7 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 8 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 7 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 8 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 7 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Goals Galore</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles.</t>
+          <t>Complete Rush Bonuses alongside your teammates to earn Rush Points!</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>10000 Coins / Evo Unlock</t>
+          <t>2X 89+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
@@ -2977,25 +2977,37 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Drive or Park the bus? - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/||score 3 goals or more and win in 60 separate matches in champions, rivals, live events or squad battles.||goals galore</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/||complete rush bonuses alongside your teammates to earn rush points!||weekly rush points - ea sports fc 26 objectives</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -3010,22 +3022,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Tough to Beat</t>
+          <t>2,500 Rush Points</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles.</t>
+          <t>Earn 2,500 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>10000 Coins</t>
+          <t>1x 2x 85+ Rare Gold Players Pack / 1x 88+ Rare Gold Player Pack / 1x 2x 89+ Rare Gold Players Pack / 4X 83+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
@@ -3041,25 +3053,37 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Drive or Park the bus? - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/||concede 1 goal or less and win in 30 separate matches in champions, rivals, live events or squad battles.||tough to beat</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/||earn 2,500 points by completing bonuses in rush.||2,500 rush points</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -3070,24 +3094,28 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Score 1</t>
+          <t>10,000 Rush Points</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in the Festival of Football Gauntlet 2.</t>
+          <t>Earn 10,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1x 10x 87+ Rare Gold Players Pack / 1x 8x 88+ Rare Gold Players Pack / 3x 5x 90+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
+          <t>4X 83+ Rare Gold Players Pack / 3X 84+ Rare Gold Players Pack / 4X 84+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -3096,42 +3124,42 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||score at least 1 goal in the festival of football gauntlet 2.||score 1</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/||earn 10,000 points by completing bonuses in rush.||10,000 rush points</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -3142,24 +3170,28 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Score in 4</t>
+          <t>25,000 Rush Points</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2.</t>
+          <t>Earn 25,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>10X 86+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+          <t>3X 84+ Rare Gold Players Pack / 4X 84+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -3168,42 +3200,42 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||score at least 1 goal in 4 separate matches in the festival of football gauntlet 2.||score in 4</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/||earn 25,000 points by completing bonuses in rush.||25,000 rush points</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -3214,24 +3246,28 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Doubles</t>
+          <t>35,000 Rush Points</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Win at least 2 matches within a single round in the Festival of Football Gauntlet 2.</t>
+          <t>Earn 35,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>10X 86+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+          <t>4X 84+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack / 88+ Rare Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -3240,42 +3276,42 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||win at least 2 matches within a single round in the festival of football gauntlet 2.||doubles</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/||earn 35,000 points by completing bonuses in rush.||35,000 rush points</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -3286,24 +3322,28 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A Pair of Doubles</t>
+          <t>45,000 Rush Points</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice.</t>
+          <t>Earn 45,000 points by completing bonuses in Rush.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>10X 86+ Rare Gold Players Pack / Evo Unlock</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+          <t>2X 85+ Rare Gold Players Pack / 88+ Rare Gold Player Pack</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -3312,42 +3352,42 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||win at least 2 matches within a single round in the festival of football gauntlet 2, twice.||a pair of doubles</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/||earn 45,000 points by completing bonuses in rush.||45,000 rush points</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -3358,24 +3398,28 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Triplets</t>
+          <t>3 of 5 Objectives</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Win at least 3 matches within a single round in the Festival of Football Gauntlet 2.</t>
+          <t>Play 5 Squad Battles</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / 10X 87+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>2,000 SP / 250 SP</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -3389,37 +3433,37 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||win at least 3 matches within a single round in the festival of football gauntlet 2.||triplets</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 squad battles||3 of 5 objectives</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -3430,25 +3474,33 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>A Pair of Triplets</t>
+          <t>3 of 5 Objectives</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice.</t>
+          <t>Play 5 Squad Battles matches on Min. Semi-Pro difficulty.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Evo Unlock / 10X 87+ Rare Gold Players Pack / 8X 88+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+          <t>2,000 SP / 250 SP</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -3461,37 +3513,37 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||win at least 3 matches within a single round in the festival of football gauntlet 2, twice.||a pair of triplets</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 squad battles matches on min. semi-pro difficulty.||3 of 5 objectives</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -3502,24 +3554,28 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Score in 8</t>
+          <t>Play 5 Rivals</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2.</t>
+          <t>Play 5 Rivals</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>10X 87+ Rare Gold Players Pack / 8X 88+ Rare Gold Players Pack / 5X 90+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
+          <t>2,000 SP / 250 SP</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -3533,37 +3589,37 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||score at least 1 goal in 8 separate matches in the festival of football gauntlet 2.||score in 8</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 rivals||play 5 rivals</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -3574,24 +3630,28 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Score in 12</t>
+          <t>Play 5 matches in Rivals.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2.</t>
+          <t>Play 5 matches in Rivals.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>5X 90+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Rivals</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -3605,37 +3665,37 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||score at least 1 goal in 12 separate matches in the festival of football gauntlet 2.||score in 12</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 matches in rivals.||play 5 matches in rivals.</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -3646,24 +3706,28 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Score 2</t>
+          <t>Play 5 Champions</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Score at least 2 goals in the Festival of Football Gauntlet 2.</t>
+          <t>Play 5 Champions</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1x 7x 84+ Rare Gold Players Pack / 1x 7x 85+ Rare Gold Players Pack / 1x 10x 86+ Rare Gold Players Pack / 5X 84+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -3672,42 +3736,42 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/||score at least 2 goals in the festival of football gauntlet 2.||score 2</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 champions||play 5 champions</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -3718,24 +3782,28 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Play 3</t>
+          <t>Play 5 matches in Champions.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Play 3 matches in the Festival of Football Gauntlet 2.</t>
+          <t>Play 5 matches in Champions.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5X 84+ Rare Gold Players Pack / 7X 84+ Rare Gold Players Pack / 7X 85+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Champions</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -3744,42 +3812,42 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/||play 3 matches in the festival of football gauntlet 2.||play 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 matches in champions.||play 5 matches in champions.</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -3790,24 +3858,28 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Play 8</t>
+          <t>Play 5 Rush</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Play 8 matches in the Festival of Football Gauntlet 2.</t>
+          <t>Play 5 Rush</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7X 84+ Rare Gold Players Pack / 7X 85+ Rare Gold Players Pack / 10X 86+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -3816,42 +3888,42 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/||play 8 matches in the festival of football gauntlet 2.||play 8</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 rush||play 5 rush</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -3862,24 +3934,28 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Score in 8</t>
+          <t>Play 5 Ultimate Team Rush matches.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2.</t>
+          <t>Play 5 Ultimate Team Rush matches.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7X 85+ Rare Gold Players Pack / 10X 86+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
+          <t>250 SP</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -3888,42 +3964,42 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/||score at least 1 goal in 8 separate matches in the festival of football gauntlet 2.||score in 8</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 ultimate team rush matches.||play 5 ultimate team rush matches.</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -3934,29 +4010,29 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Assist in 10</t>
+          <t>Play 5 Live Events</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
+          <t>Play 5 Live Events</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>250 SP</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>Live Events</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -3964,30 +4040,42 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/||assist 1 goal in 10 separate matches with min. 3 glory hunters in your starting 11 in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||assist in 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 live events||play 5 live events</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -3998,29 +4086,29 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Defiant Defender</t>
+          <t>Play 5 matches in any Ultimate Team Live Event.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr"/>
+          <t>Play 5 matches in any Ultimate Team Live Event.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>250 SP</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>Live Events / Any Ultimate Team mode</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -4028,30 +4116,42 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/||concede 3 goals or less in 15 separate matches with min. 3 glory hunters in your starting 11 in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||defiant defender</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/||play 5 matches in any ultimate team live event.||play 5 matches in any ultimate team live event.</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -4062,22 +4162,26 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Win in 30</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr"/>
+          <t>Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events).</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Buy 10 Player Items on the Transfer Market. / 450 SP</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events</t>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -4092,30 +4196,42 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/981-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/||win in 30 separate matches with min. 3 glory hunters in your starting 11 in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||win in 30</t>
+          <t>https://www.fut.gg/objectives/seasonal/981-weekly-objectives/||play 10 matches in squad battles on min. semi-pro difficulty (or rush/rivals/champions/live events).||play 10</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -4126,22 +4242,26 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Score in 50</t>
+          <t>Win 10</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr"/>
+          <t>Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events).</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>450 SP</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles / Rivals / Champions / Live Events</t>
+          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -4156,30 +4276,42 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
+          <t>https://www.fut.gg/objectives/seasonal/981-weekly-objectives/</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/||score in 50 separate matches with min. 3 glory hunters in your starting 11 in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||score in 50</t>
+          <t>https://www.fut.gg/objectives/seasonal/981-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rush/rivals/champions/live events).||win 10</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -4190,26 +4322,26 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Score 1</t>
+          <t>Score 10</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Score 1 goal in the Moment of Glory Live Event.</t>
+          <t>Score 10 goals in any Ultimate Team game mode using a player from Mexico.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>2x 3x 85+ Rare Gold Players Pack / 2x 3x 86+ Rare Gold Players Pack / 1x 7x 87+ Rare Gold Players Pack / 5000 Coins</t>
+          <t>450 SP</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Moment of Glory Live Event</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr"/>
@@ -4220,42 +4352,42 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
+          <t>https://www.fut.gg/objectives/seasonal/981-weekly-objectives/</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score 1 goal in the moment of glory live event.||score 1</t>
+          <t>https://www.fut.gg/objectives/seasonal/981-weekly-objectives/||score 10 goals in any ultimate team game mode using a player from mexico.||score 10</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -4266,26 +4398,26 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Score 5</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals in the Moment of Glory Live Event.</t>
+          <t>Play 1 match in any Ultimate Team game mode and earn SP!</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>5000 Coins / 2 Of 8 Playstyle+ Pick</t>
+          <t>300 SP / 100 SP</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Moment of Glory Live Event</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
@@ -4296,42 +4428,42 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
+          <t>https://www.fut.gg/objectives/seasonal/951-daily-objectives/</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score 5 goals in the moment of glory live event.||score 5</t>
+          <t>https://www.fut.gg/objectives/seasonal/951-daily-objectives/||play 1 match in any ultimate team game mode and earn sp!||play 1</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -4342,28 +4474,24 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Score 10</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Score 10 goals in the Moment of Glory Live Event.</t>
+          <t>Score 2 goals</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>2 Of 8 Playstyle+ Pick / 3X 85+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Moment of Glory Live Event</t>
-        </is>
-      </c>
+          <t>300 SP / 100 SP</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -4372,42 +4500,42 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
+          <t>https://www.fut.gg/objectives/seasonal/951-daily-objectives/</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score 10 goals in the moment of glory live event.||score 10</t>
+          <t>https://www.fut.gg/objectives/seasonal/951-daily-objectives/||score 2 goals||play 1</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -4418,26 +4546,26 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Score in 3</t>
+          <t>Play 1</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11.</t>
+          <t>Score 2 goals in any Ultimate Team game mode.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3X 85+ Rare Gold Players Pack</t>
+          <t>100 SP</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Moment of Glory Live Event</t>
+          <t>Any Ultimate Team mode</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
@@ -4448,42 +4576,42 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
+          <t>https://www.fut.gg/objectives/seasonal/951-daily-objectives/</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score at least 1 goal in 3 separate matches in the moment of glory live event while having min. 6 players from asia and oceania in your starting 11.||score in 3</t>
+          <t>https://www.fut.gg/objectives/seasonal/951-daily-objectives/||score 2 goals in any ultimate team game mode.||play 1</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -4494,26 +4622,26 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Score in 3</t>
+          <t>Goals Galore</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11.</t>
+          <t>Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3X 85+ Rare Gold Players Pack</t>
+          <t>10000 Coins / Evo Unlock</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Moment of Glory Live Event</t>
+          <t>Squad Battles / Rivals / Champions / Live Events</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
@@ -4529,37 +4657,25 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Drive or Park the bus? - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 2 days</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>7/4 02:00</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-04T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score at least 1 goal in 3 separate matches in the moment of glory live event while having min. 6 players from africa in your starting 11.||score in 3</t>
+          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/||score 3 goals or more and win in 60 separate matches in champions, rivals, live events or squad battles.||goals galore</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -4570,26 +4686,26 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Score in 3</t>
+          <t>Tough to Beat</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11.</t>
+          <t>Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3X 85+ Rare Gold Players Pack / 3X 86+ Rare Gold Players Pack</t>
+          <t>10000 Coins</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Live Events / Moment of Glory Live Event</t>
+          <t>Squad Battles / Rivals / Champions / Live Events</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
@@ -4605,37 +4721,25 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Drive or Park the bus? - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 2 days</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>7/4 02:00</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-04T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score at least 1 goal in 3 separate matches in the moment of glory live event while having min. 6 players from europe in your starting 11.||score in 3</t>
+          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/||concede 1 goal or less and win in 30 separate matches in champions, rivals, live events or squad battles.||tough to beat</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -4646,28 +4750,24 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>Score 1</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11.</t>
+          <t>Score at least 1 goal in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3X 86+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Moment of Glory Live Event</t>
-        </is>
-      </c>
+          <t>1x 10x 87+ Rare Gold Players Pack / 1x 8x 88+ Rare Gold Players Pack / 3x 5x 90+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -4676,12 +4776,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -4691,27 +4791,27 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||win 3 matches in the moment of glory live event while having min. 6 players from europe in your starting 11.||win 3</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||score at least 1 goal in the festival of football gauntlet 2.||score 1</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -4722,28 +4822,24 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>Score in 4</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11.</t>
+          <t>Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3X 86+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Moment of Glory Live Event</t>
-        </is>
-      </c>
+          <t>10X 86+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -4752,12 +4848,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -4767,27 +4863,27 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||win 3 matches in the moment of glory live event while having min. 6 players from south america in your starting 11.||win 3</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||score at least 1 goal in 4 separate matches in the festival of football gauntlet 2.||score in 4</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -4798,28 +4894,24 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>Doubles</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11.</t>
+          <t>Win at least 2 matches within a single round in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3X 86+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Moment of Glory Live Event</t>
-        </is>
-      </c>
+          <t>10X 86+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -4828,12 +4920,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>G005</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -4843,27 +4935,27 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||win 3 matches in the moment of glory live event while having min. 6 players from north america in your starting 11.||win 3</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||win at least 2 matches within a single round in the festival of football gauntlet 2.||doubles</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -4874,28 +4966,24 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Play 2</t>
+          <t>A Pair of Doubles</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Play 2 matches in the Journey of Nations South America Live Event.</t>
+          <t>Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3x 3x 83+ Rare Gold Players Pack / 1x 3x 84+ Rare Gold Players Pack / 3X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Journey of Nations South America Live Event</t>
-        </is>
-      </c>
+          <t>10X 86+ Rare Gold Players Pack / Evo Unlock</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -4909,7 +4997,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -4919,27 +5007,27 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||play 2 matches in the journey of nations south america live event.||play 2</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||win at least 2 matches within a single round in the festival of football gauntlet 2, twice.||a pair of doubles</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4950,28 +5038,24 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Win 1</t>
+          <t>Triplets</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Win 1 match in the Journey of Nations South America Live Event.</t>
+          <t>Win at least 3 matches within a single round in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Journey of Nations South America Live Event</t>
-        </is>
-      </c>
+          <t>Evo Unlock / 10X 87+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -4985,7 +5069,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -4995,27 +5079,27 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||win 1 match in the journey of nations south america live event.||win 1</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||win at least 3 matches within a single round in the festival of football gauntlet 2.||triplets</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -5026,28 +5110,24 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Play 4</t>
+          <t>A Pair of Triplets</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Play 4 matches in the Journey of Nations South America Live Event</t>
+          <t>Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Journey of Nations South America Live Event</t>
-        </is>
-      </c>
+          <t>Evo Unlock / 10X 87+ Rare Gold Players Pack / 8X 88+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -5061,7 +5141,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -5071,27 +5151,27 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||play 4 matches in the journey of nations south america live event||play 4</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||win at least 3 matches within a single round in the festival of football gauntlet 2, twice.||a pair of triplets</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -5102,28 +5182,24 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Win 2</t>
+          <t>Score in 8</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Win 2 matches in the Journey of Nations South America Live Event.</t>
+          <t>Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Journey of Nations South America Live Event</t>
-        </is>
-      </c>
+          <t>10X 87+ Rare Gold Players Pack / 8X 88+ Rare Gold Players Pack / 5X 90+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -5137,7 +5213,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -5147,27 +5223,27 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||win 2 matches in the journey of nations south america live event.||win 2</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||score at least 1 goal in 8 separate matches in the festival of football gauntlet 2.||score in 8</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -5178,28 +5254,24 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Score 5</t>
+          <t>Score in 12</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Score 5 goals in the Journey of Nations South America Live Event</t>
+          <t>Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Journey of Nations South America Live Event</t>
-        </is>
-      </c>
+          <t>5X 90+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -5213,7 +5285,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5223,27 +5295,27 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||score 5 goals in the journey of nations south america live event||score 5</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/||score at least 1 goal in 12 separate matches in the festival of football gauntlet 2.||score in 12</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -5254,28 +5326,24 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Win 3</t>
+          <t>Score 2</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Win 3 matches in the Journey of Nations South America Live Event.</t>
+          <t>Score at least 2 goals in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Journey of Nations South America Live Event</t>
-        </is>
-      </c>
+          <t>1x 7x 84+ Rare Gold Players Pack / 1x 7x 85+ Rare Gold Players Pack / 1x 10x 86+ Rare Gold Players Pack / 5X 84+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -5284,12 +5352,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -5299,27 +5367,27 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||win 3 matches in the journey of nations south america live event.||win 3</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/||score at least 2 goals in the festival of football gauntlet 2.||score 2</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -5330,7 +5398,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -5339,24 +5407,16 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
+          <t>Play 3 matches in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>300 SP</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles / Rivals / Champions / Live Events</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>5X 84+ Rare Gold Players Pack / 7X 84+ Rare Gold Players Pack / 7X 85+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -5369,37 +5429,37 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/||play 3 matches in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||play 3</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/||play 3 matches in the festival of football gauntlet 2.||play 3</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -5410,33 +5470,25 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Score in 5</t>
+          <t>Play 8</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
+          <t>Play 8 matches in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>300 SP</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles / Rivals / Champions / Live Events</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>7X 84+ Rare Gold Players Pack / 7X 85+ Rare Gold Players Pack / 10X 86+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -5449,37 +5501,37 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/||score at least 1 goal in 5 separate matches in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||score in 5</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/||play 8 matches in the festival of football gauntlet 2.||play 8</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -5490,33 +5542,25 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Score in 8</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
+          <t>Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>300 SP</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles / Rivals / Champions / Live Events</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>7X 85+ Rare Gold Players Pack / 10X 86+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -5529,37 +5573,37 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/||play 10 matches in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||play 10</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/||score at least 1 goal in 8 separate matches in the festival of football gauntlet 2.||score in 8</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -5570,23 +5614,19 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Score in 15</t>
+          <t>Assist in 10</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>300 SP</t>
-        </is>
-      </c>
+          <t>Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr"/>
       <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Squad Battles / Rivals / Champions / Live Events</t>
@@ -5604,42 +5644,30 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
+          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 2 days</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>7/4 02:00</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-04T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/||score at least 1 goal in 15 separate matches in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||score in 15</t>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/||assist 1 goal in 10 separate matches with min. 3 glory hunters in your starting 11 in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||assist in 10</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -5650,28 +5678,32 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 10 times.</t>
+          <t>Defiant Defender</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 10 times.</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>1x 5x 84+ Rare Gold Players Pack / 1x 3x 86+ Rare Gold Players Pack / 1x 100 Rare Gold Players Pack / 4X 81+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
+          <t>Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Champions / Live Events</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -5681,37 +5713,25 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 22 days</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>7/24 02:00</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-24T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 10 times.||complete the glory hunters crafting upgrade sbc 10 times.</t>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/||concede 3 goals or less in 15 separate matches with min. 3 glory hunters in your starting 11 in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||defiant defender</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5722,28 +5742,32 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 15 times.</t>
+          <t>Win in 30</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 15 times.</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>4X 81+ Rare Gold Players Pack / 4X 82+ Rare Gold Players Pack / 7X 81+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
+          <t>Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Champions / Live Events</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -5753,37 +5777,25 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 22 days</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>7/24 02:00</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-24T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 15 times.||complete the glory hunters crafting upgrade sbc 15 times.</t>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/||win in 30 separate matches with min. 3 glory hunters in your starting 11 in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||win in 30</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -5794,28 +5806,32 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 20 times.</t>
+          <t>Score in 50</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 20 times.</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>4X 82+ Rare Gold Players Pack / 7X 81+ Rare Gold Players Pack / 5X 82+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
+          <t>Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Squad Battles / Rivals / Champions / Live Events</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -5825,37 +5841,25 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>Expires in 22 days</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>7/24 02:00</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-24T02:00+09:00</t>
-        </is>
-      </c>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 20 times.||complete the glory hunters crafting upgrade sbc 20 times.</t>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/||score in 50 separate matches with min. 3 glory hunters in your starting 11 in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||score in 50</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5866,68 +5870,72 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 25 times.</t>
+          <t>Score 1</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 25 times.</t>
+          <t>Score 1 goal in the Moment of Glory Live Event.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>7X 81+ Rare Gold Players Pack / 5X 82+ Rare Gold Players Pack / 4X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
+          <t>2x 3x 85+ Rare Gold Players Pack / 2x 3x 86+ Rare Gold Players Pack / 1x 7x 87+ Rare Gold Players Pack / 5000 Coins</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Moment of Glory Live Event</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 25 times.||complete the glory hunters crafting upgrade sbc 25 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score 1 goal in the moment of glory live event.||score 1</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5938,68 +5946,72 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 30 times.</t>
+          <t>Score 5</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 30 times.</t>
+          <t>Score 5 goals in the Moment of Glory Live Event.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>5X 82+ Rare Gold Players Pack / 4X 83+ Rare Gold Players Pack / 1 Of 2 86+ Rare Gold Players</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
+          <t>5000 Coins / 2 Of 8 Playstyle+ Pick</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Moment of Glory Live Event</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 30 times.||complete the glory hunters crafting upgrade sbc 30 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score 5 goals in the moment of glory live event.||score 5</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -6010,68 +6022,72 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 35 times.</t>
+          <t>Score 10</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 35 times.</t>
+          <t>Score 10 goals in the Moment of Glory Live Event.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>4X 83+ Rare Gold Players Pack / 1 Of 2 86+ Rare Gold Players / 5X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
+          <t>2 Of 8 Playstyle+ Pick / 3X 85+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Moment of Glory Live Event</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 35 times.||complete the glory hunters crafting upgrade sbc 35 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score 10 goals in the moment of glory live event.||score 10</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -6082,68 +6098,72 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 40 times.</t>
+          <t>Score in 3</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 40 times.</t>
+          <t>Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>1 Of 2 86+ Rare Gold Players / 5X 83+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
+          <t>3X 85+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Moment of Glory Live Event</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 40 times.||complete the glory hunters crafting upgrade sbc 40 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score at least 1 goal in 3 separate matches in the moment of glory live event while having min. 6 players from asia and oceania in your starting 11.||score in 3</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6154,68 +6174,72 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 45 times.</t>
+          <t>Score in 3</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 45 times.</t>
+          <t>Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5X 83+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack / 7X 83+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
+          <t>3X 85+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Moment of Glory Live Event</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 45 times.||complete the glory hunters crafting upgrade sbc 45 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score at least 1 goal in 3 separate matches in the moment of glory live event while having min. 6 players from africa in your starting 11.||score in 3</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -6226,68 +6250,72 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 50 times.</t>
+          <t>Score in 3</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 50 times.</t>
+          <t>Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>2X 85+ Rare Gold Players Pack / 7X 83+ Rare Gold Players Pack / 1 Of 3 86+ Rare Gold Players</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
+          <t>3X 85+ Rare Gold Players Pack / 3X 86+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Moment of Glory Live Event</t>
+        </is>
+      </c>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 50 times.||complete the glory hunters crafting upgrade sbc 50 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||score at least 1 goal in 3 separate matches in the moment of glory live event while having min. 6 players from europe in your starting 11.||score in 3</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -6298,68 +6326,72 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 60 times.</t>
+          <t>Win 3</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 60 times.</t>
+          <t>Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>7X 83+ Rare Gold Players Pack / 1 Of 3 86+ Rare Gold Players / 4X 84+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
+          <t>3X 86+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Moment of Glory Live Event</t>
+        </is>
+      </c>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 60 times.||complete the glory hunters crafting upgrade sbc 60 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||win 3 matches in the moment of glory live event while having min. 6 players from europe in your starting 11.||win 3</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -6370,68 +6402,72 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 70 times.</t>
+          <t>Win 3</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 70 times.</t>
+          <t>Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>1 Of 3 86+ Rare Gold Players / 4X 84+ Rare Gold Players Pack / 3X 85+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
+          <t>3X 86+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Moment of Glory Live Event</t>
+        </is>
+      </c>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 70 times.||complete the glory hunters crafting upgrade sbc 70 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||win 3 matches in the moment of glory live event while having min. 6 players from south america in your starting 11.||win 3</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -6442,68 +6478,72 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 80 times.</t>
+          <t>Win 3</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 80 times.</t>
+          <t>Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>4X 84+ Rare Gold Players Pack / 3X 85+ Rare Gold Players Pack / 5X 84+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr"/>
+          <t>3X 86+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Moment of Glory Live Event</t>
+        </is>
+      </c>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G009</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 80 times.||complete the glory hunters crafting upgrade sbc 80 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/||win 3 matches in the moment of glory live event while having min. 6 players from north america in your starting 11.||win 3</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -6514,68 +6554,72 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 90 times.</t>
+          <t>Play 2</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 90 times.</t>
+          <t>Play 2 matches in the Journey of Nations South America Live Event.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3X 85+ Rare Gold Players Pack / 5X 84+ Rare Gold Players Pack / 3X 86+ Rare Gold Players Pack</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr"/>
+          <t>3x 3x 83+ Rare Gold Players Pack / 1x 3x 84+ Rare Gold Players Pack / 3X 83+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Journey of Nations South America Live Event</t>
+        </is>
+      </c>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 90 times.||complete the glory hunters crafting upgrade sbc 90 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||play 2 matches in the journey of nations south america live event.||play 2</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -6586,68 +6630,72 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 95 times.</t>
+          <t>Win 1</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 95 times.</t>
+          <t>Win 1 match in the Journey of Nations South America Live Event.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>5X 84+ Rare Gold Players Pack / 3X 86+ Rare Gold Players Pack / 1 Of 3 88+ Rare Gold Players</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
+          <t>3X 83+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Journey of Nations South America Live Event</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 95 times.||complete the glory hunters crafting upgrade sbc 95 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||win 1 match in the journey of nations south america live event.||win 1</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -6658,68 +6706,72 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 100 times.</t>
+          <t>Play 4</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Complete the Glory Hunters Crafting Upgrade SBC 100 times.</t>
+          <t>Play 4 matches in the Journey of Nations South America Live Event</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3X 86+ Rare Gold Players Pack / 1 Of 3 88+ Rare Gold Players</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr"/>
+          <t>3X 83+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Live Events / Journey of Nations South America Live Event</t>
+        </is>
+      </c>
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>action_line_fallback</t>
+          <t>description_line_with_backward_title</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 days</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>7/24 02:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24T02:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 100 times.||complete the glory hunters crafting upgrade sbc 100 times.</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||play 4 matches in the journey of nations south america live event||play 4</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -6730,26 +6782,26 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Win 2</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Complete Rush Bonuses alongside your teammates to earn Rush Points!</t>
+          <t>Win 2 matches in the Journey of Nations South America Live Event.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>2X 89+ Rare Gold Players Pack</t>
+          <t>3X 83+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Live Events / Journey of Nations South America Live Event</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr"/>
@@ -6760,42 +6812,42 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||complete rush bonuses alongside your teammates to earn rush points!||weekly rush points - ea sports fc 26 objectives</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||win 2 matches in the journey of nations south america live event.||win 2</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -6806,26 +6858,26 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>2,500 Rush Points</t>
+          <t>Score 5</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Earn 2,500 points by completing bonuses in Rush.</t>
+          <t>Score 5 goals in the Journey of Nations South America Live Event</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>1x 2x 85+ Rare Gold Players Pack / 1x 88+ Rare Gold Player Pack / 1x 2x 89+ Rare Gold Players Pack / 4X 83+ Rare Gold Players Pack</t>
+          <t>3X 83+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Live Events / Journey of Nations South America Live Event</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
@@ -6836,42 +6888,42 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 2,500 points by completing bonuses in rush.||2,500 rush points</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||score 5 goals in the journey of nations south america live event||score 5</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -6882,26 +6934,26 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>10,000 Rush Points</t>
+          <t>Win 3</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Earn 10,000 points by completing bonuses in Rush.</t>
+          <t>Win 3 matches in the Journey of Nations South America Live Event.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>4X 83+ Rare Gold Players Pack / 3X 84+ Rare Gold Players Pack / 4X 84+ Rare Gold Players Pack</t>
+          <t>3X 83+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Live Events / Journey of Nations South America Live Event</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr"/>
@@ -6912,42 +6964,42 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G010</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 10,000 points by completing bonuses in rush.||10,000 rush points</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/||win 3 matches in the journey of nations south america live event.||win 3</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -6958,29 +7010,33 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>25,000 Rush Points</t>
+          <t>Play 3</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Earn 25,000 points by completing bonuses in Rush.</t>
+          <t>Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>3X 84+ Rare Gold Players Pack / 4X 84+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack</t>
+          <t>300 SP</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr"/>
+          <t>Squad Battles / Rivals / Champions / Live Events</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -6988,12 +7044,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -7003,27 +7059,27 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 25,000 points by completing bonuses in rush.||25,000 rush points</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/||play 3 matches in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||play 3</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -7034,29 +7090,33 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>35,000 Rush Points</t>
+          <t>Score in 5</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Earn 35,000 points by completing bonuses in Rush.</t>
+          <t>Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>4X 84+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack / 88+ Rare Gold Player Pack</t>
+          <t>300 SP</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr"/>
+          <t>Squad Battles / Rivals / Champions / Live Events</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -7064,12 +7124,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -7079,27 +7139,27 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 35,000 points by completing bonuses in rush.||35,000 rush points</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/||score at least 1 goal in 5 separate matches in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||score in 5</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -7110,29 +7170,33 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>45,000 Rush Points</t>
+          <t>Play 10</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Earn 45,000 points by completing bonuses in Rush.</t>
+          <t>Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2X 85+ Rare Gold Players Pack / 88+ Rare Gold Player Pack</t>
+          <t>300 SP</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr"/>
+          <t>Squad Battles / Rivals / Champions / Live Events</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -7140,12 +7204,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>G009</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -7155,27 +7219,27 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/||earn 45,000 points by completing bonuses in rush.||45,000 rush points</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/||play 10 matches in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||play 10</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -7186,29 +7250,33 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>3 of 5 Objectives</t>
+          <t>Score in 15</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles</t>
+          <t>Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions).</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>2,000 SP / 250 SP</t>
+          <t>300 SP</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr"/>
+          <t>Squad Battles / Rivals / Champions / Live Events</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Min. Semi-Pro</t>
+        </is>
+      </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
           <t>description_line_with_backward_title</t>
@@ -7216,42 +7284,42 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G011</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 squad battles||3 of 5 objectives</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/||score at least 1 goal in 15 separate matches in squad battles on min. semi-pro difficulty (or live events/rivals/champions).||score in 15</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -7262,76 +7330,68 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>3 of 5 Objectives</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 10 times.</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Squad Battles matches on Min. Semi-Pro difficulty.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 10 times.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>2,000 SP / 250 SP</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>1x 5x 84+ Rare Gold Players Pack / 1x 3x 86+ Rare Gold Players Pack / 1x 100 Rare Gold Players Pack / 4X 81+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 squad battles matches on min. semi-pro difficulty.||3 of 5 objectives</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 10 times.||complete the glory hunters crafting upgrade sbc 10 times.</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -7342,72 +7402,68 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rivals</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 15 times.</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rivals</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 15 times.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>2,000 SP / 250 SP</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>Rivals</t>
-        </is>
-      </c>
+          <t>4X 81+ Rare Gold Players Pack / 4X 82+ Rare Gold Players Pack / 7X 81+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 rivals||play 5 rivals</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 15 times.||complete the glory hunters crafting upgrade sbc 15 times.</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -7418,72 +7474,68 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in Rivals.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 20 times.</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in Rivals.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 20 times.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>Rivals</t>
-        </is>
-      </c>
+          <t>4X 82+ Rare Gold Players Pack / 7X 81+ Rare Gold Players Pack / 5X 82+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 matches in rivals.||play 5 matches in rivals.</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 20 times.||complete the glory hunters crafting upgrade sbc 20 times.</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
@@ -7494,72 +7546,68 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Champions</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 25 times.</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Champions</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 25 times.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Champions</t>
-        </is>
-      </c>
+          <t>7X 81+ Rare Gold Players Pack / 5X 82+ Rare Gold Players Pack / 4X 83+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 champions||play 5 champions</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 25 times.||complete the glory hunters crafting upgrade sbc 25 times.</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
@@ -7570,72 +7618,68 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in Champions.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 30 times.</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in Champions.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 30 times.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>Champions</t>
-        </is>
-      </c>
+          <t>5X 82+ Rare Gold Players Pack / 4X 83+ Rare Gold Players Pack / 1 Of 2 86+ Rare Gold Players</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 matches in champions.||play 5 matches in champions.</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 30 times.||complete the glory hunters crafting upgrade sbc 30 times.</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
@@ -7646,72 +7690,68 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rush</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 35 times.</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Rush</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 35 times.</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>4X 83+ Rare Gold Players Pack / 1 Of 2 86+ Rare Gold Players / 5X 83+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 rush||play 5 rush</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 35 times.||complete the glory hunters crafting upgrade sbc 35 times.</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
@@ -7722,72 +7762,68 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Ultimate Team Rush matches.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 40 times.</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Ultimate Team Rush matches.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 40 times.</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
+          <t>1 Of 2 86+ Rare Gold Players / 5X 83+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr"/>
       <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 ultimate team rush matches.||play 5 ultimate team rush matches.</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 40 times.||complete the glory hunters crafting upgrade sbc 40 times.</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
@@ -7798,72 +7834,68 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Live Events</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 45 times.</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Play 5 Live Events</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 45 times.</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>Live Events</t>
-        </is>
-      </c>
+          <t>5X 83+ Rare Gold Players Pack / 2X 85+ Rare Gold Players Pack / 7X 83+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 live events||play 5 live events</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 45 times.||complete the glory hunters crafting upgrade sbc 45 times.</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
@@ -7874,72 +7906,68 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in any Ultimate Team Live Event.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 50 times.</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Play 5 matches in any Ultimate Team Live Event.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 50 times.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>250 SP</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>Live Events / Any Ultimate Team mode</t>
-        </is>
-      </c>
+          <t>2X 85+ Rare Gold Players Pack / 7X 83+ Rare Gold Players Pack / 1 Of 3 86+ Rare Gold Players</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>G010</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/||play 5 matches in any ultimate team live event.||play 5 matches in any ultimate team live event.</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 50 times.||complete the glory hunters crafting upgrade sbc 50 times.</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -7950,76 +7978,68 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Play 10</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 60 times.</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events).</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 60 times.</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Buy 10 Player Items on the Transfer Market. / 450 SP</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>7X 83+ Rare Gold Players Pack / 1 Of 3 86+ Rare Gold Players / 4X 84+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/||play 10 matches in squad battles on min. semi-pro difficulty (or rush/rivals/champions/live events).||play 10</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 60 times.||complete the glory hunters crafting upgrade sbc 60 times.</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
@@ -8030,76 +8050,68 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Win 10</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 70 times.</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events).</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 70 times.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>450 SP</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>Squad Battles / Rivals / Champions / Live Events / Rush</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>Min. Semi-Pro</t>
-        </is>
-      </c>
+          <t>1 Of 3 86+ Rare Gold Players / 4X 84+ Rare Gold Players Pack / 3X 85+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/||win 10 matches in squad battles on min. semi-pro difficulty (or rush/rivals/champions/live events).||win 10</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 70 times.||complete the glory hunters crafting upgrade sbc 70 times.</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
@@ -8110,72 +8122,68 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Score 10</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 80 times.</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Score 10 goals in any Ultimate Team game mode using a player from Mexico.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 80 times.</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>450 SP</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>Any Ultimate Team mode</t>
-        </is>
-      </c>
+          <t>4X 84+ Rare Gold Players Pack / 3X 85+ Rare Gold Players Pack / 5X 84+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>G011</t>
+          <t>G012</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/||score 10 goals in any ultimate team game mode using a player from mexico.||score 10</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 80 times.||complete the glory hunters crafting upgrade sbc 80 times.</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
@@ -8186,32 +8194,28 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 90 times.</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Play 1 match in any Ultimate Team game mode and earn SP!</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 90 times.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>225 SP / 75 SP</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>Any Ultimate Team mode</t>
-        </is>
-      </c>
+          <t>3X 85+ Rare Gold Players Pack / 5X 84+ Rare Gold Players Pack / 3X 86+ Rare Gold Players Pack</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -8221,37 +8225,37 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/||play 1 match in any ultimate team game mode and earn sp!||play 1</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 90 times.||complete the glory hunters crafting upgrade sbc 90 times.</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
@@ -8262,28 +8266,28 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 95 times.</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Score 2 goals</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 95 times.</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>225 SP / 75 SP</t>
+          <t>5X 84+ Rare Gold Players Pack / 3X 86+ Rare Gold Players Pack / 1 Of 3 88+ Rare Gold Players</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr"/>
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -8293,37 +8297,37 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/||score 2 goals||play 1</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 95 times.||complete the glory hunters crafting upgrade sbc 95 times.</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
@@ -8334,32 +8338,28 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Play 1</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 100 times.</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Score 2 goals in any Ultimate Team game mode.</t>
+          <t>Complete the Glory Hunters Crafting Upgrade SBC 100 times.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>75 SP</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>Any Ultimate Team mode</t>
-        </is>
-      </c>
+          <t>3X 86+ Rare Gold Players Pack / 1 Of 3 88+ Rare Gold Players</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
       <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>description_line_with_backward_title</t>
+          <t>action_line_fallback</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
@@ -8369,37 +8369,37 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/||score 2 goals in any ultimate team game mode.||play 1</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/||complete the glory hunters crafting upgrade sbc 100 times.||complete the glory hunters crafting upgrade sbc 100 times.</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -20424,168 +20424,180 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock</t>
+          <t>NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17%</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 7 days 5 Objectives 36% 64%</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz</t>
+          <t>NEW Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 5 days 8 of 10 Objectives 68% 32%</t>
+          <t>NEW Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 7 days 2,000 total 3 of 5 Objectives 76% 24%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
+          <t>https://www.fut.gg/objectives/seasonal/981-weekly-objectives/</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick</t>
+          <t>NEW Weekly Objectives Complete weekly Objectives to earn SP! 750 SP</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 5 days 5 Objectives 77% 23%</t>
+          <t>NEW Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 7 days 3,000 total 5 Objectives 75% 25%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7/7 02:00</t>
+          <t>7/10 02:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07T02:00+09:00</t>
+          <t>2026-07-10T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
+          <t>https://www.fut.gg/objectives/seasonal/951-daily-objectives/</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Milestone</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+</t>
+          <t>NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12%</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 7 days 300 total 2 Objectives 69% 31%</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Expires in 7 days</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7/10 02:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10T02:00+09:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
+          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Live Events</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens</t>
+          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 2 days 9 Objectives 96% 4%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 2 days</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7/4 02:00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-04T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -20595,249 +20607,237 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack</t>
+          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 2 days 6 Objectives 81% 19%</t>
+          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 4 days 8 of 10 Objectives 69% 31%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP</t>
+          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 2 days 2,000 total 4 Objectives 93% 7%</t>
+          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 4 days 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7/4 02:00</t>
+          <t>7/7 02:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04T02:00+09:00</t>
+          <t>2026-07-07T02:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Milestone</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack</t>
+          <t>Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 22 days 15 Objectives 41% 59%</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Expires in 22 days</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>7/24 02:00</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24T02:00+09:00</t>
-        </is>
-      </c>
+          <t>Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12%</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens</t>
+          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 37% 63%</t>
+          <t>Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 23 hours 9 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Live Events</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP</t>
+          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 81% 19%</t>
+          <t>Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 23 hours 6 Objectives 81% 19%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP</t>
+          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 22 hours 3,000 total 5 Objectives 77% 23%</t>
+          <t>Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 23 hours 2,000 total 4 Objectives 93% 7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 23 hours</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/4 01:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-04T01:00+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP</t>
+          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 22 hours 225 total 2 Objectives 79% 21%</t>
+          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 21 days 15 Objectives 41% 59%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 22 hours</t>
+          <t>Expires in 21 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7/3 00:00</t>
+          <t>7/24 02:00</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T00:00+09:00</t>
+          <t>2026-07-24T02:00+09:00</t>
         </is>
       </c>
     </row>
@@ -20859,12 +20859,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 8 days 3,000 total 5 Objectives 95% 5%</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 7 days 3,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 8 days 2,000 total 3 Objectives 85% 15%</t>
+          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 7 days 2,000 total 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -20933,12 +20933,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 8 days 7 Objectives 83% 17%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 7 days 7 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -20970,12 +20970,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 8 days 1 Objectives 92% 8%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 7 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -21007,12 +21007,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 8 days 5 Objectives 86% 14%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 7 days 5 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -21044,12 +21044,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 8 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 7 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Expires in 8 days</t>
+          <t>Expires in 7 days</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -21991,17 +21991,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Drive or Park the bus? - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
+          <t>https://www.fut.gg/objectives/campaigns/969-weekly-rush-points/</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! NEW Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 7 days 5 Objectives 36% 64% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22013,17 +22013,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
+          <t>Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
+          <t>https://www.fut.gg/objectives/seasonal/974-season-8-weekly-play-5/</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 5 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! NEW Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 7 days 2,000 total 3 of 5 Objectives 76% 24% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22035,17 +22035,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
+          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
+          <t>https://www.fut.gg/objectives/seasonal/981-weekly-objectives/</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 5 days 5 Objectives 77% 23% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! NEW Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 7 days 3,000 total 5 Objectives 75% 25% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22057,17 +22057,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
+          <t>https://www.fut.gg/objectives/seasonal/951-daily-objectives/</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! NEW Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 7 days 300 total 2 Objectives 69% 31% Rewards 300 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 100 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 100 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22079,17 +22079,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
+          <t>Drive or Park the bus? - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
+          <t>https://www.fut.gg/objectives/milestones/1042-drive-or-park-the-bus/</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 2 days 9 Objectives 96% 4% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22101,17 +22101,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
+          <t>https://www.fut.gg/objectives/live-events/1034-festival-of-football-gauntlet-2/</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 2 days 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 4 days 8 of 10 Objectives 69% 31% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22123,17 +22123,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
+          <t>Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
+          <t>https://www.fut.gg/objectives/live-events/1035-festival-of-football-gauntlet-2-bonus/</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 2 days 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 4 days 5 Objectives 77% 23% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22145,17 +22145,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
+          <t>Chase the Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
+          <t>https://www.fut.gg/objectives/milestones/1031-chase-the-glory/</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 22 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Chase the Glory Chase the Glory - EA SPORTS FC 26 Objectives Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. Chase the Glory Complete the Chase the Glory challenges to earn Evolution Consumables! All rewards untradeable. GH 4th Finesse Shot+ GH 4th Intercept+ 4 Objectives 88% 12% Rewards GH 4th Finesse Shot+ GH 4th Intercept+ GH 4th Pinged Pass+ GH 4th Incisive Pass+ GH 4th Anticipate+ GH 4th Bruiser+ GH 4th Rapid+ GH 4th Quick Step+ GH 4th Technical+ GH 4th Low Driven Shot+ Assist in 10 Assist 1 goal in 10 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Pinged Pass+ GH 4th Incisive Pass+ Defiant Defender Concede 3 goals or less in 15 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Anticipate+ GH 4th Bruiser+ Win in 30 Win in 30 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Rapid+ GH 4th Quick Step+ Score in 50 Score in 50 separate matches with min. 3 Glory Hunters in your starting 11 in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). GH 4th Technical+ GH 4th Low Driven Shot+ © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22167,17 +22167,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points - EA SPORTS FC 26 Objectives</t>
+          <t>Moment of Glory - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/campaigns/968-weekly-rush-points/</t>
+          <t>https://www.fut.gg/objectives/live-events/1033-moment-of-glory/</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 22 hours 5 Objectives 37% 63% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Moment of Glory Moment of Glory - EA SPORTS FC 26 Objectives Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. Moment of Glory Compete in the Moment of Glory Live Event and earn exclusive rewards! All rewards untradeable. 7X 87+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick 150 Tokens Expires in 23 hours 9 Objectives 95% 5% Rewards Anticipate+ Given the Keys 5000 Coins 2 Of 8 Playstyle+ Pick Award 2 Of 8 Playstyle+ Pick 150 Tokens 2x 3x 85+ Rare Gold Players Pack 2x 3x 86+ Rare Gold Players Pack 1x 7x 87+ Rare Gold Players Pack Score 1 Score 1 goal in the Moment of Glory Live Event. 5000 Coins Score 5 Score 5 goals in the Moment of Glory Live Event. 2 Of 8 Playstyle+ Pick Score 10 Score 10 goals in the Moment of Glory Live Event. Award Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Asia and Oceania in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Africa in your starting 11. 3X 85+ Rare Gold Players Pack Score in 3 Score at least 1 goal in 3 separate matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. Anticipate+ Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from Europe in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from South America in your starting 11. 3X 86+ Rare Gold Players Pack Win 3 Win 3 matches in the Moment of Glory Live Event while having min. 6 players from North America in your starting 11. Given the Keys © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22189,17 +22189,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives</t>
+          <t>Journey of Nations South America - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/975-season-8-weekly-play-4/</t>
+          <t>https://www.fut.gg/objectives/live-events/1043-journey-of-nations-south-america/</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 4 Season 8 Weekly Play 4 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 4 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 22 hours 2,000 total 3 of 5 Objectives 81% 19% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations South America Journey of Nations South America - EA SPORTS FC 26 Objectives Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations South America Compete in the Journey of Nations South America Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 23 hours 6 Objectives 81% 19% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations South America Live Event. Hunter Win 1 Win 1 match in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations South America Live Event Shadow Win 2 Win 2 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations South America Live Event Award Win 3 Win 3 matches in the Journey of Nations South America Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22211,17 +22211,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Week 1 - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/954-weekly-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1032-glory-hunters-week-1/</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 22 hours 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 1 Glory Hunters Week 1 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and SP. Glory Hunters Week 1 Complete all the challenges to earn Festival of Football Tokens and SP. 40 Tokens 800 SP Expires in 23 hours 2,000 total 4 Objectives 93% 7% Rewards 2,000 SP 30 Tokens 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 5 Score at least 1 goal in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP Play 10 Play 10 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 300 SP Score in 15 Score at least 1 goal in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens 300 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22233,17 +22233,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives - EA SPORTS FC 26 Objectives</t>
+          <t>Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/objectives/seasonal/950-daily-objectives/</t>
+          <t>https://www.fut.gg/objectives/campaigns/1040-glory-hunters-crafting-upgrade-completionist/</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 75 SP Expires in 22 hours 225 total 2 Objectives 79% 21% Rewards 225 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 75 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 75 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 21 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 8 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 7 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22287,7 +22287,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 8 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 7 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 8 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 7 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 8 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 7 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22353,7 +22353,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 8 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 7 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -22375,7 +22375,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 8 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 7 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 03:03:20</t>
+          <t>2026-07-06 03:02:18</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 02:00:00</t>
+          <t>2026-07-06 02:00:00</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Bonus Completionist Knockout Glory 2 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. NEW Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 6 days 4 Objectives 60% 40% Rewards 50 Tokens 2 Of 8 Playstyle+ Pick Evo Unlock 1 Of 2 86+ Rare Gold Players Evo Unlock 1x 6x 83+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 2 Tournament. 50 Tokens 2 Of 8 Playstyle+ Pick Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 2 Tournament. Evo Unlock Win Semi-Finals Win the Semi-Finals in the Knockout Glory 2 Tournament. 6X 83+ Rare Gold Players Pack Win the Final Win the Knockout Glory 2 Tournament. 1 Of 2 86+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Bonus Completionist Knockout Glory 2 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 5 days 4 Objectives 67% 33% Rewards 50 Tokens 2 Of 8 Playstyle+ Pick Evo Unlock 1 Of 2 86+ Rare Gold Players Evo Unlock 1x 6x 83+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 2 Tournament. 50 Tokens 2 Of 8 Playstyle+ Pick Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 2 Tournament. Evo Unlock Win Semi-Finals Win the Semi-Finals in the Knockout Glory 2 Tournament. 6X 83+ Rare Gold Players Pack Win the Final Win the Knockout Glory 2 Tournament. 1 Of 2 86+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Tournament Knockout Glory 2 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. NEW Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 6 days 3 of 4 Objectives 68% 32% Rewards 2 Of 8 Playstyle+ Pick Evo Unlock 2 Of 8 Playstyle+ Pick 100 Tokens Evo Unlock 1x 3x 83+ Rare Gold Players Pack 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 2 Tournament. 3X 83+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 2 Tournament. Evo Unlock 2 Of 8 Playstyle+ Pick Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Tournament Knockout Glory 2 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 5 days 3 of 4 Objectives 71% 29% Rewards 2 Of 8 Playstyle+ Pick Evo Unlock 2 Of 8 Playstyle+ Pick 100 Tokens Evo Unlock 1x 3x 83+ Rare Gold Players Pack 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 2 Tournament. 3X 83+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 2 Tournament. Evo Unlock 2 Of 8 Playstyle+ Pick Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Switch it Up! Switch it Up! - EA SPORTS FC 26 Objectives Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. NEW Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 6 days 3 of 4 Objectives 74% 26% Rewards 5000 Coins 5000 Coins 5000 Coins 5000 Coins Evo Unlock 3 Back Swag Score at least 1 goal in 5 separate matches using the 3-5-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Back to Basics Score at least 1 goal in 5 separate matches using the 4-4-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins The Other 4-5-1 Score at least 1 goal in 5 separate matches using the 4-5-1 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Try Something New! Score at least 1 goal in 50 separate matches using the 4-4-1-1(2) formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Switch it Up! Switch it Up! - EA SPORTS FC 26 Objectives Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 5 days 3 of 4 Objectives 78% 22% Rewards 5000 Coins 5000 Coins 5000 Coins 5000 Coins Evo Unlock 3 Back Swag Score at least 1 goal in 5 separate matches using the 3-5-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Back to Basics Score at least 1 goal in 5 separate matches using the 4-4-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins The Other 4-5-1 Score at least 1 goal in 5 separate matches using the 4-5-1 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Try Something New! Score at least 1 goal in 50 separate matches using the 4-4-1-1(2) formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Europe Journey of Nations Europe - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 82% 18% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Europe Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Europe Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Europe Live Event. Award Win 3 Win 3 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Europe Journey of Nations Europe - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 5 days 6 Objectives 82% 18% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Europe Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Europe Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Europe Live Event. Award Win 3 Win 3 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Bonus Completionist Knockout Glory 1 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 6 days 4 Objectives 74% 26% Rewards Pinged Pass+ 50 Tokens Evo Unlock 1x 5x 84+ Rare Gold Players Pack 1x 8x 85+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 1 Tournament. 50 Tokens Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 1 Tournament. Pinged Pass+ Win Semi-Finals Win the Semi-Finals in the Knockout Glory 1 Tournament. Evo Unlock Win the Final Win the Knockout Glory 1 Tournament. 5X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Bonus Completionist Knockout Glory 1 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 5 days 4 Objectives 72% 28% Rewards Pinged Pass+ 50 Tokens Evo Unlock 1x 5x 84+ Rare Gold Players Pack 1x 8x 85+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 1 Tournament. 50 Tokens Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 1 Tournament. Pinged Pass+ Win Semi-Finals Win the Semi-Finals in the Knockout Glory 1 Tournament. Evo Unlock Win the Final Win the Knockout Glory 1 Tournament. 5X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Tournament Knockout Glory 1 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 6 days 3 of 4 Objectives 86% 14% Rewards 10 Creating Space Evo Unlock 100 Tokens 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 1 Tournament. Evo Unlock Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 1 Tournament. 10 Antoine Semenyo (Loan) Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Tournament Knockout Glory 1 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 5 days 3 of 4 Objectives 84% 16% Rewards 10 Creating Space Evo Unlock 100 Tokens 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 1 Tournament. Evo Unlock Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 1 Tournament. 10 Antoine Semenyo (Loan) Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory Bonus Completionist Knockout Glory Bonus Completionist - EA SPORTS FC 26 Objectives Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 6 days 2 Objectives 88% 12% Rewards 1 Of 3 89+ Rare Gold Player Pick 1x 7x 86+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Knockout Glory 1 Complete the Knockout Glory 1 Bonus Objective. 7X 86+ Rare Gold Players Pack Knockout Glory 2 Complete the Knockout Glory 2 Bonus Objective. 5X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory Bonus Completionist Knockout Glory Bonus Completionist - EA SPORTS FC 26 Objectives Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 5 days 2 Objectives 88% 12% Rewards 1 Of 3 89+ Rare Gold Player Pick 1x 7x 86+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Knockout Glory 1 Complete the Knockout Glory 1 Bonus Objective. 7X 86+ Rare Gold Players Pack Knockout Glory 2 Complete the Knockout Glory 2 Bonus Objective. 5X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 2 Glory Hunters Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 6 days 4 Objectives 92% 8% Rewards Consumable 30 Tokens Shadow 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Consumable Score in 5 Score in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens Scoring Striker Score with a ST in 10 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Shadow Assist in 15 Assist in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 2 Glory Hunters Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 5 days 4 Objectives 89% 11% Rewards Consumable 30 Tokens Shadow 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Consumable Score in 5 Score in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens Scoring Striker Score with a ST in 10 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Shadow Assist in 15 Assist in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Festival of Football SP Chase Festival of Football SP Chase - EA SPORTS FC 26 Objectives Complete challenges across Ultimate Team to earn SP! Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 5 days 7,000 total 5 Objectives 89% 11% Rewards 7,000 SP Score 5 Score 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Assist 5 Assist 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Play 10 Play 10 Rivals matches. 750 SP Complete 7 Complete any 7 SBC groups. 750 SP Play 15 Play 15 matches in any Ultimate Team game mode. 750 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Festival of Football SP Chase Festival of Football SP Chase - EA SPORTS FC 26 Objectives Complete challenges across Ultimate Team to earn SP! Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 4 days 7,000 total 5 Objectives 89% 11% Rewards 7,000 SP Score 5 Score 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Assist 5 Assist 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Play 10 Play 10 Rivals matches. 750 SP Complete 7 Complete any 7 SBC groups. 750 SP Play 15 Play 15 matches in any Ultimate Team game mode. 750 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 31% 69% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 4 days 5 Objectives 32% 68% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 77% 23% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 4 days 2,000 total 3 of 5 Objectives 77% 23% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 5 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 4 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 5 days 300 total 2 Objectives 71% 29% Rewards 300 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 100 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 100 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 4 days 300 total 2 Objectives 71% 29% Rewards 300 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 100 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 100 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1357,7 +1357,7 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 84% 16% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 2 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 23 hours 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 2 days 5 Objectives 77% 23% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 23 hours 5 Objectives 76% 24% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 19 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 18 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 5 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 4 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 5 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 4 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 5 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 4 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 5 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 4 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 5 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 4 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 5 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 4 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M101" s="3" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M102" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="L103" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M103" s="3" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="M104" s="3" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M106" s="3" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M107" s="3" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M108" s="3" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M109" s="3" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M110" s="3" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -22840,17 +22840,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NEW Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock</t>
+          <t>Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NEW Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 6 days 4 Objectives 60% 40%</t>
+          <t>Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 5 days 4 Objectives 67% 33%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -22877,17 +22877,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NEW Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock</t>
+          <t>Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NEW Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 6 days 3 of 4 Objectives 68% 32%</t>
+          <t>Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 5 days 3 of 4 Objectives 71% 29%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -22914,17 +22914,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NEW Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock</t>
+          <t>Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NEW Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 6 days 3 of 4 Objectives 74% 26%</t>
+          <t>Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 5 days 3 of 4 Objectives 78% 22%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -22981,12 +22981,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 82% 18%</t>
+          <t>Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 5 days 6 Objectives 82% 18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -23018,12 +23018,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 6 days 4 Objectives 74% 26%</t>
+          <t>Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 5 days 4 Objectives 72% 28%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -23055,12 +23055,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 6 days 3 of 4 Objectives 86% 14%</t>
+          <t>Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 5 days 3 of 4 Objectives 84% 16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -23092,12 +23092,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 6 days 2 Objectives 88% 12%</t>
+          <t>Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 5 days 2 Objectives 88% 12%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -23129,12 +23129,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 6 days 4 Objectives 92% 8%</t>
+          <t>Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 5 days 4 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 6 days</t>
+          <t>Expires in 5 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -23166,12 +23166,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 5 days 7,000 total 5 Objectives 89% 11%</t>
+          <t>Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 4 days 7,000 total 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -23203,12 +23203,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 31% 69%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 4 days 5 Objectives 32% 68%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -23240,12 +23240,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 77% 23%</t>
+          <t>Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 4 days 2,000 total 3 of 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -23277,12 +23277,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 5 days 3,000 total 5 Objectives 77% 23%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 4 days 3,000 total 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -23314,12 +23314,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 5 days 300 total 2 Objectives 71% 29%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 4 days 300 total 2 Objectives 71% 29%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17%</t>
+          <t>Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 84% 16%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -23376,12 +23376,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 2 days 8 of 10 Objectives 68% 32%</t>
+          <t>Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 24 hours 8 of 10 Objectives 68% 32%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -23413,12 +23413,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 2 days 5 Objectives 77% 23%</t>
+          <t>Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 24 hours 5 Objectives 76% 24%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Expires in 2 days</t>
+          <t>Expires in 24 hours</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -23475,12 +23475,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 19 days 15 Objectives 41% 59%</t>
+          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 18 days 15 Objectives 41% 59%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Expires in 19 days</t>
+          <t>Expires in 18 days</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -23512,12 +23512,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 5 days 3,000 total 5 Objectives 95% 5%</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 4 days 3,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 5 days 2,000 total 3 Objectives 85% 15%</t>
+          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 4 days 2,000 total 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 5 days 7 Objectives 83% 17%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 4 days 7 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -23623,12 +23623,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 5 days 1 Objectives 92% 8%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 4 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -23660,12 +23660,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 5 days 5 Objectives 86% 14%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 4 days 5 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -23697,12 +23697,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 5 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 4 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Expires in 5 days</t>
+          <t>Expires in 4 days</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Bonus Completionist Knockout Glory 2 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. NEW Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 6 days 4 Objectives 60% 40% Rewards 50 Tokens 2 Of 8 Playstyle+ Pick Evo Unlock 1 Of 2 86+ Rare Gold Players Evo Unlock 1x 6x 83+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 2 Tournament. 50 Tokens 2 Of 8 Playstyle+ Pick Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 2 Tournament. Evo Unlock Win Semi-Finals Win the Semi-Finals in the Knockout Glory 2 Tournament. 6X 83+ Rare Gold Players Pack Win the Final Win the Knockout Glory 2 Tournament. 1 Of 2 86+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Bonus Completionist Knockout Glory 2 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 5 days 4 Objectives 67% 33% Rewards 50 Tokens 2 Of 8 Playstyle+ Pick Evo Unlock 1 Of 2 86+ Rare Gold Players Evo Unlock 1x 6x 83+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 2 Tournament. 50 Tokens 2 Of 8 Playstyle+ Pick Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 2 Tournament. Evo Unlock Win Semi-Finals Win the Semi-Finals in the Knockout Glory 2 Tournament. 6X 83+ Rare Gold Players Pack Win the Final Win the Knockout Glory 2 Tournament. 1 Of 2 86+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24676,7 +24676,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Tournament Knockout Glory 2 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. NEW Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 6 days 3 of 4 Objectives 68% 32% Rewards 2 Of 8 Playstyle+ Pick Evo Unlock 2 Of 8 Playstyle+ Pick 100 Tokens Evo Unlock 1x 3x 83+ Rare Gold Players Pack 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 2 Tournament. 3X 83+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 2 Tournament. Evo Unlock 2 Of 8 Playstyle+ Pick Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Tournament Knockout Glory 2 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 5 days 3 of 4 Objectives 71% 29% Rewards 2 Of 8 Playstyle+ Pick Evo Unlock 2 Of 8 Playstyle+ Pick 100 Tokens Evo Unlock 1x 3x 83+ Rare Gold Players Pack 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 2 Tournament. 3X 83+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 2 Tournament. Evo Unlock 2 Of 8 Playstyle+ Pick Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24698,7 +24698,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Switch it Up! Switch it Up! - EA SPORTS FC 26 Objectives Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. NEW Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 6 days 3 of 4 Objectives 74% 26% Rewards 5000 Coins 5000 Coins 5000 Coins 5000 Coins Evo Unlock 3 Back Swag Score at least 1 goal in 5 separate matches using the 3-5-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Back to Basics Score at least 1 goal in 5 separate matches using the 4-4-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins The Other 4-5-1 Score at least 1 goal in 5 separate matches using the 4-5-1 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Try Something New! Score at least 1 goal in 50 separate matches using the 4-4-1-1(2) formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Switch it Up! Switch it Up! - EA SPORTS FC 26 Objectives Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 5 days 3 of 4 Objectives 78% 22% Rewards 5000 Coins 5000 Coins 5000 Coins 5000 Coins Evo Unlock 3 Back Swag Score at least 1 goal in 5 separate matches using the 3-5-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Back to Basics Score at least 1 goal in 5 separate matches using the 4-4-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins The Other 4-5-1 Score at least 1 goal in 5 separate matches using the 4-5-1 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Try Something New! Score at least 1 goal in 50 separate matches using the 4-4-1-1(2) formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24742,7 +24742,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Europe Journey of Nations Europe - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 6 days 6 Objectives 82% 18% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Europe Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Europe Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Europe Live Event. Award Win 3 Win 3 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Europe Journey of Nations Europe - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 5 days 6 Objectives 82% 18% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Europe Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Europe Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Europe Live Event. Award Win 3 Win 3 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24764,7 +24764,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Bonus Completionist Knockout Glory 1 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 6 days 4 Objectives 74% 26% Rewards Pinged Pass+ 50 Tokens Evo Unlock 1x 5x 84+ Rare Gold Players Pack 1x 8x 85+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 1 Tournament. 50 Tokens Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 1 Tournament. Pinged Pass+ Win Semi-Finals Win the Semi-Finals in the Knockout Glory 1 Tournament. Evo Unlock Win the Final Win the Knockout Glory 1 Tournament. 5X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Bonus Completionist Knockout Glory 1 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 5 days 4 Objectives 72% 28% Rewards Pinged Pass+ 50 Tokens Evo Unlock 1x 5x 84+ Rare Gold Players Pack 1x 8x 85+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 1 Tournament. 50 Tokens Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 1 Tournament. Pinged Pass+ Win Semi-Finals Win the Semi-Finals in the Knockout Glory 1 Tournament. Evo Unlock Win the Final Win the Knockout Glory 1 Tournament. 5X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24786,7 +24786,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Tournament Knockout Glory 1 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 6 days 3 of 4 Objectives 86% 14% Rewards 10 Creating Space Evo Unlock 100 Tokens 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 1 Tournament. Evo Unlock Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 1 Tournament. 10 Antoine Semenyo (Loan) Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Tournament Knockout Glory 1 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 5 days 3 of 4 Objectives 84% 16% Rewards 10 Creating Space Evo Unlock 100 Tokens 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 1 Tournament. Evo Unlock Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 1 Tournament. 10 Antoine Semenyo (Loan) Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory Bonus Completionist Knockout Glory Bonus Completionist - EA SPORTS FC 26 Objectives Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 6 days 2 Objectives 88% 12% Rewards 1 Of 3 89+ Rare Gold Player Pick 1x 7x 86+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Knockout Glory 1 Complete the Knockout Glory 1 Bonus Objective. 7X 86+ Rare Gold Players Pack Knockout Glory 2 Complete the Knockout Glory 2 Bonus Objective. 5X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory Bonus Completionist Knockout Glory Bonus Completionist - EA SPORTS FC 26 Objectives Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 5 days 2 Objectives 88% 12% Rewards 1 Of 3 89+ Rare Gold Player Pick 1x 7x 86+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Knockout Glory 1 Complete the Knockout Glory 1 Bonus Objective. 7X 86+ Rare Gold Players Pack Knockout Glory 2 Complete the Knockout Glory 2 Bonus Objective. 5X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24830,7 +24830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 2 Glory Hunters Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 6 days 4 Objectives 92% 8% Rewards Consumable 30 Tokens Shadow 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Consumable Score in 5 Score in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens Scoring Striker Score with a ST in 10 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Shadow Assist in 15 Assist in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 2 Glory Hunters Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 5 days 4 Objectives 89% 11% Rewards Consumable 30 Tokens Shadow 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Consumable Score in 5 Score in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens Scoring Striker Score with a ST in 10 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Shadow Assist in 15 Assist in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24852,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Festival of Football SP Chase Festival of Football SP Chase - EA SPORTS FC 26 Objectives Complete challenges across Ultimate Team to earn SP! Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 5 days 7,000 total 5 Objectives 89% 11% Rewards 7,000 SP Score 5 Score 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Assist 5 Assist 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Play 10 Play 10 Rivals matches. 750 SP Complete 7 Complete any 7 SBC groups. 750 SP Play 15 Play 15 matches in any Ultimate Team game mode. 750 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Festival of Football SP Chase Festival of Football SP Chase - EA SPORTS FC 26 Objectives Complete challenges across Ultimate Team to earn SP! Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 4 days 7,000 total 5 Objectives 89% 11% Rewards 7,000 SP Score 5 Score 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Assist 5 Assist 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Play 10 Play 10 Rivals matches. 750 SP Complete 7 Complete any 7 SBC groups. 750 SP Play 15 Play 15 matches in any Ultimate Team game mode. 750 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 5 days 5 Objectives 31% 69% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 4 days 5 Objectives 32% 68% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24896,7 +24896,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 5 days 2,000 total 3 of 5 Objectives 77% 23% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 4 days 2,000 total 3 of 5 Objectives 77% 23% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24918,7 +24918,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 5 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 4 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24940,7 +24940,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 5 days 300 total 2 Objectives 71% 29% Rewards 300 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 100 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 100 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 4 days 300 total 2 Objectives 71% 29% Rewards 300 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 100 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 100 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24962,7 +24962,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 83% 17% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Milestones &gt; Drive or Park the bus? Drive or Park the bus? - EA SPORTS FC 26 Objectives Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Drive or Park the bus? Choose your style of play and complete 1 of 2 challenges to earn Coins and an Evolution! All rewards are untradeable. Evo Unlock 1 of 2 Objectives 84% 16% Rewards 10000 Coins 10000 Coins Evo Unlock Goals Galore Score 3 goals or more and win in 60 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins Tough to Beat Concede 1 goal or less and win in 30 separate matches in Champions, Rivals, Live Events or Squad Battles. 10000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 2 days 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Festival of Football Gauntlet 2 - EA SPORTS FC 26 Objectives Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Festival of Football Gauntlet 2 Complete 8 of 10 challenges in the Festival of Football Gauntlet 2 and earn big rewards! All rewards untradeable. Kai Havertz Expires in 23 hours 8 of 10 Objectives 68% 32% Rewards 20 Tokens 30 Tokens 25 Tokens Evo Unlock 1x 10x 86+ Rare Gold Players Pack 1x 10x 87+ Rare Gold Players Pack 1x 8x 88+ Rare Gold Players Pack 3x 5x 90+ Rare Gold Players Pack Score 1 Score at least 1 goal in the Festival of Football Gauntlet 2. 20 Tokens Score in 4 Score at least 1 goal in 4 separate matches in the Festival of Football Gauntlet 2. 30 Tokens Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Doubles Win at least 2 matches within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2. Evo Unlock A Pair of Triplets Win at least 3 matches within a single round in the Festival of Football Gauntlet 2, twice. 10X 87+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 8X 88+ Rare Gold Players Pack Perfect Round Complete a Perfect Round in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack Double Perfect Complete a Perfect Round in the Festival of Football Gauntlet 2, twice. 5X 90+ Rare Gold Players Pack Score in 12 Score at least 1 goal in 12 separate matches in the Festival of Football Gauntlet 2. 5X 90+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -25006,7 +25006,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 2 days 5 Objectives 77% 23% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Festival of Football Gauntlet 2 Bonus Festival of Football Gauntlet 2 Bonus - EA SPORTS FC 26 Objectives Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. Festival of Football Gauntlet 2 Bonus Compete in the Festival of Football Gauntlet 2 and earn exclusive rewards! All rewards untradeable. 50 Tokens 2 Of 8 Playstyle+ Pick Expires in 23 hours 5 Objectives 76% 24% Rewards 25 Tokens 50 Tokens 2 Of 8 Playstyle+ Pick 1x 5x 84+ Rare Gold Players Pack 1x 7x 84+ Rare Gold Players Pack 1x 7x 85+ Rare Gold Players Pack 1x 10x 86+ Rare Gold Players Pack Score 2 Score at least 2 goals in the Festival of Football Gauntlet 2. 5X 84+ Rare Gold Players Pack Play 3 Play 3 matches in the Festival of Football Gauntlet 2. 7X 84+ Rare Gold Players Pack Play 8 Play 8 matches in the Festival of Football Gauntlet 2. 7X 85+ Rare Gold Players Pack Score in 8 Score at least 1 goal in 8 separate matches in the Festival of Football Gauntlet 2. 10X 86+ Rare Gold Players Pack A Pair of Ones Win at least 1 match within a single round in the Festival of Football Gauntlet 2, twice. 25 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 19 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 18 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -25072,7 +25072,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 5 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 4 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 5 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 4 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 5 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 4 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -25138,7 +25138,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 5 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 4 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -25160,7 +25160,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 5 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 4 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 5 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 4 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>

--- a/latest_raw/futgg_raw_objectives_latest.xlsx
+++ b/latest_raw/futgg_raw_objectives_latest.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 03:55:37</t>
+          <t>2026-07-08 04:02:02</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 02:00:00</t>
+          <t>2026-07-08 02:00:00</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Bonus Completionist Knockout Glory 2 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 4 days 4 Objectives 67% 33% Rewards 50 Tokens 2 Of 8 Playstyle+ Pick Evo Unlock 1 Of 2 86+ Rare Gold Players Evo Unlock 1x 6x 83+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 2 Tournament. 50 Tokens 2 Of 8 Playstyle+ Pick Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 2 Tournament. Evo Unlock Win Semi-Finals Win the Semi-Finals in the Knockout Glory 2 Tournament. 6X 83+ Rare Gold Players Pack Win the Final Win the Knockout Glory 2 Tournament. 1 Of 2 86+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Bonus Completionist Knockout Glory 2 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 3 days 4 Objectives 67% 33% Rewards 50 Tokens 2 Of 8 Playstyle+ Pick Evo Unlock 1 Of 2 86+ Rare Gold Players Evo Unlock 1x 6x 83+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 2 Tournament. 50 Tokens 2 Of 8 Playstyle+ Pick Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 2 Tournament. Evo Unlock Win Semi-Finals Win the Semi-Finals in the Knockout Glory 2 Tournament. 6X 83+ Rare Gold Players Pack Win the Final Win the Knockout Glory 2 Tournament. 1 Of 2 86+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Tournament Knockout Glory 2 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 4 days 3 of 4 Objectives 73% 27% Rewards 2 Of 8 Playstyle+ Pick Evo Unlock 2 Of 8 Playstyle+ Pick 100 Tokens Evo Unlock 1x 3x 83+ Rare Gold Players Pack 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 2 Tournament. 3X 83+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 2 Tournament. Evo Unlock 2 Of 8 Playstyle+ Pick Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Tournament Knockout Glory 2 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 3 days 3 of 4 Objectives 73% 27% Rewards 2 Of 8 Playstyle+ Pick Evo Unlock 2 Of 8 Playstyle+ Pick 100 Tokens Evo Unlock 1x 3x 83+ Rare Gold Players Pack 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 2 Tournament. 3X 83+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 2 Tournament. Evo Unlock 2 Of 8 Playstyle+ Pick Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Switch it Up! Switch it Up! - EA SPORTS FC 26 Objectives Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 4 days 3 of 4 Objectives 79% 21% Rewards 5000 Coins 5000 Coins 5000 Coins 5000 Coins Evo Unlock 3 Back Swag Score at least 1 goal in 5 separate matches using the 3-5-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Back to Basics Score at least 1 goal in 5 separate matches using the 4-4-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins The Other 4-5-1 Score at least 1 goal in 5 separate matches using the 4-5-1 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Try Something New! Score at least 1 goal in 50 separate matches using the 4-4-1-1(2) formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Switch it Up! Switch it Up! - EA SPORTS FC 26 Objectives Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 3 days 3 of 4 Objectives 79% 21% Rewards 5000 Coins 5000 Coins 5000 Coins 5000 Coins Evo Unlock 3 Back Swag Score at least 1 goal in 5 separate matches using the 3-5-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Back to Basics Score at least 1 goal in 5 separate matches using the 4-4-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins The Other 4-5-1 Score at least 1 goal in 5 separate matches using the 4-5-1 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Try Something New! Score at least 1 goal in 50 separate matches using the 4-4-1-1(2) formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Europe Journey of Nations Europe - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 4 days 6 Objectives 82% 18% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Europe Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Europe Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Europe Live Event. Award Win 3 Win 3 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Europe Journey of Nations Europe - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 80% 20% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Europe Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Europe Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Europe Live Event. Award Win 3 Win 3 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Bonus Completionist Knockout Glory 1 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 4 days 4 Objectives 70% 30% Rewards Pinged Pass+ 50 Tokens Evo Unlock 1x 5x 84+ Rare Gold Players Pack 1x 8x 85+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 1 Tournament. 50 Tokens Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 1 Tournament. Pinged Pass+ Win Semi-Finals Win the Semi-Finals in the Knockout Glory 1 Tournament. Evo Unlock Win the Final Win the Knockout Glory 1 Tournament. 5X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Bonus Completionist Knockout Glory 1 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 3 days 4 Objectives 68% 32% Rewards Pinged Pass+ 50 Tokens Evo Unlock 1x 5x 84+ Rare Gold Players Pack 1x 8x 85+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 1 Tournament. 50 Tokens Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 1 Tournament. Pinged Pass+ Win Semi-Finals Win the Semi-Finals in the Knockout Glory 1 Tournament. Evo Unlock Win the Final Win the Knockout Glory 1 Tournament. 5X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Tournament Knockout Glory 1 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 4 days 3 of 4 Objectives 84% 16% Rewards 10 Creating Space Evo Unlock 100 Tokens 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 1 Tournament. Evo Unlock Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 1 Tournament. 10 Antoine Semenyo (Loan) Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Tournament Knockout Glory 1 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 3 days 3 of 4 Objectives 82% 18% Rewards 10 Creating Space Evo Unlock 100 Tokens 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 1 Tournament. Evo Unlock Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 1 Tournament. 10 Antoine Semenyo (Loan) Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory Bonus Completionist Knockout Glory Bonus Completionist - EA SPORTS FC 26 Objectives Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 4 days 2 Objectives 88% 12% Rewards 1 Of 3 89+ Rare Gold Player Pick 1x 7x 86+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Knockout Glory 1 Complete the Knockout Glory 1 Bonus Objective. 7X 86+ Rare Gold Players Pack Knockout Glory 2 Complete the Knockout Glory 2 Bonus Objective. 5X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory Bonus Completionist Knockout Glory Bonus Completionist - EA SPORTS FC 26 Objectives Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 3 days 2 Objectives 86% 14% Rewards 1 Of 3 89+ Rare Gold Player Pick 1x 7x 86+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Knockout Glory 1 Complete the Knockout Glory 1 Bonus Objective. 7X 86+ Rare Gold Players Pack Knockout Glory 2 Complete the Knockout Glory 2 Bonus Objective. 5X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 2 Glory Hunters Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 4 days 4 Objectives 90% 10% Rewards Consumable 30 Tokens Shadow 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Consumable Score in 5 Score in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens Scoring Striker Score with a ST in 10 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Shadow Assist in 15 Assist in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 2 Glory Hunters Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 3 days 4 Objectives 88% 13% Rewards Consumable 30 Tokens Shadow 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Consumable Score in 5 Score in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens Scoring Striker Score with a ST in 10 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Shadow Assist in 15 Assist in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Festival of Football SP Chase Festival of Football SP Chase - EA SPORTS FC 26 Objectives Complete challenges across Ultimate Team to earn SP! Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 3 days 7,000 total 5 Objectives 89% 11% Rewards 7,000 SP Score 5 Score 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Assist 5 Assist 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Play 10 Play 10 Rivals matches. 750 SP Complete 7 Complete any 7 SBC groups. 750 SP Play 15 Play 15 matches in any Ultimate Team game mode. 750 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Festival of Football SP Chase Festival of Football SP Chase - EA SPORTS FC 26 Objectives Complete challenges across Ultimate Team to earn SP! Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 2 days 7,000 total 5 Objectives 89% 11% Rewards 7,000 SP Score 5 Score 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Assist 5 Assist 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Play 10 Play 10 Rivals matches. 750 SP Complete 7 Complete any 7 SBC groups. 750 SP Play 15 Play 15 matches in any Ultimate Team game mode. 750 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 32% 68% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 31% 69% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 77% 23% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 1 day 2,000 total 3 of 5 Objectives 76% 24% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 3 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 1 day 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 3 days 300 total 2 Objectives 71% 29% Rewards 300 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 100 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 100 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Daily Objectives Daily Objectives - EA SPORTS FC 26 Objectives Play, complete, and earn SP from the daily Objective every 24 hours! Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 1 day 300 total 2 Objectives 71% 29% Rewards 300 SP Play 1 Play 1 match in any Ultimate Team game mode and earn SP! 100 SP Score 2 goals Score 2 goals in any Ultimate Team game mode. 100 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 17 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Crafting Upgrade Completionist Glory Hunters Crafting Upgrade Completionist - EA SPORTS FC 26 Objectives Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 16 days 15 Objectives 41% 59% Rewards 1 Of 2 86+ Rare Gold Players 1 Of 3 86+ Rare Gold Players 1 Of 3 88+ Rare Gold Players 1x 4x 81+ Rare Gold Players Pack 1x 4x 82+ Rare Gold Players Pack 1x 7x 81+ Rare Gold Players Pack 1x 5x 82+ Rare Gold Players Pack 1x 4x 83+ Rare Gold Players Pack 1x 5x 83+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 7x 83+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 5x 84+ Rare Gold Players Pack 1x 3x 86+ Rare Gold Players Pack 1x 100 Rare Gold Players Pack 10 Completions Complete the Glory Hunters Crafting Upgrade SBC 10 times. 4X 81+ Rare Gold Players Pack 15 Completions Complete the Glory Hunters Crafting Upgrade SBC 15 times. 4X 82+ Rare Gold Players Pack 20 Completions Complete the Glory Hunters Crafting Upgrade SBC 20 times. 7X 81+ Rare Gold Players Pack 25 Completions Complete the Glory Hunters Crafting Upgrade SBC 25 times. 5X 82+ Rare Gold Players Pack 30 Completions Complete the Glory Hunters Crafting Upgrade SBC 30 times. 4X 83+ Rare Gold Players Pack 35 Completions Complete the Glory Hunters Crafting Upgrade SBC 35 times. 1 Of 2 86+ Rare Gold Players 40 Completions Complete the Glory Hunters Crafting Upgrade SBC 40 times. 5X 83+ Rare Gold Players Pack 45 Completions Complete the Glory Hunters Crafting Upgrade SBC 45 times. 2X 85+ Rare Gold Players Pack 50 Completions Complete the Glory Hunters Crafting Upgrade SBC 50 times. 7X 83+ Rare Gold Players Pack 60 Completions Complete the Glory Hunters Crafting Upgrade SBC 60 times. 1 Of 3 86+ Rare Gold Players 70 Completions Complete the Glory Hunters Crafting Upgrade SBC 70 times. 4X 84+ Rare Gold Players Pack 80 Completions Complete the Glory Hunters Crafting Upgrade SBC 80 times. 3X 85+ Rare Gold Players Pack 90 Completions Complete the Glory Hunters Crafting Upgrade SBC 90 times. 5X 84+ Rare Gold Players Pack 95 Completions Complete the Glory Hunters Crafting Upgrade SBC 95 times. 3X 86+ Rare Gold Players Pack 100 Completions Complete the Glory Hunters Crafting Upgrade SBC 100 times. 1 Of 3 88+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 3 days 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Seasonal Objective Seasonal Objective - EA SPORTS FC 26 Objectives Complete Seasonal Objectives to earn SP! Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 1 day 3,000 total 5 Objectives 95% 5% Rewards 3,000 SP Play 25 Play 25 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 20 Play 20 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 15 Play 15 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 10 Play 10 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP Play 5 Play 5 matches in Squad Battles, Rush, Rivals, Champions or Live Events. 350 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 3 days 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Path to Glory Home Kit Path to Glory Home Kit - EA SPORTS FC 26 Objectives Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 1 day 2,000 total 3 Objectives 85% 15% Rewards 2,000 SP Win 3 Win 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 500 SP Score 3 Score 3 goals in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP Play 3 Play 3 matches in any Ultimate Team game mode while having the Path to Glory Home Kit equipped. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 3 days 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Season 8 Exhibition - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 1 day 7 Objectives 83% 17% Rewards Evo Unlock Evo Unlock 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 88+ Rare Gold Players Evo Unlock 1x 10x 87+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack 1x 3x 88+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Score in 30 Score at least 1 goal in 30 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 25 Score at least 1 goal in 25 separate matches in the Season 8 Exhibition event. Evo Unlock Score in 20 Score at least 1 goal in 20 separate matches with a ST in the Season 8 Exhibition event. 10X 87+ Rare Gold Players Pack Assist in 20 Assist at least 1 goal in 20 separate matches with a CM in the Season 8 Exhibition event. 1 Of 4 89+ Rare Gold Player Pick Play 20 Play 20 matches in the Season 8 Exhibition event. 5X 87+ Rare Gold Players Pack Play 10 Play 10 matches in the Season 8 Exhibition event. 1 Of 4 88+ Rare Gold Players Play 5 Play 5 matches in the Season 8 Exhibition event. 3X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 3 days 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Season 8 Exhibition Weekly Play - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 1 day 1 Objectives 92% 8% Rewards Item Shadow Play 9 Play 9 matches in the Season 8 Exhibition event. Item © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 3 days 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Season 8 Exhibition Weekly Play Completionist Season 8 Exhibition Weekly Play Completionist - EA SPORTS FC 26 Objectives Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 1 day 5 Objectives 86% 14% Rewards 1 Of 3 Fof Gh Team 1 Player Pick 1 Of 3 Fof Gotg Player Pick 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick 1x 93+ FOF PTG Team 2 Player Pack 1x 93+ FOF PTG Team 1 Player Pack 1x 5x 87+ Rare Gold Players Pack Week 5 Complete the Season 8 Exhibition Weekly Play Objective 5 times. 1 Of 3 Fof Gh Team 1 Player Pick Week 4 Complete the Season 8 Exhibition Weekly Play Objective 4 times. 1 Of 3 Fof Gotg Player Pick Week 3 Complete the Season 8 Exhibition Weekly Play Objective 3 times. 93+ Fof Ptg Team 2 Player Pack Week 2 Complete the Season 8 Exhibition Weekly Play Objective 2 times. 93+ Fof Ptg Team 1 Player Pack Week 1 Complete the Season 8 Exhibition Weekly Play Objective 1 time. 5X 87+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 3 days 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play Completionist Season 8 Weekly Play Completionist - EA SPORTS FC 26 Objectives Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 1 day 4 of 5 Objectives 91% 9% Rewards 1 Of 4 89+ Rare Gold Player Pick 1 Of 4 89+ Rare Gold Player Pick 1x 5x 88+ Rare Gold Players Pack 1x 3x 85+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x FOF PTG Player Pack Week 5 Complete the Season 8 Weekly Play 5 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 4 Complete the Season 8 Weekly Play 4 Objective. 1 Of 4 89+ Rare Gold Player Pick Week 3 Complete the Season 8 Weekly Play 3 Objective. 5X 88+ Rare Gold Players Pack Week 2 Complete the Season 8 Weekly Play 2 Objective. 3X 85+ Rare Gold Players Pack Week 1 Complete the Season 8 Weekly Play 1 Objective. 4X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2378,14 +2378,14 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; Play Like a Pro: Tekkz Play Like a Pro: Tekkz - EA SPORTS FC 26 Objectives Want to improve your finishing skills? Scan the QR code to watch the video and learn to play like a pro with a Finesse Shot tutorial from Tekkz. All rewards are untradeable. Play Like a Pro: Tekkz Want to improve your finishing skills? Scan the QR code to watch the video and learn to play like a pro with a Finesse Shot tutorial from Tekkz. All rewards are untradeable. 2X 82+ Rare Gold Players Pack Expires in 3 months 3 Objectives 30% 70% Rewards 10 2x 80+ Rare Gold Player Pack 1x 2x 82+ Rare Gold Players Pack Low Driven Finesse Shots Score 10 goals using a Low Driven Finesse Shot in any Ultimate Team game mode. 80+ Rare Gold Player Pack Long Finesse Shots Score 10 goals from outside the box using a Finesse Shot in any Ultimate Team game mode. 80+ Rare Gold Player Pack Finesse Shots Score 3 goals using a Finesse Shot in any Ultimate Team game mode. 10 Olivier Giroud (Loan) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; Play Like a Pro: Tekkz Play Like a Pro: Tekkz - EA SPORTS FC 26 Objectives Want to improve your finishing skills? Scan the QR code to watch the video and learn to play like a pro with a Finesse Shot tutorial from Tekkz. All rewards are untradeable. Play Like a Pro: Tekkz Want to improve your finishing skills? Scan the QR code to watch the video and learn to play like a pro with a Finesse Shot tutorial from Tekkz. All rewards are untradeable. 2X 82+ Rare Gold Players Pack Expires in 2 months 3 Objectives 30% 70% Rewards 10 2x 80+ Rare Gold Player Pack 1x 2x 82+ Rare Gold Players Pack Low Driven Finesse Shots Score 10 goals using a Low Driven Finesse Shot in any Ultimate Team game mode. 80+ Rare Gold Player Pack Long Finesse Shots Score 10 goals from outside the box using a Finesse Shot in any Ultimate Team game mode. 80+ Rare Gold Player Pack Finesse Shots Score 3 goals using a Finesse Shot in any Ultimate Team game mode. 10 Olivier Giroud (Loan) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2420,14 +2420,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; Play Like a Pro: ManuBachoore Play Like a Pro: ManuBachoore - EA SPORTS FC 26 Objectives Want to improve your finishing skills? Scan the QR Code to watch the video and learn to play like a pro with a Low Driven Shot tutorial from ManuBachoore. All rewards are untradeable. Play Like a Pro: ManuBachoore Want to improve your finishing skills? Scan the QR Code to watch the video and learn to play like a pro with a Low Driven Shot tutorial from ManuBachoore. All rewards are untradeable. 2X 82+ Rare Gold Players Pack Expires in 3 months 3 Objectives 30% 70% Rewards 10 2x 80+ Rare Gold Player Pack 1x 2x 82+ Rare Gold Players Pack Low Driven Power Shots Score 10 goals using a Low Driven Power Shot in any Ultimate Team game mode. 80+ Rare Gold Player Pack Low Driven Volleys Score 10 goals using a Low Driven Volley in any Ultimate Team game mode. 80+ Rare Gold Player Pack Low Driven Shots Score 3 goals using a Low Driven Shot in any Ultimate Team game mode. 10 Erling Haaland (Loan) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; Play Like a Pro: ManuBachoore Play Like a Pro: ManuBachoore - EA SPORTS FC 26 Objectives Want to improve your finishing skills? Scan the QR Code to watch the video and learn to play like a pro with a Low Driven Shot tutorial from ManuBachoore. All rewards are untradeable. Play Like a Pro: ManuBachoore Want to improve your finishing skills? Scan the QR Code to watch the video and learn to play like a pro with a Low Driven Shot tutorial from ManuBachoore. All rewards are untradeable. 2X 82+ Rare Gold Players Pack Expires in 2 months 3 Objectives 30% 70% Rewards 10 2x 80+ Rare Gold Player Pack 1x 2x 82+ Rare Gold Players Pack Low Driven Power Shots Score 10 goals using a Low Driven Power Shot in any Ultimate Team game mode. 80+ Rare Gold Player Pack Low Driven Volleys Score 10 goals using a Low Driven Volley in any Ultimate Team game mode. 80+ Rare Gold Player Pack Low Driven Shots Score 3 goals using a Low Driven Shot in any Ultimate Team game mode. 10 Erling Haaland (Loan) © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Teams FC Pro Teams - EA SPORTS FC 26 Objectives Build your collection of FC Pro Team Crests and Kits by completing the objective. All rewards are untradeable. FC Pro Teams Build your collection of FC Pro Team Crests and Kits by completing the objective. All rewards are untradeable. Single Draft Token Pack Expires in 3 months 13 Objectives 16% 84% Rewards Rblz Gaming Badge Twisted Minds Badge Badge Tuzzy Esports Team Vitality Badge Team Liquid Badge Team Falcons Badge Manchester City Esports Badge Luna Esports Badge Badge Gaimin Gladiators Futwiz Badge Fokus Badge Dux Badge Badge Blue United Efc 1x Single Draft Token Pack RBLZ Gaming Win 1 match in any Ultimate Team game mode while using at least 3 RB Leipzig (Bundesliga) players in your starting 11. Rblz Gaming Badge Twisted Minds Score 2 goals in any Ultimate Team game mode using a player from Saudi Arabia. Twisted Minds Badge Tuzzy E-sports Win 1 match in any Ultimate Team game mode while using at least 3 players from Brazil in your starting 11. Badge Tuzzy Esports Team Vitality Win 1 match in any Ultimate Team game mode while using at least 3 players from France in your starting 11. Team Vitality Badge Team Liquid Win 1 match in any Ultimate Team game mode while using at least 3 players from the Netherlands in your starting 11. Team Liquid Badge Team Falcons Win 1 match in any Ultimate Team game mode while using at least 3 players from Saudi Arabia in your starting 11. Team Falcons Badge Manchester City Esports Win 1 match in any Ultimate Team game mode while using at least 3 Manchester City players (Premier League) in your starting 11. Manchester City Esports Badge Luna Esports Win 1 match in any Ultimate Team game mode while using at least 3 players from Portugal in your starting 11. Luna Esports Badge Gaimin Gladiators Win 1 match in any Ultimate Team game mode while using at least 3 players from Canada in your starting 11. Badge Gaimin Gladiators FUTWIZ Win 1 match in any Ultimate Team game mode while using at least 3 players from England in your starting 11. Futwiz Badge FOKUS Win 1 match in any Ultimate Team game mode while using at least 3 players from Germany in your starting 11. Fokus Badge DUX Gaming Win 1 match in any Ultimate Team game mode while using at least 3 players from Spain in your starting 11. Dux Badge Blue United Win 1 match in any Ultimate Team game mode while using at least 3 players from Japan in your starting 11. Badge Blue United Efc © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Teams FC Pro Teams - EA SPORTS FC 26 Objectives Build your collection of FC Pro Team Crests and Kits by completing the objective. All rewards are untradeable. FC Pro Teams Build your collection of FC Pro Team Crests and Kits by completing the objective. All rewards are untradeable. Single Draft Token Pack Expires in 2 months 13 Objectives 16% 84% Rewards Rblz Gaming Badge Twisted Minds Badge Badge Tuzzy Esports Team Vitality Badge Team Liquid Badge Team Falcons Badge Manchester City Esports Badge Luna Esports Badge Badge Gaimin Gladiators Futwiz Badge Fokus Badge Dux Badge Badge Blue United Efc 1x Single Draft Token Pack RBLZ Gaming Win 1 match in any Ultimate Team game mode while using at least 3 RB Leipzig (Bundesliga) players in your starting 11. Rblz Gaming Badge Twisted Minds Score 2 goals in any Ultimate Team game mode using a player from Saudi Arabia. Twisted Minds Badge Tuzzy E-sports Win 1 match in any Ultimate Team game mode while using at least 3 players from Brazil in your starting 11. Badge Tuzzy Esports Team Vitality Win 1 match in any Ultimate Team game mode while using at least 3 players from France in your starting 11. Team Vitality Badge Team Liquid Win 1 match in any Ultimate Team game mode while using at least 3 players from the Netherlands in your starting 11. Team Liquid Badge Team Falcons Win 1 match in any Ultimate Team game mode while using at least 3 players from Saudi Arabia in your starting 11. Team Falcons Badge Manchester City Esports Win 1 match in any Ultimate Team game mode while using at least 3 Manchester City players (Premier League) in your starting 11. Manchester City Esports Badge Luna Esports Win 1 match in any Ultimate Team game mode while using at least 3 players from Portugal in your starting 11. Luna Esports Badge Gaimin Gladiators Win 1 match in any Ultimate Team game mode while using at least 3 players from Canada in your starting 11. Badge Gaimin Gladiators FUTWIZ Win 1 match in any Ultimate Team game mode while using at least 3 players from England in your starting 11. Futwiz Badge FOKUS Win 1 match in any Ultimate Team game mode while using at least 3 players from Germany in your starting 11. Fokus Badge DUX Gaming Win 1 match in any Ultimate Team game mode while using at least 3 players from Spain in your starting 11. Dux Badge Blue United Win 1 match in any Ultimate Team game mode while using at least 3 players from Japan in your starting 11. Badge Blue United Efc © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2504,14 +2504,14 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Teams Masterclass FC Pro Teams Masterclass - EA SPORTS FC 26 Objectives Use your collection of FC Pro Team Crests to complete the objective. All rewards are untradeable. FC Pro Teams Masterclass Use your collection of FC Pro Team Crests to complete the objective. All rewards are untradeable. 5X 80+ Rare Gold Players Pack Expires in 3 months 13 Objectives 16% 84% Rewards 13x 80+ Rare Gold Player Pack 1x 5x 80+ Rare Gold Players Pack RBLZ Gaming Win 2 games in any Ultimate Team game mode while equipping the RBLZ Gaming Crest. 80+ Rare Gold Player Pack Twisted Minds Win 2 games in any Ultimate Team game mode while equipping the Twisted Minds Crest. 80+ Rare Gold Player Pack Tuzzy E-sports Win 2 games in any Ultimate Team game mode while equipping the Tuzzy E-sports Crest. 80+ Rare Gold Player Pack Team Vitality Win 2 games in any Ultimate Team game mode while equipping the Team Vitality Crest. 80+ Rare Gold Player Pack Team Liquid Win 2 games in any Ultimate Team game mode while equipping the Team Liquid Crest. 80+ Rare Gold Player Pack Team Falcons Win 2 games in any Ultimate Team game mode while equipping the Team Falcons Crest. 80+ Rare Gold Player Pack Manchester City Esports Win 2 games in any Ultimate Team game mode while equipping the Manchester City Esports Crest. 80+ Rare Gold Player Pack Luna Esports Win 2 games in any Ultimate Team game mode while equipping the Luna Esports Crest. 80+ Rare Gold Player Pack Gaimin Gladiators Win 2 games in any Ultimate Team game mode while equipping the Gaimin Gladiators Crest. 80+ Rare Gold Player Pack FUTWIZ Win 2 games in any Ultimate Team game mode while equipping the FUTWIZ Crest. 80+ Rare Gold Player Pack FOKUS Win 2 games in any Ultimate Team game mode while equipping the FOKUS Crest. 80+ Rare Gold Player Pack DUX Gaming Win 2 games in any Ultimate Team game mode while equipping the DUX Gaming Crest. 80+ Rare Gold Player Pack Blue United Win 2 games in any Ultimate Team game mode while equipping the Blue United Crest. 80+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; FC Pro &gt; FC Pro Teams Masterclass FC Pro Teams Masterclass - EA SPORTS FC 26 Objectives Use your collection of FC Pro Team Crests to complete the objective. All rewards are untradeable. FC Pro Teams Masterclass Use your collection of FC Pro Team Crests to complete the objective. All rewards are untradeable. 5X 80+ Rare Gold Players Pack Expires in 2 months 13 Objectives 16% 84% Rewards 13x 80+ Rare Gold Player Pack 1x 5x 80+ Rare Gold Players Pack RBLZ Gaming Win 2 games in any Ultimate Team game mode while equipping the RBLZ Gaming Crest. 80+ Rare Gold Player Pack Twisted Minds Win 2 games in any Ultimate Team game mode while equipping the Twisted Minds Crest. 80+ Rare Gold Player Pack Tuzzy E-sports Win 2 games in any Ultimate Team game mode while equipping the Tuzzy E-sports Crest. 80+ Rare Gold Player Pack Team Vitality Win 2 games in any Ultimate Team game mode while equipping the Team Vitality Crest. 80+ Rare Gold Player Pack Team Liquid Win 2 games in any Ultimate Team game mode while equipping the Team Liquid Crest. 80+ Rare Gold Player Pack Team Falcons Win 2 games in any Ultimate Team game mode while equipping the Team Falcons Crest. 80+ Rare Gold Player Pack Manchester City Esports Win 2 games in any Ultimate Team game mode while equipping the Manchester City Esports Crest. 80+ Rare Gold Player Pack Luna Esports Win 2 games in any Ultimate Team game mode while equipping the Luna Esports Crest. 80+ Rare Gold Player Pack Gaimin Gladiators Win 2 games in any Ultimate Team game mode while equipping the Gaimin Gladiators Crest. 80+ Rare Gold Player Pack FUTWIZ Win 2 games in any Ultimate Team game mode while equipping the FUTWIZ Crest. 80+ Rare Gold Player Pack FOKUS Win 2 games in any Ultimate Team game mode while equipping the FOKUS Crest. 80+ Rare Gold Player Pack DUX Gaming Win 2 games in any Ultimate Team game mode while equipping the DUX Gaming Crest. 80+ Rare Gold Player Pack Blue United Win 2 games in any Ultimate Team game mode while equipping the Blue United Crest. 80+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr"/>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr"/>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr"/>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr"/>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr"/>
@@ -15374,7 +15374,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr"/>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr"/>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr"/>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr"/>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr"/>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr"/>
@@ -15918,7 +15918,7 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr"/>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr"/>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr"/>
@@ -16122,7 +16122,7 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr"/>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr"/>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr"/>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr"/>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr"/>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr"/>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr"/>
@@ -16666,7 +16666,7 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr"/>
@@ -16734,7 +16734,7 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr"/>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr"/>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr"/>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr"/>
@@ -17074,7 +17074,7 @@
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr"/>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr"/>
@@ -21881,12 +21881,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 4 days 4 Objectives 67% 33%</t>
+          <t>Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 3 days 4 Objectives 67% 33%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -21918,12 +21918,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 4 days 3 of 4 Objectives 73% 27%</t>
+          <t>Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 3 days 3 of 4 Objectives 73% 27%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -21955,12 +21955,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 4 days 3 of 4 Objectives 79% 21%</t>
+          <t>Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 3 days 3 of 4 Objectives 79% 21%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -22017,12 +22017,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 4 days 6 Objectives 82% 18%</t>
+          <t>Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 80% 20%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 4 days 4 Objectives 70% 30%</t>
+          <t>Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 3 days 4 Objectives 68% 32%</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -22091,12 +22091,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 4 days 3 of 4 Objectives 84% 16%</t>
+          <t>Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 3 days 3 of 4 Objectives 82% 18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -22128,12 +22128,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 4 days 2 Objectives 88% 12%</t>
+          <t>Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 3 days 2 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -22165,12 +22165,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 4 days 4 Objectives 90% 10%</t>
+          <t>Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 3 days 4 Objectives 88% 13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Expires in 4 days</t>
+          <t>Expires in 3 days</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -22202,12 +22202,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 3 days 7,000 total 5 Objectives 89% 11%</t>
+          <t>Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 2 days 7,000 total 5 Objectives 89% 11%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -22239,12 +22239,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 32% 68%</t>
+          <t>Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 31% 69%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -22276,12 +22276,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 77% 23%</t>
+          <t>Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 2 days 2,000 total 3 of 5 Objectives 76% 24%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -22313,12 +22313,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 3 days 3,000 total 5 Objectives 77% 23%</t>
+          <t>Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 2 days 3,000 total 5 Objectives 77% 23%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -22350,12 +22350,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 3 days 300 total 2 Objectives 71% 29%</t>
+          <t>Daily Objectives Play, complete, and earn SP from the daily Objective every 24 hours! 100 SP Expires in 2 days 300 total 2 Objectives 71% 29%</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -22437,12 +22437,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 17 days 15 Objectives 41% 59%</t>
+          <t>Glory Hunters Crafting Upgrade Completionist Complete the Glory Hunters Crafting Upgrade to earn additional pack rewards! All rewards are untradeable. 100 Rare Gold Players Pack Expires in 16 days 15 Objectives 41% 59%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Expires in 17 days</t>
+          <t>Expires in 16 days</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -22474,12 +22474,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 3 days 3,000 total 5 Objectives 95% 5%</t>
+          <t>Seasonal Objective Complete Seasonal Objectives to earn SP! 1250 SP Expires in 2 days 3,000 total 5 Objectives 95% 5%</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -22511,12 +22511,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 3 days 2,000 total 3 Objectives 85% 15%</t>
+          <t>Path to Glory Home Kit Equip the Path to Glory Home Kit and complete the objectives to earn additional SP. 1000 SP Expires in 2 days 2,000 total 3 Objectives 85% 15%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -22548,12 +22548,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 3 days 7 Objectives 83% 17%</t>
+          <t>Season 8 Exhibition Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 5X 88+ Rare Gold Players Pack Evo Unlock Expires in 2 days 7 Objectives 83% 17%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -22585,12 +22585,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 3 days 1 Objectives 92% 8%</t>
+          <t>Season 8 Exhibition Weekly Play Compete in the Season 8 Exhibition event to earn Coin boost and a consumable item! All rewards are untradeable. Shadow Expires in 2 days 1 Objectives 92% 8%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -22622,12 +22622,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 3 days 5 Objectives 86% 14%</t>
+          <t>Season 8 Exhibition Weekly Play Completionist Compete in the Season 8 Exhibition event to earn exclusive rewards! All rewards are untradeable. 1 Of 3 94+ Fof Ptg/Gotg/Gh Team 1 Player Pick Expires in 2 days 5 Objectives 86% 14%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 3 days 4 of 5 Objectives 91% 9%</t>
+          <t>Season 8 Weekly Play Completionist Complete any 4 of the 5 Season 8 Weekly Play Objectives and claim bonus pack rewards. All rewards are untradeable. Fof Ptg Player Pack Expires in 2 days 4 of 5 Objectives 91% 9%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 days</t>
+          <t>Expires in 2 days</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -23099,12 +23099,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Play Like a Pro: Tekkz Want to improve your finishing skills? Scan the QR code to watch the video and learn to play like a pro with a Finesse Shot tutorial from Tekkz. All rewards are untradeable. 2X 82+ Rare Gold Players Pack Expires in 3 months 3 Objectives 30% 70%</t>
+          <t>Play Like a Pro: Tekkz Want to improve your finishing skills? Scan the QR code to watch the video and learn to play like a pro with a Finesse Shot tutorial from Tekkz. All rewards are untradeable. 2X 82+ Rare Gold Players Pack Expires in 2 months 3 Objectives 30% 70%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -23128,12 +23128,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Play Like a Pro: ManuBachoore Want to improve your finishing skills? Scan the QR Code to watch the video and learn to play like a pro with a Low Driven Shot tutorial from ManuBachoore. All rewards are untradeable. 2X 82+ Rare Gold Players Pack Expires in 3 months 3 Objectives 30% 70%</t>
+          <t>Play Like a Pro: ManuBachoore Want to improve your finishing skills? Scan the QR Code to watch the video and learn to play like a pro with a Low Driven Shot tutorial from ManuBachoore. All rewards are untradeable. 2X 82+ Rare Gold Players Pack Expires in 2 months 3 Objectives 30% 70%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -23157,12 +23157,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>FC Pro Teams Build your collection of FC Pro Team Crests and Kits by completing the objective. All rewards are untradeable. Single Draft Token Pack Expires in 3 months 13 Objectives 16% 84%</t>
+          <t>FC Pro Teams Build your collection of FC Pro Team Crests and Kits by completing the objective. All rewards are untradeable. Single Draft Token Pack Expires in 2 months 13 Objectives 16% 84%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -23186,12 +23186,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>FC Pro Teams Masterclass Use your collection of FC Pro Team Crests to complete the objective. All rewards are untradeable. 5X 80+ Rare Gold Players Pack Expires in 3 months 13 Objectives 16% 84%</t>
+          <t>FC Pro Teams Masterclass Use your collection of FC Pro Team Crests to complete the objective. All rewards are untradeable. 5X 80+ Rare Gold Players Pack Expires in 2 months 13 Objectives 16% 84%</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Expires in 3 months</t>
+          <t>Expires in 2 months</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -23616,7 +23616,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Bonus Completionist Knockout Glory 2 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 4 days 4 Objectives 67% 33% Rewards 50 Tokens 2 Of 8 Playstyle+ Pick Evo Unlock 1 Of 2 86+ Rare Gold Players Evo Unlock 1x 6x 83+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 2 Tournament. 50 Tokens 2 Of 8 Playstyle+ Pick Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 2 Tournament. Evo Unlock Win Semi-Finals Win the Semi-Finals in the Knockout Glory 2 Tournament. 6X 83+ Rare Gold Players Pack Win the Final Win the Knockout Glory 2 Tournament. 1 Of 2 86+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Bonus Completionist Knockout Glory 2 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 2 Bonus Completionist Compete and dominate in the Knockout Glory 2 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 5X 87+ Rare Gold Players Pack Evo Unlock Expires in 3 days 4 Objectives 67% 33% Rewards 50 Tokens 2 Of 8 Playstyle+ Pick Evo Unlock 1 Of 2 86+ Rare Gold Players Evo Unlock 1x 6x 83+ Rare Gold Players Pack 1x 5x 87+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 2 Tournament. 50 Tokens 2 Of 8 Playstyle+ Pick Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 2 Tournament. Evo Unlock Win Semi-Finals Win the Semi-Finals in the Knockout Glory 2 Tournament. 6X 83+ Rare Gold Players Pack Win the Final Win the Knockout Glory 2 Tournament. 1 Of 2 86+ Rare Gold Players © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23638,7 +23638,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Tournament Knockout Glory 2 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 4 days 3 of 4 Objectives 73% 27% Rewards 2 Of 8 Playstyle+ Pick Evo Unlock 2 Of 8 Playstyle+ Pick 100 Tokens Evo Unlock 1x 3x 83+ Rare Gold Players Pack 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 2 Tournament. 3X 83+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 2 Tournament. Evo Unlock 2 Of 8 Playstyle+ Pick Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 2 Tournament Knockout Glory 2 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 2 Tournament Complete 3 out of the 4 challenges to earn Glory Hunters Gavi, Packs, Tokens and Evolutions. All rewards are untradeable. Gavi 100 Tokens Evo Unlock Expires in 3 days 3 of 4 Objectives 73% 27% Rewards 2 Of 8 Playstyle+ Pick Evo Unlock 2 Of 8 Playstyle+ Pick 100 Tokens Evo Unlock 1x 3x 83+ Rare Gold Players Pack 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 2 Tournament. 3X 83+ Rare Gold Players Pack 2 Of 8 Playstyle+ Pick Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 2 Tournament. Evo Unlock 2 Of 8 Playstyle+ Pick Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 2 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23660,7 +23660,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Switch it Up! Switch it Up! - EA SPORTS FC 26 Objectives Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 4 days 3 of 4 Objectives 79% 21% Rewards 5000 Coins 5000 Coins 5000 Coins 5000 Coins Evo Unlock 3 Back Swag Score at least 1 goal in 5 separate matches using the 3-5-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Back to Basics Score at least 1 goal in 5 separate matches using the 4-4-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins The Other 4-5-1 Score at least 1 goal in 5 separate matches using the 4-5-1 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Try Something New! Score at least 1 goal in 50 separate matches using the 4-4-1-1(2) formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Switch it Up! Switch it Up! - EA SPORTS FC 26 Objectives Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Switch it Up! Give more formations a try and complete 3 of 4 challenges to earn coins and an Evolution! All rewards untradeable. Evo Unlock Expires in 3 days 3 of 4 Objectives 79% 21% Rewards 5000 Coins 5000 Coins 5000 Coins 5000 Coins Evo Unlock 3 Back Swag Score at least 1 goal in 5 separate matches using the 3-5-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Back to Basics Score at least 1 goal in 5 separate matches using the 4-4-2 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins The Other 4-5-1 Score at least 1 goal in 5 separate matches using the 4-5-1 formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins Try Something New! Score at least 1 goal in 50 separate matches using the 4-4-1-1(2) formation (without changing) in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions) while having min. 3 Glory Hunters players in your starting 11. 5000 Coins © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23704,7 +23704,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Europe Journey of Nations Europe - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 4 days 6 Objectives 82% 18% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Europe Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Europe Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Europe Live Event. Award Win 3 Win 3 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Journey of Nations Europe Journey of Nations Europe - EA SPORTS FC 26 Objectives Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. Journey of Nations Europe Compete in the Journey of Nations Europe Live Event to earn exclusive rewards! All rewards untradeable. 3X 84+ Rare Gold Players Pack Expires in 3 days 6 Objectives 80% 20% Rewards Hunter Shadow Award 3x 3x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Journey of Nations Europe Live Event. Hunter Win 1 Win 1 match in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Play 4 Play 4 matches in the Journey of Nations Europe Live Event. Shadow Win 2 Win 2 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack Score 5 Score 5 goals in the Journey of Nations Europe Live Event. Award Win 3 Win 3 matches in the Journey of Nations Europe Live Event. 3X 83+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23726,7 +23726,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Bonus Completionist Knockout Glory 1 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 4 days 4 Objectives 70% 30% Rewards Pinged Pass+ 50 Tokens Evo Unlock 1x 5x 84+ Rare Gold Players Pack 1x 8x 85+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 1 Tournament. 50 Tokens Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 1 Tournament. Pinged Pass+ Win Semi-Finals Win the Semi-Finals in the Knockout Glory 1 Tournament. Evo Unlock Win the Final Win the Knockout Glory 1 Tournament. 5X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Bonus Completionist Knockout Glory 1 Bonus Completionist - EA SPORTS FC 26 Objectives Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. Knockout Glory 1 Bonus Completionist Compete and dominate in the Knockout Glory 1 Tournament and prove your knockout pedigree to earn packs, tokens and consumables! All rewards untradeable. 8X 85+ Rare Gold Players Pack Expires in 3 days 4 Objectives 68% 32% Rewards Pinged Pass+ 50 Tokens Evo Unlock 1x 5x 84+ Rare Gold Players Pack 1x 8x 85+ Rare Gold Players Pack Win Round of 16 Win the Round of 16 in the Knockout Glory 1 Tournament. 50 Tokens Win Quarter-Finals Win the Quarter-Finals in the Knockout Glory 1 Tournament. Pinged Pass+ Win Semi-Finals Win the Semi-Finals in the Knockout Glory 1 Tournament. Evo Unlock Win the Final Win the Knockout Glory 1 Tournament. 5X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23748,7 +23748,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Tournament Knockout Glory 1 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 4 days 3 of 4 Objectives 84% 16% Rewards 10 Creating Space Evo Unlock 100 Tokens 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 1 Tournament. Evo Unlock Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 1 Tournament. 10 Antoine Semenyo (Loan) Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory 1 Tournament Knockout Glory 1 Tournament - EA SPORTS FC 26 Objectives Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Knockout Glory 1 Tournament Complete 3 out of the 4 challenges to earn Packs, Tokens and Evolutions. All rewards are untradeable. Creating Space 100 Tokens Expires in 3 days 3 of 4 Objectives 82% 18% Rewards 10 Creating Space Evo Unlock 100 Tokens 2x 3x 84+ Rare Gold Players Pack Play 2 Play 2 matches in the Knockout Glory 1 Tournament. Evo Unlock Score in 4 Score 1 goal in 4 separate matches in the Knockout Glory 1 Tournament. 10 Antoine Semenyo (Loan) Score in 8 Score 1 goal in 8 separate matches in the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack Win Tournament Win the Knockout Glory 1 Tournament. 3X 84+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23770,7 +23770,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory Bonus Completionist Knockout Glory Bonus Completionist - EA SPORTS FC 26 Objectives Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 4 days 2 Objectives 88% 12% Rewards 1 Of 3 89+ Rare Gold Player Pick 1x 7x 86+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Knockout Glory 1 Complete the Knockout Glory 1 Bonus Objective. 7X 86+ Rare Gold Players Pack Knockout Glory 2 Complete the Knockout Glory 2 Bonus Objective. 5X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Live Events &gt; Knockout Glory Bonus Completionist Knockout Glory Bonus Completionist - EA SPORTS FC 26 Objectives Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. Knockout Glory Bonus Completionist Complete the Knockout Glory Bonus Objectives to earn bonus packs! All rewards untradeable. 1 Of 3 89+ Rare Gold Player Pick Expires in 3 days 2 Objectives 86% 14% Rewards 1 Of 3 89+ Rare Gold Player Pick 1x 7x 86+ Rare Gold Players Pack 1x 5x 88+ Rare Gold Players Pack Knockout Glory 1 Complete the Knockout Glory 1 Bonus Objective. 7X 86+ Rare Gold Players Pack Knockout Glory 2 Complete the Knockout Glory 2 Bonus Objective. 5X 88+ Rare Gold Players Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 2 Glory Hunters Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 4 days 4 Objectives 90% 10% Rewards Consumable 30 Tokens Shadow 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Consumable Score in 5 Score in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens Scoring Striker Score with a ST in 10 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Shadow Assist in 15 Assist in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Glory Hunters Week 2 Glory Hunters Week 2 - EA SPORTS FC 26 Objectives Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable Glory Hunters Week 2 Complete all the challenges to earn Festival of Football Tokens and Chemistry Styles! All rewards are untradeable 40 Tokens Expires in 3 days 4 Objectives 88% 13% Rewards Consumable 30 Tokens Shadow 30 Tokens 40 Tokens Play 3 Play 3 matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Consumable Score in 5 Score in 5 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens Scoring Striker Score with a ST in 10 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). Shadow Assist in 15 Assist in 15 separate matches in Squad Battles on min. Semi-Pro Difficulty (or Live Events/Rivals/Champions). 30 Tokens © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23814,7 +23814,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Festival of Football SP Chase Festival of Football SP Chase - EA SPORTS FC 26 Objectives Complete challenges across Ultimate Team to earn SP! Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 3 days 7,000 total 5 Objectives 89% 11% Rewards 7,000 SP Score 5 Score 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Assist 5 Assist 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Play 10 Play 10 Rivals matches. 750 SP Complete 7 Complete any 7 SBC groups. 750 SP Play 15 Play 15 matches in any Ultimate Team game mode. 750 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Festival of Football SP Chase Festival of Football SP Chase - EA SPORTS FC 26 Objectives Complete challenges across Ultimate Team to earn SP! Festival of Football SP Chase Complete challenges across Ultimate Team to earn SP! 3250 SP Expires in 2 days 7,000 total 5 Objectives 89% 11% Rewards 7,000 SP Score 5 Score 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Assist 5 Assist 5 goals in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 750 SP Play 10 Play 10 Rivals matches. 750 SP Complete 7 Complete any 7 SBC groups. 750 SP Play 15 Play 15 matches in any Ultimate Team game mode. 750 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23836,7 +23836,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 3 days 5 Objectives 32% 68% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Campaign &gt; Weekly Rush Points Weekly Rush Points - EA SPORTS FC 26 Objectives Complete Rush Bonuses alongside your teammates to earn Rush Points! Weekly Rush Points Complete Rush Bonuses alongside your teammates to earn Rush Points! 2X 89+ Rare Gold Players Pack 100 Tokens Expires in 2 days 5 Objectives 31% 69% Rewards 100 Tokens 1x 4x 83+ Rare Gold Players Pack 1x 3x 84+ Rare Gold Players Pack 1x 4x 84+ Rare Gold Players Pack 1x 2x 85+ Rare Gold Players Pack 1x 88+ Rare Gold Player Pack 1x 2x 89+ Rare Gold Players Pack 2,500 Rush Points Earn 2,500 points by completing bonuses in Rush. 4X 83+ Rare Gold Players Pack 10,000 Rush Points Earn 10,000 points by completing bonuses in Rush. 3X 84+ Rare Gold Players Pack 25,000 Rush Points Earn 25,000 points by completing bonuses in Rush. 4X 84+ Rare Gold Players Pack 35,000 Rush Points Earn 35,000 points by completing bonuses in Rush. 2X 85+ Rare Gold Players Pack 45,000 Rush Points Earn 45,000 points by completing bonuses in Rush. 88+ Rare Gold Player Pack © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 3 days 2,000 total 3 of 5 Objectives 77% 23% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Season 8 Weekly Play 5 Season 8 Weekly Play 5 - EA SPORTS FC 26 Objectives Complete 3 out of the 5 challenges to earn SP! Season 8 Weekly Play 5 Complete 3 out of the 5 challenges to earn SP! 750 SP Expires in 1 day 2,000 total 3 of 5 Objectives 76% 24% Rewards 2,000 SP Play 5 Squad Battles Play 5 Squad Battles matches on Min. Semi-Pro difficulty. 250 SP Play 5 Rivals Play 5 matches in Rivals. 250 SP Play 5 Champions Play 5 matches in Champions. 250 SP Play 5 Rush Play 5 Ultimate Team Rush matches. 250 SP Play 5 Live Events Play 5 matches in any Ultimate Team Live Event. 250 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
         </is>
       </c>
     </row>
@@ -23880,7 +23880,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 3 days 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Score 10 Score 10 goals in any Ultimate Team game mode using a player from Mexico. 450 SP © 2026 Stormstrike Inc. All rights reserved. Privacy Policy | Terms of Service | Business Inquiries | FIFAIndex | MUT.GG | CFB.FAN | ForzaGarage</t>
+          <t>Players SBC Squad Builder Evolutions Objectives Evo Lab GG Club Log In FUT.GG &gt; Objectives &gt; Seasonal &gt; Weekly Objectives Weekly Objectives - EA SPORTS FC 26 Objectives Complete weekly Objectives to earn SP! Weekly Objectives Complete weekly Objectives to earn SP! 750 SP Expires in 1 day 3,000 total 5 Objectives 77% 23% Rewards 3,000 SP List 10 List 10 Player Items on the Transfer Market. 450 SP Buy 10 Buy 10 Player Items on the Transfer Market. 450 SP Play 10 Play 10 matches in Squad Battles on Min. Semi-Pro difficulty (or Rush/Rivals/Champions/Live Events). 450 SP Win 10 Win 10 matches in Squad Battles on Min. Semi-Pro